--- a/data/database.xlsx
+++ b/data/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oleh.koval\Desktop\Правила_9пакет\prodject_rules\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE126D2E-6FAE-4C20-93DD-6FBE98CCE8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED5C2E66-FA9D-4C44-A17E-9366310D5C43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="128">
   <si>
     <t>cod</t>
   </si>
@@ -283,6 +283,135 @@
   </si>
   <si>
     <t>Активне</t>
+  </si>
+  <si>
+    <t>LR.2.2</t>
+  </si>
+  <si>
+    <t>Дослідження маркерів ураження серцевого або скелетних м’язів</t>
+  </si>
+  <si>
+    <t>LR22</t>
+  </si>
+  <si>
+    <t>Дослідження маркерів ураження серцевого або скелетних м’язів: креатинкінази (код 2157-6), креатинкінази МВ (код 32673-6), тропоніну (код 42757-5) або міоглобіну (код K34003) за 24 годин При визначенні вартості за проведення вказаних досліджень з одного зразка застосовуються такі додаткові коефіцієнти: ▪ При одночасному виконанні двох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97. Оплата здійснюється за проведення максимум 2-х показників з переліку</t>
+  </si>
+  <si>
+    <t>LR.2.3</t>
+  </si>
+  <si>
+    <t>Визначення субкласів ліпопротеідів</t>
+  </si>
+  <si>
+    <t>LR23</t>
+  </si>
+  <si>
+    <t>Визначення субкласів ліпопротеідів (код 14646-4 та код 22748-8) Оплата здійснюється за дослідження, що виконані не більше двох разів за 12 місяців.</t>
+  </si>
+  <si>
+    <t>LR.2.4</t>
+  </si>
+  <si>
+    <t>Визначення вітаміну B1</t>
+  </si>
+  <si>
+    <t>LR24</t>
+  </si>
+  <si>
+    <t>Визначення вітаміну B1 (код 32554-8) або вітаміну B2 (код 73723-9), або вітаміну B3 (код 79402-4), або вітаміну B6 (код 39786-9), або вітаміну A/ретинол (код F34001) або вітаміну C (код 1903-4). Оплата здійснюється за дослідження кожного показника з переліку, що виконаний не більше двох разів за 12 місяців.</t>
+  </si>
+  <si>
+    <t>LR.2.5</t>
+  </si>
+  <si>
+    <t>Визначення вітаміну B12</t>
+  </si>
+  <si>
+    <t>LR25</t>
+  </si>
+  <si>
+    <t>Визначення вітаміну B12 (код B34015). Оплата здійснюється за дослідження, що виконане не більше одного разу за 12 місяців.</t>
+  </si>
+  <si>
+    <t>LR.2.6</t>
+  </si>
+  <si>
+    <t>Визначення мозкового натрійуретичного пропептиду</t>
+  </si>
+  <si>
+    <t>LR26</t>
+  </si>
+  <si>
+    <t>Визначення мозкового натрійуретичного пропептиду (NT-proBNP) (код 33762-6): - у пацієнта із системною склеродермією (код за МКХ-10 L94.0 або L94.1, або M33.9 ) – оплата здійснюється за дослідження, що виконані не більше 2-х разів за 12 місяців - у пацієнта із легеневою артеріальною гіпертензією (код за МКХ-10 I27) для спостереження за прогресуванням захворювання – оплата здійснюється за дослідження, що виконані не більше 4-х разів за 12 місяців</t>
+  </si>
+  <si>
+    <t>LR.2.7</t>
+  </si>
+  <si>
+    <t>Визначення онкомаркерів</t>
+  </si>
+  <si>
+    <t>LR27</t>
+  </si>
+  <si>
+    <t>Визначення онкомаркерів: альфа-фетопротеїну (код 1834-1 або код 19176-7), антигену CA 15.3 (код A33027), антигену CA 19.9 (код A33028), антигену CA 125 (код A33026), сироваткового антигену, асоційованого з раком (CASA) (код S34001), раково-ембріонального антигену (код A33029), бета-субодиниці хоріонічного гонадотропіну людини (код 21198-7), нейрон специфічної енолази (код 44802-7 або код 15060-7), тиреоглобуліну (код 3013-0 або код 14918-7) в сироватці або іншій рідині організму. При визначенні вартості за проведення вказаних досліджень з одного зразка застосовуються такі додаткові коефіцієнти: ▪ При одночасному виконанні двох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97. Оплата здійснюється за дослідження кожного показника з переліку не більше 2 разів за 12 місяців</t>
+  </si>
+  <si>
+    <t>LR.2.8</t>
+  </si>
+  <si>
+    <t>Визначення простатоспецифічного антигену</t>
+  </si>
+  <si>
+    <t>LR28</t>
+  </si>
+  <si>
+    <t>Визначення простатоспецифічного антигену (код Y34003): - для пацієнтів високого ризику – оплата здійснюється за дослідження один раз на 11 місяців - для будь-якого іншого пацієнта – оплата здійснюється за дослідження один раз на 23 місяців</t>
+  </si>
+  <si>
+    <t>LR.2.9</t>
+  </si>
+  <si>
+    <t>Кількісне визначення фракцій ПСА</t>
+  </si>
+  <si>
+    <t>LR29</t>
+  </si>
+  <si>
+    <t>Кількісне визначення фракцій ПСА та будь-якого похідного індексу (код Y34011 Аналіз; вільний/загальний простатичний специфічний антиген) – оплата здійснюється при таких результатах простатоспецифічного антигену (код Y34003): (a) понад 2,0 нг/мл, але менше або дорівнює 5,5 нг/мл для пацієнтів із сімейним анамнезом раку простати; або (b) більше 3,0 нг/мл, але менше або дорівнює 5,5 нг/мл для пацієнтів віком від 50 років, але менше 70 років; або (c) понад 5,5 нг/мл, але менше або дорівнює 10,0 нг/мл для пацієнтів віком щонайменше 70 років Оплата здійснюється за дослідження показника не частіше одного разу на 11 місяців Включає код Y34003 Аналіз; простатичний специфічний антиген (ПСА)</t>
+  </si>
+  <si>
+    <t>LR.2.10</t>
+  </si>
+  <si>
+    <t>LR210</t>
+  </si>
+  <si>
+    <t>Визначення простатоспецифічного антигену (код Y34011 або Y34011) для моніторингу раніше діагностованих захворювань передміхурової залози (включаючи рак передміхурової залози (код C61), простатит (код N41) або передракові захворювання, такі як атипова проліферація малих ацинусів (код N42.3). Оплата здійснюється за кожне проведене дослідження.</t>
+  </si>
+  <si>
+    <t>LR.2.11</t>
+  </si>
+  <si>
+    <t>Кількісне визначення в крові або сечі гормонів і білків</t>
+  </si>
+  <si>
+    <t>LR211</t>
+  </si>
+  <si>
+    <t>Кількісне визначення в крові або сечі гормонів і білків, що зв’язують гормони — АКТГ (код T34034), тиреотропний гормон (тиреотропін,ТТГ) (код T34028), альдостерон (код T34029), андростендіон (код X34001), С-пептид (код T34021), кортизол (код T34007), дегідроепіандростерон-сульфат ДГЕАС (DHEAS) (код A34025), тестостерон (код A34033 або X34007), ФСГ (код Y34006 або X34005), гормон росту (код 2963-7), 17-оксипрогестерон (17-ОН) (код 1668-3), інсулін (код T34019), ЛГ (код X34002 або Y34007), естрадіол (код X34004 або Y34008), прогестерон (код X34003 або Y34009), пролактин (код A34032), паратиреоїдний гормон (код 14866-8), ренін (код A34040), глобулін, що зв’язує статеві гормони (код X34006 або Y34004) При визначенні вартості за проведення вказаних досліджень з одного зразка застосовуються такі додаткові коефіцієнти: ▪ При одночасному виконанні двох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97. ▪ При одночасному виконанні трьох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97; на 3-ий показник – коефіцієнт 0,94. ▪ При одночасному виконанні чотирьох показників або більше показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97; на 3-й показник – коефіцієнт 0,94; на 4-й показник – коефіцієнт 0,91. ▪ При одночасному виконанні п’яти показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97; на 3-й показник – коефіцієнт 0,94; на 4-й показник – коефіцієнт 0,91, на 5-й показник – коефіцієнт 0,88. Оплата здійснюється за проведення максимум 5-х показників з переліку</t>
+  </si>
+  <si>
+    <t>LR.2.12</t>
+  </si>
+  <si>
+    <t>Визначення глюкози</t>
+  </si>
+  <si>
+    <t>LR212</t>
+  </si>
+  <si>
+    <t>Визначення глюкози (коди T34005 Аналіз; глюкоза або T34026 Аналіз; глюкоза; випадкова або T34025 Аналіз; глюкоза; натщесерце) Оплата здійснюється при наявності у ДЗ ЕМЗ «спостереження» з кодом 15074-8)</t>
   </si>
 </sst>
 </file>
@@ -616,7 +745,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
@@ -869,6 +998,160 @@
         <v>26</v>
       </c>
     </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" t="s">
+        <v>86</v>
+      </c>
+      <c r="D19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" t="s">
+        <v>98</v>
+      </c>
+      <c r="D22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" t="s">
+        <v>102</v>
+      </c>
+      <c r="D23" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" t="s">
+        <v>105</v>
+      </c>
+      <c r="C24" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" t="s">
+        <v>113</v>
+      </c>
+      <c r="C26" t="s">
+        <v>114</v>
+      </c>
+      <c r="D26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C27" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" t="s">
+        <v>124</v>
+      </c>
+      <c r="C29" t="s">
+        <v>125</v>
+      </c>
+      <c r="D29" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -877,7 +1160,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D456371C-55CC-41A7-AFCE-65668AB9659F}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="18.21875" customWidth="1"/>
@@ -1107,6 +1390,193 @@
         <v>80</v>
       </c>
     </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18">
+        <v>9</v>
+      </c>
+      <c r="C18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>111</v>
+      </c>
+      <c r="B20">
+        <v>9</v>
+      </c>
+      <c r="C20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21">
+        <v>9</v>
+      </c>
+      <c r="C21" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23">
+        <v>9</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>74</v>
+      </c>
+      <c r="E23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>126</v>
+      </c>
+      <c r="B24">
+        <v>9</v>
+      </c>
+      <c r="C24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" t="s">
+        <v>124</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1115,7 +1585,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D500C81C-80F5-46C0-959E-2202AF945DAB}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
@@ -1391,7 +1861,228 @@
         <v>83</v>
       </c>
     </row>
+    <row r="14" spans="1:8" ht="86.4">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" s="2">
+        <v>45658</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="28.8">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>84</v>
+      </c>
+      <c r="E15" s="2">
+        <v>45658</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="57.6">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" s="2">
+        <v>45658</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="28.8">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" s="2">
+        <v>45658</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="76.2" customHeight="1">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>84</v>
+      </c>
+      <c r="E18" s="2">
+        <v>45658</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="127.8" customHeight="1">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" s="2">
+        <v>45658</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="43.2">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="115.2">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>115</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="57.6">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>118</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>84</v>
+      </c>
+      <c r="E22" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="273.60000000000002">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>122</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="43.2">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>126</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/database.xlsx
+++ b/data/database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oleh.koval\Desktop\Правила_9пакет\prodject_rules\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED5C2E66-FA9D-4C44-A17E-9366310D5C43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8E0B88-9000-4CFA-86AE-362BDC2738D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33900" yWindow="2985" windowWidth="21600" windowHeight="11235" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dicts" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="129">
   <si>
     <t>cod</t>
   </si>
@@ -412,6 +412,9 @@
   </si>
   <si>
     <t>Визначення глюкози (коди T34005 Аналіз; глюкоза або T34026 Аналіз; глюкоза; випадкова або T34025 Аналіз; глюкоза; натщесерце) Оплата здійснюється при наявності у ДЗ ЕМЗ «спостереження» з кодом 15074-8)</t>
+  </si>
+  <si>
+    <t>docs/nakaz_377.pdf</t>
   </si>
 </sst>
 </file>
@@ -2094,8 +2097,8 @@
   <cols>
     <col min="2" max="2" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.44140625" customWidth="1"/>
-    <col min="6" max="6" width="16.44140625" customWidth="1"/>
+    <col min="5" max="5" width="69.21875" customWidth="1"/>
+    <col min="6" max="6" width="18.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2134,6 +2137,9 @@
       <c r="E2" t="s">
         <v>39</v>
       </c>
+      <c r="F2" t="s">
+        <v>128</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/database.xlsx
+++ b/data/database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oleh.koval\Desktop\Правила_9пакет\prodject_rules\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8E0B88-9000-4CFA-86AE-362BDC2738D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A04C1FC-8565-4F0E-9ACC-4253510101D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33900" yWindow="2985" windowWidth="21600" windowHeight="11235" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dicts" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="134">
   <si>
     <t>cod</t>
   </si>
@@ -415,6 +415,21 @@
   </si>
   <si>
     <t>docs/nakaz_377.pdf</t>
+  </si>
+  <si>
+    <t>Модифіковано</t>
+  </si>
+  <si>
+    <t>Змінено 1.09.2025 *(виключено код X34001, доповнено кодом W34001)</t>
+  </si>
+  <si>
+    <t>Кількісне визначення в крові або сечі гормонів і білків, що зв’язують гормони — АКТГ (код T34034), тиреотропний гормон (тиреотропін,ТТГ) (код T34028), альдостерон (код T34029), андростендіон (код W34001)*, С-пептид (код T34021), кортизол (код T34007), дегідроепіандростерон-сульфат ДГЕАС (DHEAS) (код A34025), тестостерон (код A34033 або X34007), ФСГ (код Y34006 або X34005), гормон росту (код 2963-7), 17-оксипрогестерон (17-ОН) (код 1668-3), інсулін (код T34019), ЛГ (код X34002 або Y34007), естрадіол (код X34004 або Y34008), прогестерон (код X34003 або Y34009), пролактин (код A34032), паратиреоїдний гормон (код 14866-8), ренін (код A34040), глобулін, що зв’язує статеві гормони (код X34006 або Y34004) При визначенні вартості за проведення вказаних досліджень з одного зразка застосовуються такі додаткові коефіцієнти: ▪ При одночасному виконанні двох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97. ▪ При одночасному виконанні трьох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97; на 3-ий показник – коефіцієнт 0,94. ▪ При одночасному виконанні чотирьох показників або більше показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97; на 3-й показник – коефіцієнт 0,94; на 4-й показник – коефіцієнт 0,91. При одночасному виконанні п’яти показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97; на 3-й показник – коефіцієнт 0,94; на 4-й показник – коефіцієнт 0,91, на 5-й показник – коефіцієнт 0,88. Оплата здійснюється за проведення максимум 5-х показників з переліку</t>
+  </si>
+  <si>
+    <t>Про внесення змін до наказу Національної служби здоров’я України від 15 травня 2025 року № 377</t>
+  </si>
+  <si>
+    <t>docs/nakaz_620.pdf</t>
   </si>
 </sst>
 </file>
@@ -441,12 +456,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -461,13 +482,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
@@ -1588,13 +1611,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D500C81C-80F5-46C0-959E-2202AF945DAB}">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.6640625" customWidth="1"/>
+    <col min="7" max="7" width="23.44140625" customWidth="1"/>
     <col min="8" max="8" width="85.77734375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2055,7 +2079,7 @@
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="E23" s="2">
         <v>45839</v>
@@ -2082,6 +2106,30 @@
       </c>
       <c r="H24" s="3" t="s">
         <v>127</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="273.60000000000002">
+      <c r="A25" s="4">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C25" s="4">
+        <v>2</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" s="5">
+        <v>45901</v>
+      </c>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -2092,7 +2140,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7557B9E7-A285-4BCD-94D2-7512532AA228}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="11.77734375" bestFit="1" customWidth="1"/>
@@ -2141,6 +2189,26 @@
         <v>128</v>
       </c>
     </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>620</v>
+      </c>
+      <c r="C3" s="2">
+        <v>45883</v>
+      </c>
+      <c r="D3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F3" t="s">
+        <v>133</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/database.xlsx
+++ b/data/database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oleh.koval\Desktop\Правила_9пакет\prodject_rules\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A04C1FC-8565-4F0E-9ACC-4253510101D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C69E55-1E16-471E-B693-E5AE81B8ACD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37800" yWindow="1485" windowWidth="28800" windowHeight="11235" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dicts" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="136">
   <si>
     <t>cod</t>
   </si>
@@ -430,6 +430,12 @@
   </si>
   <si>
     <t>docs/nakaz_620.pdf</t>
+  </si>
+  <si>
+    <t>Про внесення змін до наказу Національної служби здоров’я України від 15 травня 2025 року № 377 Додаток 1</t>
+  </si>
+  <si>
+    <t>docs/nakaz_620_dodatoc_1.pdf</t>
   </si>
 </sst>
 </file>
@@ -482,7 +488,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -490,7 +496,8 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
@@ -2112,20 +2119,20 @@
       <c r="A25" s="4">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C25" s="4">
-        <v>2</v>
-      </c>
-      <c r="D25" s="4" t="s">
+      <c r="C25" s="5">
+        <v>3</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="6">
         <v>45901</v>
       </c>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4" t="s">
+      <c r="F25" s="5"/>
+      <c r="G25" s="5" t="s">
         <v>130</v>
       </c>
       <c r="H25" s="3" t="s">
@@ -2140,13 +2147,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7557B9E7-A285-4BCD-94D2-7512532AA228}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="69.21875" customWidth="1"/>
-    <col min="6" max="6" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="100.88671875" customWidth="1"/>
+    <col min="6" max="6" width="39.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2209,6 +2216,26 @@
         <v>133</v>
       </c>
     </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>620</v>
+      </c>
+      <c r="C4" s="2">
+        <v>45883</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F4" t="s">
+        <v>135</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/database.xlsx
+++ b/data/database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oleh.koval\Desktop\Правила_9пакет\prodject_rules\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C69E55-1E16-471E-B693-E5AE81B8ACD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F9916C6-89C5-49DE-A14D-F4A8056D9501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37800" yWindow="1485" windowWidth="28800" windowHeight="11235" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dicts" sheetId="1" r:id="rId1"/>
@@ -147,9 +147,6 @@
     <t>title</t>
   </si>
   <si>
-    <t>Про встановлення правил щодо визначення послуг за сервісом “Лабораторна діагностика” пакету медичних послуг «Профілактика, діагностика, спостереження та лікування в амбулаторних умовах» у 2025 році</t>
-  </si>
-  <si>
     <t>file_path</t>
   </si>
   <si>
@@ -436,6 +433,9 @@
   </si>
   <si>
     <t>docs/nakaz_620_dodatoc_1.pdf</t>
+  </si>
+  <si>
+    <t>Про встановлення правил щодо визначення послуг за сервісом “Лабораторна діагностика” пакету медичних послуг «Профілактика, діагностика, спостереження та лікування в амбулаторних умовах» у 2025 році Додаток</t>
   </si>
 </sst>
 </file>
@@ -488,7 +488,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -496,8 +496,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
@@ -787,7 +785,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -854,10 +852,10 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="D6" t="s">
         <v>26</v>
@@ -868,10 +866,10 @@
         <v>20</v>
       </c>
       <c r="B7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
@@ -938,10 +936,10 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" t="s">
         <v>57</v>
-      </c>
-      <c r="C12" t="s">
-        <v>58</v>
       </c>
       <c r="D12" t="s">
         <v>26</v>
@@ -952,10 +950,10 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" t="s">
         <v>61</v>
-      </c>
-      <c r="C13" t="s">
-        <v>62</v>
       </c>
       <c r="D13" t="s">
         <v>26</v>
@@ -966,10 +964,10 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
         <v>26</v>
@@ -980,10 +978,10 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s">
         <v>26</v>
@@ -994,10 +992,10 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D16" t="s">
         <v>26</v>
@@ -1008,10 +1006,10 @@
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s">
         <v>25</v>
@@ -1019,13 +1017,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" t="s">
         <v>80</v>
-      </c>
-      <c r="C18" t="s">
-        <v>81</v>
       </c>
       <c r="D18" t="s">
         <v>26</v>
@@ -1033,13 +1031,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" t="s">
         <v>85</v>
-      </c>
-      <c r="C19" t="s">
-        <v>86</v>
       </c>
       <c r="D19" t="s">
         <v>26</v>
@@ -1047,13 +1045,13 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" t="s">
         <v>89</v>
-      </c>
-      <c r="C20" t="s">
-        <v>90</v>
       </c>
       <c r="D20" t="s">
         <v>26</v>
@@ -1061,13 +1059,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B21" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" t="s">
         <v>93</v>
-      </c>
-      <c r="C21" t="s">
-        <v>94</v>
       </c>
       <c r="D21" t="s">
         <v>26</v>
@@ -1075,13 +1073,13 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B22" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" t="s">
         <v>97</v>
-      </c>
-      <c r="C22" t="s">
-        <v>98</v>
       </c>
       <c r="D22" t="s">
         <v>26</v>
@@ -1089,13 +1087,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C23" t="s">
         <v>101</v>
-      </c>
-      <c r="C23" t="s">
-        <v>102</v>
       </c>
       <c r="D23" t="s">
         <v>26</v>
@@ -1103,13 +1101,13 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B24" t="s">
+        <v>104</v>
+      </c>
+      <c r="C24" t="s">
         <v>105</v>
-      </c>
-      <c r="C24" t="s">
-        <v>106</v>
       </c>
       <c r="D24" t="s">
         <v>26</v>
@@ -1117,13 +1115,13 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B25" t="s">
+        <v>108</v>
+      </c>
+      <c r="C25" t="s">
         <v>109</v>
-      </c>
-      <c r="C25" t="s">
-        <v>110</v>
       </c>
       <c r="D25" t="s">
         <v>26</v>
@@ -1131,13 +1129,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B26" t="s">
+        <v>112</v>
+      </c>
+      <c r="C26" t="s">
         <v>113</v>
-      </c>
-      <c r="C26" t="s">
-        <v>114</v>
       </c>
       <c r="D26" t="s">
         <v>26</v>
@@ -1145,13 +1143,13 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D27" t="s">
         <v>26</v>
@@ -1159,13 +1157,13 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B28" t="s">
+        <v>119</v>
+      </c>
+      <c r="C28" t="s">
         <v>120</v>
-      </c>
-      <c r="C28" t="s">
-        <v>121</v>
       </c>
       <c r="D28" t="s">
         <v>26</v>
@@ -1173,13 +1171,13 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B29" t="s">
+        <v>123</v>
+      </c>
+      <c r="C29" t="s">
         <v>124</v>
-      </c>
-      <c r="C29" t="s">
-        <v>125</v>
       </c>
       <c r="D29" t="s">
         <v>26</v>
@@ -1221,7 +1219,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2">
         <v>9</v>
@@ -1238,7 +1236,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B3">
         <v>9</v>
@@ -1250,12 +1248,12 @@
         <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B4">
         <v>9</v>
@@ -1267,12 +1265,12 @@
         <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5">
         <v>9</v>
@@ -1289,7 +1287,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6">
         <v>9</v>
@@ -1306,7 +1304,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B7">
         <v>9</v>
@@ -1323,7 +1321,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8">
         <v>9</v>
@@ -1335,12 +1333,12 @@
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B9">
         <v>9</v>
@@ -1352,12 +1350,12 @@
         <v>6</v>
       </c>
       <c r="E9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -1369,12 +1367,12 @@
         <v>6</v>
       </c>
       <c r="E10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B11">
         <v>9</v>
@@ -1386,12 +1384,12 @@
         <v>6</v>
       </c>
       <c r="E11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B12">
         <v>9</v>
@@ -1403,12 +1401,12 @@
         <v>6</v>
       </c>
       <c r="E12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B13">
         <v>9</v>
@@ -1417,15 +1415,15 @@
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B14">
         <v>9</v>
@@ -1434,15 +1432,15 @@
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B15">
         <v>9</v>
@@ -1451,15 +1449,15 @@
         <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B16">
         <v>9</v>
@@ -1468,15 +1466,15 @@
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B17">
         <v>9</v>
@@ -1485,15 +1483,15 @@
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B18">
         <v>9</v>
@@ -1502,15 +1500,15 @@
         <v>2</v>
       </c>
       <c r="D18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B19">
         <v>9</v>
@@ -1519,15 +1517,15 @@
         <v>2</v>
       </c>
       <c r="D19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B20">
         <v>9</v>
@@ -1536,15 +1534,15 @@
         <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B21">
         <v>9</v>
@@ -1553,15 +1551,15 @@
         <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E21" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B22">
         <v>9</v>
@@ -1570,15 +1568,15 @@
         <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B23">
         <v>9</v>
@@ -1587,15 +1585,15 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B24">
         <v>9</v>
@@ -1604,10 +1602,10 @@
         <v>2</v>
       </c>
       <c r="D24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -1660,19 +1658,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E2" s="2">
         <v>45839</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="44.4" customHeight="1">
@@ -1680,19 +1678,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E3" s="2">
         <v>45658</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="52.2" customHeight="1">
@@ -1700,19 +1698,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E4" s="2">
         <v>45658</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="47.4" customHeight="1">
@@ -1720,19 +1718,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E5" s="2">
         <v>45658</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="86.4">
@@ -1740,19 +1738,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E6" s="2">
         <v>45658</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="169.8" customHeight="1">
@@ -1760,19 +1758,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E7" s="2">
         <v>45658</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="115.2">
@@ -1780,19 +1778,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E8" s="2">
         <v>45839</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="160.80000000000001" customHeight="1">
@@ -1800,19 +1798,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E9" s="2">
         <v>45839</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="43.2">
@@ -1820,19 +1818,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E10" s="2">
         <v>45839</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="28.8">
@@ -1840,19 +1838,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E11" s="2">
         <v>45839</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="34.200000000000003" customHeight="1">
@@ -1860,19 +1858,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E12" s="2">
         <v>45839</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="302.39999999999998">
@@ -1880,19 +1878,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E13" s="2">
         <v>45658</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="86.4">
@@ -1900,19 +1898,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E14" s="2">
         <v>45658</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="28.8">
@@ -1920,19 +1918,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E15" s="2">
         <v>45658</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="57.6">
@@ -1940,19 +1938,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E16" s="2">
         <v>45658</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="28.8">
@@ -1960,19 +1958,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E17" s="2">
         <v>45658</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="76.2" customHeight="1">
@@ -1980,19 +1978,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E18" s="2">
         <v>45658</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="127.8" customHeight="1">
@@ -2000,19 +1998,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E19" s="2">
         <v>45658</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="43.2">
@@ -2020,19 +2018,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E20" s="2">
         <v>45839</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="115.2">
@@ -2040,19 +2038,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E21" s="2">
         <v>45839</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="57.6">
@@ -2060,19 +2058,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E22" s="2">
         <v>45839</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="273.60000000000002">
@@ -2080,19 +2078,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E23" s="2">
         <v>45839</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="43.2">
@@ -2100,43 +2098,42 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E24" s="2">
         <v>45839</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="273.60000000000002">
       <c r="A25" s="4">
         <v>24</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C25" s="5">
+      <c r="B25" t="s">
+        <v>121</v>
+      </c>
+      <c r="C25">
         <v>3</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E25" s="6">
+      <c r="D25" t="s">
+        <v>83</v>
+      </c>
+      <c r="E25" s="2">
         <v>45901</v>
       </c>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5" t="s">
+      <c r="G25" t="s">
+        <v>129</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -2173,7 +2170,7 @@
         <v>38</v>
       </c>
       <c r="F1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2190,10 +2187,10 @@
         <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>135</v>
       </c>
       <c r="F2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2210,10 +2207,10 @@
         <v>37</v>
       </c>
       <c r="E3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F3" t="s">
         <v>132</v>
-      </c>
-      <c r="F3" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2230,10 +2227,10 @@
         <v>37</v>
       </c>
       <c r="E4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F4" t="s">
         <v>134</v>
-      </c>
-      <c r="F4" t="s">
-        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/data/database.xlsx
+++ b/data/database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oleh.koval\Desktop\Правила_9пакет\prodject_rules\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F9916C6-89C5-49DE-A14D-F4A8056D9501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{135EDECE-5431-4743-911A-2E79D49849A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dicts" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="rule_versions" sheetId="3" r:id="rId3"/>
     <sheet name="documents" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">rule_versions!$A$1:$H$50</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -28,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1019" uniqueCount="387">
   <si>
     <t>cod</t>
   </si>
@@ -436,18 +439,834 @@
   </si>
   <si>
     <t>Про встановлення правил щодо визначення послуг за сервісом “Лабораторна діагностика” пакету медичних послуг «Профілактика, діагностика, спостереження та лікування в амбулаторних умовах» у 2025 році Додаток</t>
+  </si>
+  <si>
+    <t>LR.2.13</t>
+  </si>
+  <si>
+    <t>Визначення толерантності до глюкози</t>
+  </si>
+  <si>
+    <t>LR213</t>
+  </si>
+  <si>
+    <t>Визначення толерантності до глюкози Код T34009 Аналіз; толерантність до глюкози: ▪ Оплата здійснюється за виконання щонайменше 2-х досліджень глюкози крові (до вживання розчину глюкози та після вживання розчину глюкози) та наявності двох спостережень у ДЗ з кодом визначення глюкози та її результатами Включає такі дослідження T34005 або T34023 або T34025 або T34026 або T34038 у разі проведення в один день. Код T34038 Аналіз; глюкозотолерантний тест ▪ Оплата здійснюється за виконання щонайменше 3-х досліджень глюкози крові та наявності щонайменше трьох спостережень у ДЗ з кодом визначення глюкози та її результатами ▪ Включає такі дослідження T34005 або T34023 або T34025 або T34026 або T34009 у разі проведення в один день.</t>
+  </si>
+  <si>
+    <t>LR.2.14</t>
+  </si>
+  <si>
+    <t>Кількісне визначення HbA1c (глікованого гемоглобіну)</t>
+  </si>
+  <si>
+    <t>LR214</t>
+  </si>
+  <si>
+    <t>Кількісне визначення HbA1c (глікованого гемоглобіну) (код T34010): ▪ для діагностики діабету у безсимптомних пацієнтів з високим ризиком – оплата здійснюється за дослідження один раз на 12 місяців ▪ для пацієнтів з встановленим діабетом – оплата здійснюється за дослідження не частіше 4 разів за 12 місяців</t>
+  </si>
+  <si>
+    <t>LR.2.15</t>
+  </si>
+  <si>
+    <t>LR.2.16</t>
+  </si>
+  <si>
+    <t>LR.2.17</t>
+  </si>
+  <si>
+    <t>LR.2.18</t>
+  </si>
+  <si>
+    <t>LR.2.19</t>
+  </si>
+  <si>
+    <t>LR.2.20</t>
+  </si>
+  <si>
+    <t>LR.2.21</t>
+  </si>
+  <si>
+    <t>LR.2.22</t>
+  </si>
+  <si>
+    <t>LR.2.23</t>
+  </si>
+  <si>
+    <t>LR.2.24</t>
+  </si>
+  <si>
+    <t>L3</t>
+  </si>
+  <si>
+    <t>Кількісне визначення фруктозаміну</t>
+  </si>
+  <si>
+    <t>Дослідження кислотно-лужного стану крові</t>
+  </si>
+  <si>
+    <t>Кількісне визначення міді</t>
+  </si>
+  <si>
+    <t>Кількісне визначення продуктів розпаду або утворення колагену</t>
+  </si>
+  <si>
+    <t>Визначення карбамазепіну</t>
+  </si>
+  <si>
+    <t>Визначення 25-гідроксивітаміну D</t>
+  </si>
+  <si>
+    <t>Визначення співвідношення альбуміну/креатиніну</t>
+  </si>
+  <si>
+    <t>Дослідження з кодами</t>
+  </si>
+  <si>
+    <t>Дослідження, які не підлягають оплаті</t>
+  </si>
+  <si>
+    <t>Дослідження класу L2 підлягають оплаті</t>
+  </si>
+  <si>
+    <t>LR215</t>
+  </si>
+  <si>
+    <t>LR216</t>
+  </si>
+  <si>
+    <t>LR217</t>
+  </si>
+  <si>
+    <t>LR218</t>
+  </si>
+  <si>
+    <t>LR219</t>
+  </si>
+  <si>
+    <t>LR220</t>
+  </si>
+  <si>
+    <t>LR221</t>
+  </si>
+  <si>
+    <t>LR222</t>
+  </si>
+  <si>
+    <t>LR223</t>
+  </si>
+  <si>
+    <t>LR224</t>
+  </si>
+  <si>
+    <t>Кількісне визначення фруктозаміну (код T34017) у пацієнтів з встановленим діабетом, у т.ч. гестаційним Оплата здійснюється за дослідження не частіше 4 разів за 12 місяців</t>
+  </si>
+  <si>
+    <t>Дослідження кислотно-лужного стану крові (код A34020) зокрема: вуглекислого газу (код 11557-6), кисню (код 11556-8), рН (код 11558-4), бікарбонату (код 1959-6), лактату (код 2524-7) за 24 години При визначенні вартості за проведення вказаних досліджень з одного зразка застосовуються такі додаткові коефіцієнти: ▪ При одночасному виконанні двох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97. ▪ При одночасному виконанні трьох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97; на 3-й показник – коефіцієнт 0,94. ▪ При одночасному виконанні чотирьох показників або більше показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97; на 3-й показник – коефіцієнт 0,94; на 4-й показник – коефіцієнт 0,91. ▪ При одночасному виконанні п’яти показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97; на 3-й показник – коефіцієнт 0,94; на 4-й показник – коефіцієнт 0,91, на 5-й показник – коефіцієнт 0,88. Оплата здійснюється за проведення максимум 5-х показників з переліку</t>
+  </si>
+  <si>
+    <t>Кількісне визначення міді (код 47100-3 або 12556-7), марганцю (код 5681-2), селену (код 5722-4) або цинку (код A34023) у крові При визначенні вартості за проведення вказаних досліджень з одного зразка застосовуються такі додаткові коефіцієнти: ▪ При одночасному виконанні двох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97. Оплата здійснюється за проведення максимум 2-х показників з переліку.</t>
+  </si>
+  <si>
+    <t>Кількісне визначення продуктів розпаду або утворення колагену (код 41171-0 або 47255-5) для моніторингу пацієнтів із: ▪ доведеною низькою мінеральною щільністю кісткової тканини ▪ метаболічним захворюванням кісток ▪ хворобою Педжета</t>
+  </si>
+  <si>
+    <t>Визначення карбамазепіну (код 3433-0), дігоксину (код K34005), етанолу (код A34031), літію (код 14334-7 або 25463-1), ацетамінофену (код 29529-5), фенобарбіталу (код 10338-2), фенітоїну (код N34003), вальпроату (код 4086-5) При визначенні вартості за проведення вказаних досліджень з одного зразка застосовуються такі додаткові коефіцієнти: ▪ При одночасному виконанні двох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97. ▪ При одночасному виконанні трьох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97; на 3-ий показник – коефіцієнт 0,94. ▪ При одночасному виконанні чотирьох показників або більше показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97; на 3-й показник – коефіцієнт 0,94; на 4-й показник – коефіцієнт 0,91. Оплата здійснюється за проведення максимум 4-х показників з переліку</t>
+  </si>
+  <si>
+    <t>Визначення 25-гідроксивітаміну D (код T34031 Аналіз; вітамін D) у пацієнта, який: ▪ має ознаки або симптоми остеопорозу або остеомаляції; або ▪ має підвищену лужну фосфатазу та нормальні показники функції печінки; або ▪ має гіперпаратиреоз, гіпо- або гіперкальціємію або гіпофосфатемію; або ▪ страждає на порушення всмоктування в кишечнику (наприклад, через наявність у пацієнта муковісцидозу, синдрому короткої кишки, запального захворювання кишечника або нелікованої целіакії або стан після баріатричної операції); або ▪ приймає ліки, які знижують рівень 25OH-D (наприклад, протисудомні засоби); або ▪ має хронічну ниркову недостатність або є реципієнтом трансплантованої нирки; або ▪ має вік менше 16 років і має ознаки або симптоми рахіту; або ▪ є немовлям, який має ознаки дефіциту вітаміну D; або ▪ є дитиною, яка знаходиться виключно на грудному вигодовуванні та має принаймні один інший фактор ризику, згаданий у цьому правилі; або ▪ має брата/сестру молодше 16 років і який/яка має дефіцит вітаміну D.</t>
+  </si>
+  <si>
+    <t>Визначення співвідношення альбуміну/креатиніну (код A35008) включає визначення креатиніну в сечі (код U34002 Аналіз; креатинін) при вказані в ДЗ «сеча»</t>
+  </si>
+  <si>
+    <t>Дослідження з кодами: A34038, K34003, B34024, T34031, F34001, X38001, A33041, P34001, T35002, A35003, R38001, N34002, A38001 T38001, K34002 K38001, Y35001, W38001, A34022, H34001, U34001, U34003, U34002, W34001, A34030, X34001, S34001, Y34001 – оплата здійснюється за умови вказання потрібної інформації в текстовому полі ДЗ</t>
+  </si>
+  <si>
+    <t>Дослідження, які не підлягають оплаті: - T34022 Аналіз; гемоглобін А. - D34009 Аналіз; Шиллінга - 14743-9 Глюкоза [Моль/об'єм] у Капілярній крові Визначення глюкометром</t>
+  </si>
+  <si>
+    <t>Дослідження класу L2 підлягають оплаті за умови виконання їх такими спеціалістами та фахівцями (коди посад в ЕСОЗ P71, P74, P17, P75, P243, P173, P146, P148, P272, P72, P274, P276, P242, P277, Р281)</t>
+  </si>
+  <si>
+    <t>Мікробіологія</t>
+  </si>
+  <si>
+    <t>LR.3.1</t>
+  </si>
+  <si>
+    <t>Виявлення патогенних мікроорганізмів у мазках з носа</t>
+  </si>
+  <si>
+    <t>LR31</t>
+  </si>
+  <si>
+    <t>Виявлення патогенних мікроорганізмів у мазках з носа (код 10353-1), горла (код R33006), очей (код 609-8) і вух (код 608-0) (крім мазків, взятих для епідеміологічного нагляду), у тому числі (якщо виконується): За виконання з одного зразка одного або більше досліджень з переліку оплата здійснюється як за одне дослідження</t>
+  </si>
+  <si>
+    <t>LR.3.2</t>
+  </si>
+  <si>
+    <t>LR.3.3</t>
+  </si>
+  <si>
+    <t>LR.3.4</t>
+  </si>
+  <si>
+    <t>LR.3.5</t>
+  </si>
+  <si>
+    <t>LR.3.6</t>
+  </si>
+  <si>
+    <t>LR.3.7</t>
+  </si>
+  <si>
+    <t>LR.3.8</t>
+  </si>
+  <si>
+    <t>LR.3.9</t>
+  </si>
+  <si>
+    <t>Визначення культури грибів</t>
+  </si>
+  <si>
+    <t>Виявлення патогенних мікроорганізмів у мазках з шийки матки</t>
+  </si>
+  <si>
+    <t>Виявлення патогенних мікроорганізмів у трахеальному аспіраті</t>
+  </si>
+  <si>
+    <t>Виявлення патогенних мікроорганізмів у рані</t>
+  </si>
+  <si>
+    <t>Виявлення патогенних мікроорганізмів у тканині</t>
+  </si>
+  <si>
+    <t>Виявлення патогенних мікроорганізмів у калі</t>
+  </si>
+  <si>
+    <t>Виявлення патогенних мікроорганізмів у калі методом мікроскопії</t>
+  </si>
+  <si>
+    <t>Виявлення культури у калі методом організм-специфічної культури</t>
+  </si>
+  <si>
+    <t>LR32</t>
+  </si>
+  <si>
+    <t>LR33</t>
+  </si>
+  <si>
+    <t>LR34</t>
+  </si>
+  <si>
+    <t>LR35</t>
+  </si>
+  <si>
+    <t>LR36</t>
+  </si>
+  <si>
+    <t>LR37</t>
+  </si>
+  <si>
+    <t>LR38</t>
+  </si>
+  <si>
+    <t>LR39</t>
+  </si>
+  <si>
+    <t>Визначення культури грибів (код 27414-2, код 6409-7, код 41026-6, код 601-5, код 87980-9, код 576-9, код S33007, код A33030, код A33008) При визначенні вартості за проведення вказаних досліджень з одного зразка застосовуються такі додаткові коефіцієнти:
+- При одночасному виконанні двох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97.
+- При одночасному виконанні трьох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97; на 3-ий показник – коефіцієнт 0,94. Оплата здійснюється за одночасне проведення максимум 3-х показників з переліку</t>
+  </si>
+  <si>
+    <t>Виявлення патогенних мікроорганізмів у мазках з шийки матки (код X33004) або геніталій (код 10352-3 та код 75269-1) або пеніса (код 14478-2) За одночасне виконання з одного зразка одного або більше досліджень з переліку оплата здійснюється як за одне дослідження</t>
+  </si>
+  <si>
+    <t>Виявлення патогенних мікроорганізмів у трахеальному аспіраті (код 52973-5 ) та у мокротинні (код 624-7). За одночасне виконання з одного зразка одного або двох досліджень з переліку оплата здійснюється як за одне дослідження</t>
+  </si>
+  <si>
+    <t>Виявлення патогенних мікроорганізмів у рані (код 632-0, код 17909-3 або код 633-8) За одночасне виконання з одного зразка одного або більше досліджень з переліку оплата здійснюється як за одне дослідження</t>
+  </si>
+  <si>
+    <t>Виявлення патогенних мікроорганізмів у тканині (код 20474-3, код 628-8) За одночасне виконання з одного зразка одного або більше досліджень з переліку оплата здійснюється як за одне дослідження</t>
+  </si>
+  <si>
+    <t>Виявлення патогенних мікроорганізмів у калі (код 6461-8, код 625-4, код 82301-3) За виконання з одного зразка одного або більше досліджень з переліку оплата здійснюється як за одне дослідження</t>
+  </si>
+  <si>
+    <t>Виявлення патогенних мікроорганізмів у калі методом мікроскопії (код 104404-9 та код 10704-5) За виконання одного або більше досліджень з переліку оплата здійснюється як за одне дослідження за 7 днів</t>
+  </si>
+  <si>
+    <t>Виявлення культури у калі методом організм-специфічної культури (код 6579-7, код 28549-4, код 88586-3, код 43371-4, код 6331-3) При визначенні вартості за проведення вказаних досліджень з одного зразка застосовуються такі додаткові коефіцієнти:
+- При одночасному виконанні двох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97. Оплата здійснюється за проведення максимум 2-х показників з переліку</t>
+  </si>
+  <si>
+    <t>Виявлення мікроорганізмів при мікроскопічному дослідженні (код 66647, код 10357-2, код 32026-7, код 14365-1, код 87969-2, код 14357-8, код 14364-4, код 14362-8, код 648-6; код X33001, код Y33001, код L33002, код W33006, код K33001, код U33002, код S33001). При визначенні вартості за проведення вказаних досліджень застосовуються такі додаткові коефіцієнти:
+"- При одночасному виконанні двох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97.
+- При одночасному виконанні трьох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97; на 3-ий показник – коефіцієнт 0,94. Оплата здійснюється за одночасне проведення максимум 3-х показників з переліку"
+"Дослідження культури у зразку (коди 10353-1, код 43307-8, код 87932-0, код 608-0, код 609-8, код 74816-0, код R33002) При визначенні вартості за проведення вказаних досліджень код застосовуються такі додаткові коефіцієнти:
+- При одночасному виконанні двох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97.
+- При одночасному виконанні трьох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97; на 3-ий показник – коефіцієнт 0,94. 
+Оплата здійснюється за одночасне проведення максимум 3-х показників з переліку"</t>
+  </si>
+  <si>
+    <t>LR310</t>
+  </si>
+  <si>
+    <t>LR.3.10</t>
+  </si>
+  <si>
+    <t>Виявлення мікроорганізмів при мікроскопічному дослідженні</t>
+  </si>
+  <si>
+    <t>LR.3.11</t>
+  </si>
+  <si>
+    <t>LR.3.12</t>
+  </si>
+  <si>
+    <t>LR.3.13</t>
+  </si>
+  <si>
+    <t>Дослідження культури у зразку</t>
+  </si>
+  <si>
+    <t>Дослідження культури крові</t>
+  </si>
+  <si>
+    <t>Визначення антигенів або антитіл гепатиту</t>
+  </si>
+  <si>
+    <t>LR311</t>
+  </si>
+  <si>
+    <t>LR312</t>
+  </si>
+  <si>
+    <t>LR313</t>
+  </si>
+  <si>
+    <t>Дослідження культури у зразку (коди 10353-1, код 43307-8, код 87932-0, код 608-0, код 609-8, код 74816-0, код R33002) При визначенні вартості за проведення вказаних досліджень код застосовуються такі додаткові коефіцієнти:
+- При одночасному виконанні двох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97.
+- При одночасному виконанні трьох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97; на 3-ий показник – коефіцієнт 0,94. Оплата здійснюється за одночасне проведення максимум 3-х показників з переліку</t>
+  </si>
+  <si>
+    <t>Дослідження культури крові
+- коди 17928-3 та 600-7 – за виконання одного або двох досліджень оплата здійснюється як за одне дослідження.
+- коди 17934-1 та 600-7 – за виконання одного або двох досліджень оплата здійснюється як за одне дослідження.</t>
+  </si>
+  <si>
+    <t>Визначення антигенів або антитіл гепатиту (код D33005, код 22314-9, код D33025, код D33011, код 49777-6, код 16937-5, код 35283-1, код 51458-8, код 13248-0, код 22330-5, код 33464-9, D33010, код 51459-6, код 13294-4, код 5193-8, код 10900-9, код 13953-5, код 104785-1, код 13952-7, код 22316-4, код 51914-0, код 31204-1, код 63557-3, код 5196-1, код 318444, код 51824-1, код 22327-1, код D33023, код 13955-0) з метою з’ясування: 1. інфекційних причин гострого або хронічного гепатиту або 2. імунного статусу або вірусоносійства у пацієнтів: після контакту з особою хворою на гепатит А, гепатит В, гепатит С або гепатит D або після вакцинації проти вище вказаних захворювань або з підозрою на гострий або хронічний гепатит; з відповідною клінічною чи лабораторною інформацією, наприклад «гепатомегалія» (код R16), «жовтяниця» (код R17) або «відхилення в дослідженнях, що свідчать про порушення функції печінки» (код R94.5 «Відхилення від норми, виявлені під час дослідження функції печінки») При визначенні вартості за проведення вказаних досліджень з одного зразка застосовуються такі додаткові коефіцієнти:
+- При одночасному виконанні двох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97.
+- При одночасному виконанні трьох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97; на 3-ий показник – коефіцієнт 0,94. Оплата здійснюється за проведення максимум 3-х показників з переліку</t>
+  </si>
+  <si>
+    <t>Визначення РНК вірусу гепатиту С (код 11259-9) у пацієнта, який відповідає щонайменше 1 критерію з наступних: (a) пацієнт є серопозитивним на гепатит С (2 різні аналізи на антитіла до гепатиту С є позитивними); (b) серологічний статус пацієнта невизначений після тестування (результати 2-х аналізів на антитіла до гепатиту С є різними);
+(c) дослідження проводиться з метою:
+- визначення статусу пацієнта щодо гепатиту С з пригніченим або ослабленим імунітетом; або
+- виявлення гострого гепатиту С до сероконверсії, якщо це вважається необхідним для клінічного ведення хворого; Оплата здійснюється за дослідження один раз на 12 місяців</t>
+  </si>
+  <si>
+    <t>LR314</t>
+  </si>
+  <si>
+    <t>LR.3.14</t>
+  </si>
+  <si>
+    <t>Визначення РНК вірусу гепатиту С</t>
+  </si>
+  <si>
+    <t>LR.3.15</t>
+  </si>
+  <si>
+    <t>LR.3.16</t>
+  </si>
+  <si>
+    <t>LR.3.17</t>
+  </si>
+  <si>
+    <t>LR.3.18</t>
+  </si>
+  <si>
+    <t>LR.3.19</t>
+  </si>
+  <si>
+    <t>LR.3.20</t>
+  </si>
+  <si>
+    <t>LR.3.21</t>
+  </si>
+  <si>
+    <t>LR.3.22</t>
+  </si>
+  <si>
+    <t>Кількісне визначення РНК вірусу гепатиту С</t>
+  </si>
+  <si>
+    <t>Визначення генотипу вірусу гепатиту С</t>
+  </si>
+  <si>
+    <t>Кількісне визначення ДНК вірусу гепатиту В</t>
+  </si>
+  <si>
+    <t>Визначення антитіл до краснухи</t>
+  </si>
+  <si>
+    <t>Виявлення ДНК до вірусу Епштейна-Барр</t>
+  </si>
+  <si>
+    <t>Виявлення антитіл до вірусу Епштейна-Барр</t>
+  </si>
+  <si>
+    <t>LR315</t>
+  </si>
+  <si>
+    <t>LR316</t>
+  </si>
+  <si>
+    <t>LR317</t>
+  </si>
+  <si>
+    <t>LR318</t>
+  </si>
+  <si>
+    <t>LR319</t>
+  </si>
+  <si>
+    <t>LR320</t>
+  </si>
+  <si>
+    <t>LR321</t>
+  </si>
+  <si>
+    <t>LR322</t>
+  </si>
+  <si>
+    <t>Визначення РНК вірусу гепатиту С (код 11259-9) у пацієнта, який проходить противірусну терапію хронічного гепатиту ВГС Оплата здійснюється за дослідження не частіше 4 разів за 12 місяців</t>
+  </si>
+  <si>
+    <t>Кількісне визначення РНК вірусу гепатиту С (вірусне навантаження) (код 11011-4 у пацієнта, який відповідає таким умовам: (a) оцінка перед початком противірусної терапії у пацієнта з хронічним гепатитом ВГС; або (b) оцінка ефективності противірусної терапії у такого пацієнта
+- При виконанні досліджень (коди 11011-4 та 11259-9) з одного зразка оплата здійснюється як за одне дослідження
+- Оплата здійснюється за дослідження двічі на 12 місяців</t>
+  </si>
+  <si>
+    <t>Визначення генотипу вірусу гепатиту С (код 32286-7) у пацієнта, який є РНК-позитивним і який оцінюється для призначення противірусної терапії хронічного гепатиту ВГС Оплата здійснюється за дослідження один раз на 12 місяців</t>
+  </si>
+  <si>
+    <t>Кількісне визначення ДНК вірусу гепатиту В (код 29610-3) у пацієнтів з позитивним поверхневим антигеном гепатиту В (код 63557-3 або 5196-1) та хронічним гепатитом В (код за МКХ-10 B18.0 або B18.1), які не отримують противірусну терапію. Оплата здійснюється за дослідження один раз на 12 місяців</t>
+  </si>
+  <si>
+    <t>Кількісне визначення ДНК вірусу гепатиту В (код 29610-3) у пацієнтів з позитивним поверхневим антигеном гепатиту В (код 63557-3 або код 5196-1) і хронічним гепатитом В (код за МКХ-10 B18.0 або B18.1), які отримують противірусну терапію. Оплата здійснюється за дослідження не частіше 4 разів на 12 місяців.</t>
+  </si>
+  <si>
+    <t>Виявлення антитіл до вірусу Епштейна-Барр:
+- виявлення антитіл (код 49178-7 та код 13238-1) – оплата здійснюється як за одне дослідження
+- виявлення антитіл специфічними серологічними методами (код 49178-7, код 13238-1, код 30340-4, код 24114-1) – при визначенні вартості за проведення вказаних досліджень застосовуються такі додаткові коефіцієнти: при одночасному виконанні (з одного зразка) двох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97. Оплата здійснюється за проведення максимум 2-х показників з переліку</t>
+  </si>
+  <si>
+    <t>Виявлення ДНК до вірусу Епштейна-Барр:
+- виявлення ДНК вірусу Epstein Barr (коди 93840-7 та 36923-1оплата здійснюється як за одне дослідження
+- виявлення ДНК вірусу Epstein Barr (коди 5002-1, 5005-4, 238584) – при визначенні вартості за проведення вказаних досліджень застосовуються такі додаткові коефіцієнти:
+- при одночасному виконанні (з одного зразка) двох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97. Оплата здійснюється за проведення максимум 2-х показників з переліку</t>
+  </si>
+  <si>
+    <t>Визначення антитіл до краснухи:
+- IgM до вірусу Rubella (код 31616-6 та код 5335-5) – оплата здійснюється як за одне дослідження
+- IgG до вірусу Rubella (код 25514-1, код 8014-3) – оплата здійснюється як за одне дослідження</t>
+  </si>
+  <si>
+    <t>LR.3.23</t>
+  </si>
+  <si>
+    <t>LR.3.24</t>
+  </si>
+  <si>
+    <t>LR.3.25</t>
+  </si>
+  <si>
+    <t>LR.3.26</t>
+  </si>
+  <si>
+    <t>LR.3.27</t>
+  </si>
+  <si>
+    <t>LR.3.28</t>
+  </si>
+  <si>
+    <t>LR.3.29</t>
+  </si>
+  <si>
+    <t>LR.3.30</t>
+  </si>
+  <si>
+    <t>Проведення тесту клітинно-опосередкованої імунної відповіді в крові для виявлення латентного туберкульозу</t>
+  </si>
+  <si>
+    <t>Визначення антитіл до Helicobacter pylori</t>
+  </si>
+  <si>
+    <t>Визначення антитіл до мікоплазми</t>
+  </si>
+  <si>
+    <t>Визначення антитіл до Treponema pallidum</t>
+  </si>
+  <si>
+    <t>Визначення антитіл до токсоплазми</t>
+  </si>
+  <si>
+    <t>Визначення антитіл до Trichinella spiralis</t>
+  </si>
+  <si>
+    <t>Визначення антитіл до Toxocara cani</t>
+  </si>
+  <si>
+    <t>Визначення антитіл до Echinococcus granulosus</t>
+  </si>
+  <si>
+    <t>LR323</t>
+  </si>
+  <si>
+    <t>LR324</t>
+  </si>
+  <si>
+    <t>LR325</t>
+  </si>
+  <si>
+    <t>LR326</t>
+  </si>
+  <si>
+    <t>LR327</t>
+  </si>
+  <si>
+    <t>LR328</t>
+  </si>
+  <si>
+    <t>LR329</t>
+  </si>
+  <si>
+    <t>LR330</t>
+  </si>
+  <si>
+    <t>Проведення тесту клітинно-опосередкованої імунної відповіді в крові для виявлення латентного туберкульозу за допомогою аналізу вивільнення гамма-інтерферону (IGRA) (код R32005) у таких осіб: (a) які контактували з особою з підтвердженим випадком активного туберкульозу (код Z20.1 Контакт з хворим або можливість зараження туберкульозом) (b) які, інфіковані вірусом імунодефіциту людини (Z21 Безсимптомне носійство вірусу імунодефіциту людини [ВІЛ]); (c) які мають розпочати або вже розпочали терапію інгібіторами фактору некрозу пухлини (TNF); (d) які мають розпочати або вже розпочали діаліз (Z49.0 Підготовчі процедури для проведення діалізу Z49.1 Екстракорпоральний діаліз; Z49.2 Інший вид діалізу) (e) з силікозом (код J62.8 Пневмоконіоз, спричинений іншим пилом, що містить кремній. Силікоз БДВ); (f) які є або плануються бути імунодепресованими через хворобу або медичне лікування, не згадане в пунктах (a) (e)</t>
+  </si>
+  <si>
+    <t>Визначення антитіл до хламідії:
+- IgM до Chlamydophila pneumoniae (коди 24004-4, 51807-6) – за виконання одного або двох досліджень оплата здійснюється як за одне дослідження
+- IgG до Toxoplasma gondii (коди 44981-9, 51806-8) – за виконання одного або двох досліджень оплата здійснюється як за одне дослідження
+- IgM до Chlamydia trachomatis B (коди 45001-5, 44994-2) – за виконання одного або двох досліджень оплата здійснюється як за одне дослідження
+- IgG до Chlamydia trachomatis B (коди 44995-9, 26715-3) – за виконання одного або двох досліджень оплата здійснюється як за одне дослідження</t>
+  </si>
+  <si>
+    <t>LR331</t>
+  </si>
+  <si>
+    <t>LR.3.31</t>
+  </si>
+  <si>
+    <t>Визначення антитіл до хламідії</t>
+  </si>
+  <si>
+    <t>LR.3.32</t>
+  </si>
+  <si>
+    <t>LR.3.33</t>
+  </si>
+  <si>
+    <t>LR.3.34</t>
+  </si>
+  <si>
+    <t>Виявлення РНК до вірусів</t>
+  </si>
+  <si>
+    <t>Виявлення антитіл до Parvovirus B19</t>
+  </si>
+  <si>
+    <t>Виявлення ДНК до Parvovirus B19</t>
+  </si>
+  <si>
+    <t>LR332</t>
+  </si>
+  <si>
+    <t>LR333</t>
+  </si>
+  <si>
+    <t>LR334</t>
+  </si>
+  <si>
+    <t>Виявлення РНК до вірусів (коди 86692-1 РНК ротавірусу, 40987-0 РНК Respiratory syncytial virus 105887-4 ДНК Adenovirus) При визначенні вартості за проведення вказаних досліджень застосовуються такі додаткові коефіцієнти: при одночасному виконанні двох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97. Оплата здійснюється за проведення максимум 2-х показників з переліку</t>
+  </si>
+  <si>
+    <t>Виявлення антитіл до Parvovirus B19:
+- виявлення антитіл IgМ до Parvovirus B19 (код 7981-4 та код 17422-7) – за виконання одного або двох досліджень оплата здійснюється як за одне дослідження
+- виявлення антитіл IgG до Parvovirus B19 (код 29675-6 та код 17422-7) – за виконання одного або двох досліджень оплата здійснюється як за одне дослідження</t>
+  </si>
+  <si>
+    <t>Виявлення ДНК до Parvovirus B19:
+- виявлення ДНК вірусу Parvovirus B19 (код 74420-1 та код 503482) – за виконання одного або двох досліджень оплата здійснюється як за одне дослідження
+- виявлення ДНК вірусу Parvovirus B19 (код 50344-1 та код 50346-6, 50348-2) – при визначенні вартості за проведення вказаних досліджень застосовуються такі додаткові коефіцієнти: – при одночасному виконанні двох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97. – оплата здійснюється за проведення максимум 2-х показників з переліку</t>
+  </si>
+  <si>
+    <t>LR336</t>
+  </si>
+  <si>
+    <t>LR.3.36</t>
+  </si>
+  <si>
+    <t>Виявлення вірусу Varicella zoster</t>
+  </si>
+  <si>
+    <t>Виявлення вірусу Varicella zoster (код 21597-0, код 15410-4, код 8049-9, код 29248-2, код 87961-9, код 106029-2) При визначенні вартості за проведення вказаних досліджень застосовуються такі додаткові коефіцієнти:
+- При одночасному виконанні двох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97.
+- При одночасному виконанні трьох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97; на 3-ий показник – коефіцієнт 0,94. Оплата здійснюється за проведення максимум 3-х показників з переліку</t>
+  </si>
+  <si>
+    <t>Виявлення вірусу простого герпесу (код 25435-9, код 19106-4, код 472290, код 44508-0, код 5850-3, код 5854-5, код 31853-5, код 31852-7) При визначенні вартості за проведення вказаних досліджень застосовуються такі додаткові коефіцієнти:
+- При одночасному виконанні двох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97.
+- При одночасному виконанні трьох показників з переліку – на 1й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97; на 3-ий показник – коефіцієнт 0,94. Оплата здійснюється за проведення максимум 3-х показників з переліку</t>
+  </si>
+  <si>
+    <t>LR337</t>
+  </si>
+  <si>
+    <t>LR.3.37</t>
+  </si>
+  <si>
+    <t>Виявлення вірусу простого герпесу</t>
+  </si>
+  <si>
+    <t>LR.3.38</t>
+  </si>
+  <si>
+    <t>Виявлення антитіл до цитомегаловірус</t>
+  </si>
+  <si>
+    <t>LR338</t>
+  </si>
+  <si>
+    <t>Виявлення антитіл до цитомегаловірус:
+- виявлення антитіл IgM (коди 30325-5, 7853-5) – за виконання одного або двох досліджень оплата здійснюється як за одне дослідження
+- виявлення антитіл Ig G (коди 22244-8, 7852-7) – за виконання одного або двох досліджень оплата здійснюється як за одне дослідження
+- виявлення ДНК (коди 4999-9, 30246-3, 83065-3, 5000-5) – при визначенні вартості за проведення вказаних досліджень застосовуються такі додаткові коефіцієнти: – при одночасному виконанні двох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97; – оплата здійснюється за проведення максимум 2-х показників з переліку.</t>
+  </si>
+  <si>
+    <t>LR.3.39</t>
+  </si>
+  <si>
+    <t>LR.3.40</t>
+  </si>
+  <si>
+    <t>LR.3.41</t>
+  </si>
+  <si>
+    <t>LR.3.42</t>
+  </si>
+  <si>
+    <t>LR.3.43</t>
+  </si>
+  <si>
+    <t>Виявлення антитіл до Borrelia burgdorferi</t>
+  </si>
+  <si>
+    <t>Дослідження спрямовані на виявлення ковіду</t>
+  </si>
+  <si>
+    <t>Проведення швидких тестів</t>
+  </si>
+  <si>
+    <t>Дослідження з кодами D33005, D33011, D33010, A33036, D33013, A33053, A33044, A33010, A33060, A33059, A34039, A33057, R33007, A33017, A33040</t>
+  </si>
+  <si>
+    <t>Дослідження класу L3 (крім кодів D33022, A33036, D33013, C19001, C19003, 94558-4)</t>
+  </si>
+  <si>
+    <t>LR339</t>
+  </si>
+  <si>
+    <t>LR340</t>
+  </si>
+  <si>
+    <t>LR341</t>
+  </si>
+  <si>
+    <t>LR342</t>
+  </si>
+  <si>
+    <t>LR343</t>
+  </si>
+  <si>
+    <t>Виявлення антитіл до Borrelia burgdorferi (код 22135-8 та код 7818-8) – за виконання одного або двох досліджень оплата здійснюється як за одне дослідження</t>
+  </si>
+  <si>
+    <t>Дослідження спрямовані на виявлення ковіду:
+- за виконання одного або декількох досліджень (коди 94819-0 та C19003 або 94500-6 або 94309-2) за виконання одного або більше досліджень оплата здійснюється як за одне дослідження
+- за виконання одного або декількох досліджень (коди C19003 COVID та 94500-6 або 94309-2) – за виконання одного або більше досліджень оплата здійснюється як за одне дослідження
+- за виконання одного або декількох досліджень (коди C19001 та 94558-4) – за виконання одного або більше досліджень оплата здійснюється як за одне дослідження
+- за виконання одного або декількох досліджень (коди 94762-2 та 94562-6 або 94563-4 або 94564-2) – за виконання одного або більше досліджень оплата здійснюється як за одне дослідження</t>
+  </si>
+  <si>
+    <t>Проведення швидких тестів (коди D33022, A33036, D33013) – оплата здійснюється як за одне дослідження</t>
+  </si>
+  <si>
+    <t>Дослідження з кодами D33005, D33011, D33010, A33036, D33013, A33053, A33044, A33010, A33060, A33059, A34039, A33057, R33007, A33017, A33040 – оплата здійснюється за умови вказання потрібної інформації в текстовому полі ДЗ</t>
+  </si>
+  <si>
+    <t>Дослідження класу L3 (крім кодів D33022, A33036, D33013, C19001, C19003, 94558-4) підлягають оплаті за умови виконання їх такими спеціалістами та фахівцями (коди посад P71, P17, P241, P39, P271, P40, P81, P273, P278, P146, P74, P173, P276, P242)</t>
+  </si>
+  <si>
+    <t>L4</t>
+  </si>
+  <si>
+    <t>Імунологія</t>
+  </si>
+  <si>
+    <t>LR410</t>
+  </si>
+  <si>
+    <t>LR41</t>
+  </si>
+  <si>
+    <t>Визначення загального імуноглобуліну А (код F33002), загального імуноглобуліну G (код H33002), загального імуноглобуліну M (код D33004), загального імуноглобуліну D (код D32001) (будь -яким методом) у сироватці, сечі або іншій рідині організму
+При визначенні вартості за проведення вказаних досліджень застосовуються такі додаткові коефіцієнти:
+- при одночасному виконанні двох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97.
+- при одночасному виконанні трьох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97; на 3-ий показник – коефіцієнт 0,94.
+Оплата здійснюється за проведення максимум 3-х показників з переліку</t>
+  </si>
+  <si>
+    <t>LR.4.1</t>
+  </si>
+  <si>
+    <t>Визначення загального імуноглобуліну А</t>
+  </si>
+  <si>
+    <t>LR.4.2</t>
+  </si>
+  <si>
+    <t>LR.4.3</t>
+  </si>
+  <si>
+    <t>LR.4.4</t>
+  </si>
+  <si>
+    <t>LR.4.5</t>
+  </si>
+  <si>
+    <t>LR.4.6</t>
+  </si>
+  <si>
+    <t>LR.4.7</t>
+  </si>
+  <si>
+    <t>LR.4.8</t>
+  </si>
+  <si>
+    <t>LR.4.9</t>
+  </si>
+  <si>
+    <t>LR.4.10</t>
+  </si>
+  <si>
+    <t>Визначення загального імуноглобуліну Е</t>
+  </si>
+  <si>
+    <t>Кількісне визначення імуноглобуліну Е</t>
+  </si>
+  <si>
+    <t>Виявлення специфічних імуноглобулінів IgE</t>
+  </si>
+  <si>
+    <t>Кількісне визначення еозинофільного катіонного білка в сироватці або плазмі</t>
+  </si>
+  <si>
+    <t>Виявлення одного з наступних антитіл (один або більше класів або ізотипів) при оцінці або діагностиці целіакії або інших синдромів гіперчутливості до глютену</t>
+  </si>
+  <si>
+    <t>Проведення діагностичних алергологічних тестів</t>
+  </si>
+  <si>
+    <t>Визначення NK-клітини</t>
+  </si>
+  <si>
+    <t>Визначення Т-супресорних/цитотоксичних клітин</t>
+  </si>
+  <si>
+    <t>Визначення В1-клітин (аутореактивних)</t>
+  </si>
+  <si>
+    <t>LR42</t>
+  </si>
+  <si>
+    <t>LR43</t>
+  </si>
+  <si>
+    <t>LR44</t>
+  </si>
+  <si>
+    <t>LR45</t>
+  </si>
+  <si>
+    <t>LR46</t>
+  </si>
+  <si>
+    <t>LR47</t>
+  </si>
+  <si>
+    <t>LR48</t>
+  </si>
+  <si>
+    <t>LR49</t>
+  </si>
+  <si>
+    <t>Визначення загального імуноглобуліну Е (код B33011) Оплата здійснюється за дослідження не частіше 2 разів за 12 місяців.</t>
+  </si>
+  <si>
+    <t>Кількісне визначення імуноглобуліну Е (загального) (код B33011) під час спостереження за пацієнтом із підтвердженою мієломою, що секретує імуноглобулін Е, доведеним вродженим імунодефіцитом або підтвердженим алергічним бронхолегеневим аспергільозом Оплата здійснюється за дослідження не частіше 6 разів за 12 місяців.</t>
+  </si>
+  <si>
+    <t>Виявлення специфічних імуноглобулінів IgE до одного або кількох потенційних алергенів (код A34016) Оплата здійснюється за дослідження не частіше 4 разів за 12 місяців.</t>
+  </si>
+  <si>
+    <t>Кількісне визначення еозинофільного катіонного білка в сироватці або плазмі, або обох (код R33004 Аналіз; імунологія; респіраторна). Оплата здійснюється за дослідження не частіше 3разів за 12 місяців рік, для моніторингу відповіді на терапію астми, що лікується кортикостероїдами, у дитини віком до 12 років.</t>
+  </si>
+  <si>
+    <t>Виявлення одного з наступних антитіл (один або більше класів або ізотипів) при оцінці або діагностиці целіакії або інших синдромів гіперчутливості до глютену: (коди D33014 Аналіз; ендомізіальні антитіла, D33015 Аналіз; антитіла до гліадину, D33031 Аналіз; антитіла до тканинної трансглутамінази, D34010 Аналіз; трансглутамаза). При визначенні вартості за проведення вказаних досліджень застосовуються такі додаткові коефіцієнти:
+- при одночасному виконанні двох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97. Оплата здійснюється за проведення дослідження дітям максимум 2-х показників з переліку</t>
+  </si>
+  <si>
+    <t>Проведення діагностичних алергологічних тестів (коди A33052 Аналіз; трансдермальний пластир кодується та код 12000-00 Шкірно-алергічна проба з використанням ≤ 20 алергенів (за НК_26) або 12003-00 Шкірноалергічна проба з використанням ≥ 21 алергену Оплата здійснюється як за одне дослідження</t>
+  </si>
+  <si>
+    <t>Визначення NK-клітини (код 21166-4 Клітини CD56/100 клітин у Зразку, код 20599-7 Клітини CD3/100 клітин у Зразку, код 26560-3 Клітини CD16/100 клітин у Зразку). При визначенні вартості за проведення вказаних досліджень застосовуються такі додаткові коефіцієнти:
+- при одночасному виконанні двох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97.</t>
+  </si>
+  <si>
+    <t>Визначення Т-супресорних/цитотоксичних клітин і деяких природних клітин-кілерів
+- проведення з одного зразка двох досліджень (код 13337-1 Клітини CD8+HLA-DR+/100 клітин у Крові та код 80222-3 Клітини CD8/100 лімфоцитів у Зразку) – вважається одним дослідженням</t>
+  </si>
+  <si>
+    <t>Визначення В1-клітин (аутореактивних):
+- проведення з одного зразка двох або більше досліджень (код 8131-5 Клітини CD5+CD19+/100 клітин у Крові або код 20611-0 Клітини CD5/100 клітин у Зразку або код 8117-4 Клітини CD19/100 клітин у Крові) – за виконання одного або більше досліджень оплата здійснюється як за одне дослідження
+- проведення з одного зразка двох досліджень (код 20593-0 Клітини CD19/100 клітин у Зразку або код 8117-4 Клітини CD19/100 клітин у Крові) – вважається одним дослідженням.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -488,14 +1307,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
@@ -776,7 +1598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D95"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
@@ -1183,15 +2005,939 @@
         <v>26</v>
       </c>
     </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" t="s">
+        <v>136</v>
+      </c>
+      <c r="C30" t="s">
+        <v>137</v>
+      </c>
+      <c r="D30" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" t="s">
+        <v>140</v>
+      </c>
+      <c r="C31" t="s">
+        <v>141</v>
+      </c>
+      <c r="D31" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" t="s">
+        <v>144</v>
+      </c>
+      <c r="C32" t="s">
+        <v>155</v>
+      </c>
+      <c r="D32" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" t="s">
+        <v>145</v>
+      </c>
+      <c r="C33" t="s">
+        <v>156</v>
+      </c>
+      <c r="D33" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
+        <v>73</v>
+      </c>
+      <c r="B34" t="s">
+        <v>146</v>
+      </c>
+      <c r="C34" t="s">
+        <v>157</v>
+      </c>
+      <c r="D34" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>73</v>
+      </c>
+      <c r="B35" t="s">
+        <v>147</v>
+      </c>
+      <c r="C35" t="s">
+        <v>158</v>
+      </c>
+      <c r="D35" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" t="s">
+        <v>148</v>
+      </c>
+      <c r="C36" t="s">
+        <v>159</v>
+      </c>
+      <c r="D36" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" t="s">
+        <v>149</v>
+      </c>
+      <c r="C37" t="s">
+        <v>160</v>
+      </c>
+      <c r="D37" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" t="s">
+        <v>150</v>
+      </c>
+      <c r="C38" t="s">
+        <v>161</v>
+      </c>
+      <c r="D38" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>73</v>
+      </c>
+      <c r="B39" t="s">
+        <v>151</v>
+      </c>
+      <c r="C39" t="s">
+        <v>162</v>
+      </c>
+      <c r="D39" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" t="s">
+        <v>73</v>
+      </c>
+      <c r="B40" t="s">
+        <v>152</v>
+      </c>
+      <c r="C40" t="s">
+        <v>163</v>
+      </c>
+      <c r="D40" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" t="s">
+        <v>73</v>
+      </c>
+      <c r="B41" t="s">
+        <v>153</v>
+      </c>
+      <c r="C41" t="s">
+        <v>164</v>
+      </c>
+      <c r="D41" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
+        <v>2</v>
+      </c>
+      <c r="B42" t="s">
+        <v>154</v>
+      </c>
+      <c r="C42" t="s">
+        <v>185</v>
+      </c>
+      <c r="D42" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>154</v>
+      </c>
+      <c r="B43" t="s">
+        <v>186</v>
+      </c>
+      <c r="C43" t="s">
+        <v>187</v>
+      </c>
+      <c r="D43" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
+        <v>154</v>
+      </c>
+      <c r="B44" t="s">
+        <v>190</v>
+      </c>
+      <c r="C44" t="s">
+        <v>198</v>
+      </c>
+      <c r="D44" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
+        <v>154</v>
+      </c>
+      <c r="B45" t="s">
+        <v>191</v>
+      </c>
+      <c r="C45" t="s">
+        <v>199</v>
+      </c>
+      <c r="D45" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
+        <v>154</v>
+      </c>
+      <c r="B46" t="s">
+        <v>192</v>
+      </c>
+      <c r="C46" t="s">
+        <v>200</v>
+      </c>
+      <c r="D46" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>154</v>
+      </c>
+      <c r="B47" t="s">
+        <v>193</v>
+      </c>
+      <c r="C47" t="s">
+        <v>201</v>
+      </c>
+      <c r="D47" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" t="s">
+        <v>154</v>
+      </c>
+      <c r="B48" t="s">
+        <v>194</v>
+      </c>
+      <c r="C48" t="s">
+        <v>202</v>
+      </c>
+      <c r="D48" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" t="s">
+        <v>154</v>
+      </c>
+      <c r="B49" t="s">
+        <v>195</v>
+      </c>
+      <c r="C49" t="s">
+        <v>203</v>
+      </c>
+      <c r="D49" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" t="s">
+        <v>154</v>
+      </c>
+      <c r="B50" t="s">
+        <v>196</v>
+      </c>
+      <c r="C50" t="s">
+        <v>204</v>
+      </c>
+      <c r="D50" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" t="s">
+        <v>154</v>
+      </c>
+      <c r="B51" t="s">
+        <v>197</v>
+      </c>
+      <c r="C51" t="s">
+        <v>205</v>
+      </c>
+      <c r="D51" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" t="s">
+        <v>154</v>
+      </c>
+      <c r="B52" t="s">
+        <v>224</v>
+      </c>
+      <c r="C52" t="s">
+        <v>225</v>
+      </c>
+      <c r="D52" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" t="s">
+        <v>154</v>
+      </c>
+      <c r="B53" t="s">
+        <v>226</v>
+      </c>
+      <c r="C53" t="s">
+        <v>229</v>
+      </c>
+      <c r="D53" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" t="s">
+        <v>154</v>
+      </c>
+      <c r="B54" t="s">
+        <v>227</v>
+      </c>
+      <c r="C54" t="s">
+        <v>230</v>
+      </c>
+      <c r="D54" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" t="s">
+        <v>154</v>
+      </c>
+      <c r="B55" t="s">
+        <v>228</v>
+      </c>
+      <c r="C55" t="s">
+        <v>231</v>
+      </c>
+      <c r="D55" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" t="s">
+        <v>154</v>
+      </c>
+      <c r="B56" t="s">
+        <v>240</v>
+      </c>
+      <c r="C56" t="s">
+        <v>241</v>
+      </c>
+      <c r="D56" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" t="s">
+        <v>154</v>
+      </c>
+      <c r="B57" t="s">
+        <v>242</v>
+      </c>
+      <c r="C57" t="s">
+        <v>241</v>
+      </c>
+      <c r="D57" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" t="s">
+        <v>154</v>
+      </c>
+      <c r="B58" t="s">
+        <v>243</v>
+      </c>
+      <c r="C58" t="s">
+        <v>250</v>
+      </c>
+      <c r="D58" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" t="s">
+        <v>154</v>
+      </c>
+      <c r="B59" t="s">
+        <v>244</v>
+      </c>
+      <c r="C59" t="s">
+        <v>251</v>
+      </c>
+      <c r="D59" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" t="s">
+        <v>154</v>
+      </c>
+      <c r="B60" t="s">
+        <v>245</v>
+      </c>
+      <c r="C60" t="s">
+        <v>252</v>
+      </c>
+      <c r="D60" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" t="s">
+        <v>154</v>
+      </c>
+      <c r="B61" t="s">
+        <v>246</v>
+      </c>
+      <c r="C61" t="s">
+        <v>252</v>
+      </c>
+      <c r="D61" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" t="s">
+        <v>154</v>
+      </c>
+      <c r="B62" t="s">
+        <v>247</v>
+      </c>
+      <c r="C62" t="s">
+        <v>255</v>
+      </c>
+      <c r="D62" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" t="s">
+        <v>154</v>
+      </c>
+      <c r="B63" t="s">
+        <v>248</v>
+      </c>
+      <c r="C63" t="s">
+        <v>254</v>
+      </c>
+      <c r="D63" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" t="s">
+        <v>154</v>
+      </c>
+      <c r="B64" t="s">
+        <v>249</v>
+      </c>
+      <c r="C64" t="s">
+        <v>253</v>
+      </c>
+      <c r="D64" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" t="s">
+        <v>154</v>
+      </c>
+      <c r="B65" t="s">
+        <v>272</v>
+      </c>
+      <c r="C65" t="s">
+        <v>280</v>
+      </c>
+      <c r="D65" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" t="s">
+        <v>154</v>
+      </c>
+      <c r="B66" t="s">
+        <v>273</v>
+      </c>
+      <c r="C66" t="s">
+        <v>281</v>
+      </c>
+      <c r="D66" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" t="s">
+        <v>154</v>
+      </c>
+      <c r="B67" t="s">
+        <v>274</v>
+      </c>
+      <c r="C67" t="s">
+        <v>282</v>
+      </c>
+      <c r="D67" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" t="s">
+        <v>154</v>
+      </c>
+      <c r="B68" t="s">
+        <v>275</v>
+      </c>
+      <c r="C68" t="s">
+        <v>283</v>
+      </c>
+      <c r="D68" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" t="s">
+        <v>154</v>
+      </c>
+      <c r="B69" t="s">
+        <v>276</v>
+      </c>
+      <c r="C69" t="s">
+        <v>284</v>
+      </c>
+      <c r="D69" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" t="s">
+        <v>154</v>
+      </c>
+      <c r="B70" t="s">
+        <v>277</v>
+      </c>
+      <c r="C70" t="s">
+        <v>285</v>
+      </c>
+      <c r="D70" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" t="s">
+        <v>154</v>
+      </c>
+      <c r="B71" t="s">
+        <v>278</v>
+      </c>
+      <c r="C71" t="s">
+        <v>286</v>
+      </c>
+      <c r="D71" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" t="s">
+        <v>154</v>
+      </c>
+      <c r="B72" t="s">
+        <v>279</v>
+      </c>
+      <c r="C72" t="s">
+        <v>287</v>
+      </c>
+      <c r="D72" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" t="s">
+        <v>154</v>
+      </c>
+      <c r="B73" t="s">
+        <v>299</v>
+      </c>
+      <c r="C73" t="s">
+        <v>300</v>
+      </c>
+      <c r="D73" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" t="s">
+        <v>154</v>
+      </c>
+      <c r="B74" t="s">
+        <v>301</v>
+      </c>
+      <c r="C74" t="s">
+        <v>304</v>
+      </c>
+      <c r="D74" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" t="s">
+        <v>154</v>
+      </c>
+      <c r="B75" t="s">
+        <v>302</v>
+      </c>
+      <c r="C75" t="s">
+        <v>305</v>
+      </c>
+      <c r="D75" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" t="s">
+        <v>154</v>
+      </c>
+      <c r="B76" t="s">
+        <v>303</v>
+      </c>
+      <c r="C76" t="s">
+        <v>306</v>
+      </c>
+      <c r="D76" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" t="s">
+        <v>154</v>
+      </c>
+      <c r="B77" t="s">
+        <v>314</v>
+      </c>
+      <c r="C77" t="s">
+        <v>315</v>
+      </c>
+      <c r="D77" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" t="s">
+        <v>154</v>
+      </c>
+      <c r="B78" t="s">
+        <v>319</v>
+      </c>
+      <c r="C78" t="s">
+        <v>320</v>
+      </c>
+      <c r="D78" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" t="s">
+        <v>154</v>
+      </c>
+      <c r="B79" t="s">
+        <v>321</v>
+      </c>
+      <c r="C79" t="s">
+        <v>322</v>
+      </c>
+      <c r="D79" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" t="s">
+        <v>154</v>
+      </c>
+      <c r="B80" t="s">
+        <v>325</v>
+      </c>
+      <c r="C80" t="s">
+        <v>330</v>
+      </c>
+      <c r="D80" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" t="s">
+        <v>154</v>
+      </c>
+      <c r="B81" t="s">
+        <v>326</v>
+      </c>
+      <c r="C81" t="s">
+        <v>331</v>
+      </c>
+      <c r="D81" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" t="s">
+        <v>154</v>
+      </c>
+      <c r="B82" t="s">
+        <v>327</v>
+      </c>
+      <c r="C82" t="s">
+        <v>332</v>
+      </c>
+      <c r="D82" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" t="s">
+        <v>154</v>
+      </c>
+      <c r="B83" t="s">
+        <v>328</v>
+      </c>
+      <c r="C83" t="s">
+        <v>333</v>
+      </c>
+      <c r="D83" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" t="s">
+        <v>154</v>
+      </c>
+      <c r="B84" t="s">
+        <v>329</v>
+      </c>
+      <c r="C84" t="s">
+        <v>334</v>
+      </c>
+      <c r="D84" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" t="s">
+        <v>2</v>
+      </c>
+      <c r="B85" t="s">
+        <v>345</v>
+      </c>
+      <c r="C85" t="s">
+        <v>346</v>
+      </c>
+      <c r="D85" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" t="s">
+        <v>345</v>
+      </c>
+      <c r="B86" t="s">
+        <v>350</v>
+      </c>
+      <c r="C86" t="s">
+        <v>351</v>
+      </c>
+      <c r="D86" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" t="s">
+        <v>345</v>
+      </c>
+      <c r="B87" t="s">
+        <v>352</v>
+      </c>
+      <c r="C87" t="s">
+        <v>361</v>
+      </c>
+      <c r="D87" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" t="s">
+        <v>345</v>
+      </c>
+      <c r="B88" t="s">
+        <v>353</v>
+      </c>
+      <c r="C88" t="s">
+        <v>362</v>
+      </c>
+      <c r="D88" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" t="s">
+        <v>345</v>
+      </c>
+      <c r="B89" t="s">
+        <v>354</v>
+      </c>
+      <c r="C89" t="s">
+        <v>363</v>
+      </c>
+      <c r="D89" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" t="s">
+        <v>345</v>
+      </c>
+      <c r="B90" t="s">
+        <v>355</v>
+      </c>
+      <c r="C90" t="s">
+        <v>364</v>
+      </c>
+      <c r="D90" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" t="s">
+        <v>345</v>
+      </c>
+      <c r="B91" t="s">
+        <v>356</v>
+      </c>
+      <c r="C91" t="s">
+        <v>365</v>
+      </c>
+      <c r="D91" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" t="s">
+        <v>345</v>
+      </c>
+      <c r="B92" t="s">
+        <v>357</v>
+      </c>
+      <c r="C92" t="s">
+        <v>366</v>
+      </c>
+      <c r="D92" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" t="s">
+        <v>345</v>
+      </c>
+      <c r="B93" t="s">
+        <v>358</v>
+      </c>
+      <c r="C93" t="s">
+        <v>367</v>
+      </c>
+      <c r="D93" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" t="s">
+        <v>345</v>
+      </c>
+      <c r="B94" t="s">
+        <v>359</v>
+      </c>
+      <c r="C94" t="s">
+        <v>368</v>
+      </c>
+      <c r="D94" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" t="s">
+        <v>345</v>
+      </c>
+      <c r="B95" t="s">
+        <v>360</v>
+      </c>
+      <c r="C95" t="s">
+        <v>369</v>
+      </c>
+      <c r="D95" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D456371C-55CC-41A7-AFCE-65668AB9659F}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E88"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="18.21875" customWidth="1"/>
@@ -1608,22 +3354,1110 @@
         <v>123</v>
       </c>
     </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>138</v>
+      </c>
+      <c r="B25">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" t="s">
+        <v>73</v>
+      </c>
+      <c r="E25" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>142</v>
+      </c>
+      <c r="B26">
+        <v>9</v>
+      </c>
+      <c r="C26" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" t="s">
+        <v>73</v>
+      </c>
+      <c r="E26" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>165</v>
+      </c>
+      <c r="B27">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" t="s">
+        <v>73</v>
+      </c>
+      <c r="E27" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>166</v>
+      </c>
+      <c r="B28">
+        <v>9</v>
+      </c>
+      <c r="C28" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" t="s">
+        <v>73</v>
+      </c>
+      <c r="E28" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>167</v>
+      </c>
+      <c r="B29">
+        <v>9</v>
+      </c>
+      <c r="C29" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" t="s">
+        <v>73</v>
+      </c>
+      <c r="E29" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>168</v>
+      </c>
+      <c r="B30">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" t="s">
+        <v>73</v>
+      </c>
+      <c r="E30" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>169</v>
+      </c>
+      <c r="B31">
+        <v>9</v>
+      </c>
+      <c r="C31" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" t="s">
+        <v>73</v>
+      </c>
+      <c r="E31" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>170</v>
+      </c>
+      <c r="B32">
+        <v>9</v>
+      </c>
+      <c r="C32" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" t="s">
+        <v>73</v>
+      </c>
+      <c r="E32" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>171</v>
+      </c>
+      <c r="B33">
+        <v>9</v>
+      </c>
+      <c r="C33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D33" t="s">
+        <v>73</v>
+      </c>
+      <c r="E33" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>172</v>
+      </c>
+      <c r="B34">
+        <v>9</v>
+      </c>
+      <c r="C34" t="s">
+        <v>2</v>
+      </c>
+      <c r="D34" t="s">
+        <v>73</v>
+      </c>
+      <c r="E34" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>173</v>
+      </c>
+      <c r="B35">
+        <v>9</v>
+      </c>
+      <c r="C35" t="s">
+        <v>2</v>
+      </c>
+      <c r="D35" t="s">
+        <v>73</v>
+      </c>
+      <c r="E35" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>174</v>
+      </c>
+      <c r="B36">
+        <v>9</v>
+      </c>
+      <c r="C36" t="s">
+        <v>2</v>
+      </c>
+      <c r="D36" t="s">
+        <v>73</v>
+      </c>
+      <c r="E36" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>188</v>
+      </c>
+      <c r="B37">
+        <v>9</v>
+      </c>
+      <c r="C37" t="s">
+        <v>2</v>
+      </c>
+      <c r="D37" t="s">
+        <v>154</v>
+      </c>
+      <c r="E37" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>206</v>
+      </c>
+      <c r="B38">
+        <v>9</v>
+      </c>
+      <c r="C38" t="s">
+        <v>2</v>
+      </c>
+      <c r="D38" t="s">
+        <v>154</v>
+      </c>
+      <c r="E38" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>207</v>
+      </c>
+      <c r="B39">
+        <v>9</v>
+      </c>
+      <c r="C39" t="s">
+        <v>2</v>
+      </c>
+      <c r="D39" t="s">
+        <v>154</v>
+      </c>
+      <c r="E39" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>208</v>
+      </c>
+      <c r="B40">
+        <v>9</v>
+      </c>
+      <c r="C40" t="s">
+        <v>2</v>
+      </c>
+      <c r="D40" t="s">
+        <v>154</v>
+      </c>
+      <c r="E40" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>209</v>
+      </c>
+      <c r="B41">
+        <v>9</v>
+      </c>
+      <c r="C41" t="s">
+        <v>2</v>
+      </c>
+      <c r="D41" t="s">
+        <v>154</v>
+      </c>
+      <c r="E41" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>210</v>
+      </c>
+      <c r="B42">
+        <v>9</v>
+      </c>
+      <c r="C42" t="s">
+        <v>2</v>
+      </c>
+      <c r="D42" t="s">
+        <v>154</v>
+      </c>
+      <c r="E42" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>211</v>
+      </c>
+      <c r="B43">
+        <v>9</v>
+      </c>
+      <c r="C43" t="s">
+        <v>2</v>
+      </c>
+      <c r="D43" t="s">
+        <v>154</v>
+      </c>
+      <c r="E43" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>212</v>
+      </c>
+      <c r="B44">
+        <v>9</v>
+      </c>
+      <c r="C44" t="s">
+        <v>2</v>
+      </c>
+      <c r="D44" t="s">
+        <v>154</v>
+      </c>
+      <c r="E44" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>213</v>
+      </c>
+      <c r="B45">
+        <v>9</v>
+      </c>
+      <c r="C45" t="s">
+        <v>2</v>
+      </c>
+      <c r="D45" t="s">
+        <v>154</v>
+      </c>
+      <c r="E45" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>223</v>
+      </c>
+      <c r="B46">
+        <v>9</v>
+      </c>
+      <c r="C46" t="s">
+        <v>2</v>
+      </c>
+      <c r="D46" t="s">
+        <v>154</v>
+      </c>
+      <c r="E46" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>232</v>
+      </c>
+      <c r="B47">
+        <v>9</v>
+      </c>
+      <c r="C47" t="s">
+        <v>2</v>
+      </c>
+      <c r="D47" t="s">
+        <v>154</v>
+      </c>
+      <c r="E47" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
+        <v>233</v>
+      </c>
+      <c r="B48">
+        <v>9</v>
+      </c>
+      <c r="C48" t="s">
+        <v>2</v>
+      </c>
+      <c r="D48" t="s">
+        <v>154</v>
+      </c>
+      <c r="E48" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>234</v>
+      </c>
+      <c r="B49">
+        <v>9</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2</v>
+      </c>
+      <c r="D49" t="s">
+        <v>154</v>
+      </c>
+      <c r="E49" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>239</v>
+      </c>
+      <c r="B50">
+        <v>9</v>
+      </c>
+      <c r="C50" t="s">
+        <v>2</v>
+      </c>
+      <c r="D50" t="s">
+        <v>154</v>
+      </c>
+      <c r="E50" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>256</v>
+      </c>
+      <c r="B51">
+        <v>9</v>
+      </c>
+      <c r="C51" t="s">
+        <v>2</v>
+      </c>
+      <c r="D51" t="s">
+        <v>154</v>
+      </c>
+      <c r="E51" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>257</v>
+      </c>
+      <c r="B52">
+        <v>9</v>
+      </c>
+      <c r="C52" t="s">
+        <v>2</v>
+      </c>
+      <c r="D52" t="s">
+        <v>154</v>
+      </c>
+      <c r="E52" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>258</v>
+      </c>
+      <c r="B53">
+        <v>9</v>
+      </c>
+      <c r="C53" t="s">
+        <v>2</v>
+      </c>
+      <c r="D53" t="s">
+        <v>154</v>
+      </c>
+      <c r="E53" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>259</v>
+      </c>
+      <c r="B54">
+        <v>9</v>
+      </c>
+      <c r="C54" t="s">
+        <v>2</v>
+      </c>
+      <c r="D54" t="s">
+        <v>154</v>
+      </c>
+      <c r="E54" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>260</v>
+      </c>
+      <c r="B55">
+        <v>9</v>
+      </c>
+      <c r="C55" t="s">
+        <v>2</v>
+      </c>
+      <c r="D55" t="s">
+        <v>154</v>
+      </c>
+      <c r="E55" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>261</v>
+      </c>
+      <c r="B56">
+        <v>9</v>
+      </c>
+      <c r="C56" t="s">
+        <v>2</v>
+      </c>
+      <c r="D56" t="s">
+        <v>154</v>
+      </c>
+      <c r="E56" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>262</v>
+      </c>
+      <c r="B57">
+        <v>9</v>
+      </c>
+      <c r="C57" t="s">
+        <v>2</v>
+      </c>
+      <c r="D57" t="s">
+        <v>154</v>
+      </c>
+      <c r="E57" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>263</v>
+      </c>
+      <c r="B58">
+        <v>9</v>
+      </c>
+      <c r="C58" t="s">
+        <v>2</v>
+      </c>
+      <c r="D58" t="s">
+        <v>154</v>
+      </c>
+      <c r="E58" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>288</v>
+      </c>
+      <c r="B59">
+        <v>9</v>
+      </c>
+      <c r="C59" t="s">
+        <v>2</v>
+      </c>
+      <c r="D59" t="s">
+        <v>154</v>
+      </c>
+      <c r="E59" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>289</v>
+      </c>
+      <c r="B60">
+        <v>9</v>
+      </c>
+      <c r="C60" t="s">
+        <v>2</v>
+      </c>
+      <c r="D60" t="s">
+        <v>154</v>
+      </c>
+      <c r="E60" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>290</v>
+      </c>
+      <c r="B61">
+        <v>9</v>
+      </c>
+      <c r="C61" t="s">
+        <v>2</v>
+      </c>
+      <c r="D61" t="s">
+        <v>154</v>
+      </c>
+      <c r="E61" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>291</v>
+      </c>
+      <c r="B62">
+        <v>9</v>
+      </c>
+      <c r="C62" t="s">
+        <v>2</v>
+      </c>
+      <c r="D62" t="s">
+        <v>154</v>
+      </c>
+      <c r="E62" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
+        <v>292</v>
+      </c>
+      <c r="B63">
+        <v>9</v>
+      </c>
+      <c r="C63" t="s">
+        <v>2</v>
+      </c>
+      <c r="D63" t="s">
+        <v>154</v>
+      </c>
+      <c r="E63" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
+        <v>293</v>
+      </c>
+      <c r="B64">
+        <v>9</v>
+      </c>
+      <c r="C64" t="s">
+        <v>2</v>
+      </c>
+      <c r="D64" t="s">
+        <v>154</v>
+      </c>
+      <c r="E64" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
+        <v>294</v>
+      </c>
+      <c r="B65">
+        <v>9</v>
+      </c>
+      <c r="C65" t="s">
+        <v>2</v>
+      </c>
+      <c r="D65" t="s">
+        <v>154</v>
+      </c>
+      <c r="E65" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
+        <v>295</v>
+      </c>
+      <c r="B66">
+        <v>9</v>
+      </c>
+      <c r="C66" t="s">
+        <v>2</v>
+      </c>
+      <c r="D66" t="s">
+        <v>154</v>
+      </c>
+      <c r="E66" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
+        <v>298</v>
+      </c>
+      <c r="B67">
+        <v>9</v>
+      </c>
+      <c r="C67" t="s">
+        <v>2</v>
+      </c>
+      <c r="D67" t="s">
+        <v>154</v>
+      </c>
+      <c r="E67" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>307</v>
+      </c>
+      <c r="B68">
+        <v>9</v>
+      </c>
+      <c r="C68" t="s">
+        <v>2</v>
+      </c>
+      <c r="D68" t="s">
+        <v>154</v>
+      </c>
+      <c r="E68" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" t="s">
+        <v>308</v>
+      </c>
+      <c r="B69">
+        <v>9</v>
+      </c>
+      <c r="C69" t="s">
+        <v>2</v>
+      </c>
+      <c r="D69" t="s">
+        <v>154</v>
+      </c>
+      <c r="E69" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>309</v>
+      </c>
+      <c r="B70">
+        <v>9</v>
+      </c>
+      <c r="C70" t="s">
+        <v>2</v>
+      </c>
+      <c r="D70" t="s">
+        <v>154</v>
+      </c>
+      <c r="E70" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" t="s">
+        <v>313</v>
+      </c>
+      <c r="B71">
+        <v>9</v>
+      </c>
+      <c r="C71" t="s">
+        <v>2</v>
+      </c>
+      <c r="D71" t="s">
+        <v>154</v>
+      </c>
+      <c r="E71" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" t="s">
+        <v>318</v>
+      </c>
+      <c r="B72">
+        <v>9</v>
+      </c>
+      <c r="C72" t="s">
+        <v>2</v>
+      </c>
+      <c r="D72" t="s">
+        <v>154</v>
+      </c>
+      <c r="E72" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
+        <v>323</v>
+      </c>
+      <c r="B73">
+        <v>9</v>
+      </c>
+      <c r="C73" t="s">
+        <v>2</v>
+      </c>
+      <c r="D73" t="s">
+        <v>154</v>
+      </c>
+      <c r="E73" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" t="s">
+        <v>335</v>
+      </c>
+      <c r="B74">
+        <v>9</v>
+      </c>
+      <c r="C74" t="s">
+        <v>2</v>
+      </c>
+      <c r="D74" t="s">
+        <v>154</v>
+      </c>
+      <c r="E74" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
+        <v>336</v>
+      </c>
+      <c r="B75">
+        <v>9</v>
+      </c>
+      <c r="C75" t="s">
+        <v>2</v>
+      </c>
+      <c r="D75" t="s">
+        <v>154</v>
+      </c>
+      <c r="E75" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
+        <v>337</v>
+      </c>
+      <c r="B76">
+        <v>9</v>
+      </c>
+      <c r="C76" t="s">
+        <v>2</v>
+      </c>
+      <c r="D76" t="s">
+        <v>154</v>
+      </c>
+      <c r="E76" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" t="s">
+        <v>338</v>
+      </c>
+      <c r="B77">
+        <v>9</v>
+      </c>
+      <c r="C77" t="s">
+        <v>2</v>
+      </c>
+      <c r="D77" t="s">
+        <v>154</v>
+      </c>
+      <c r="E77" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" t="s">
+        <v>339</v>
+      </c>
+      <c r="B78">
+        <v>9</v>
+      </c>
+      <c r="C78" t="s">
+        <v>2</v>
+      </c>
+      <c r="D78" t="s">
+        <v>154</v>
+      </c>
+      <c r="E78" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" t="s">
+        <v>348</v>
+      </c>
+      <c r="B79">
+        <v>9</v>
+      </c>
+      <c r="C79" t="s">
+        <v>2</v>
+      </c>
+      <c r="D79" t="s">
+        <v>345</v>
+      </c>
+      <c r="E79" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" t="s">
+        <v>370</v>
+      </c>
+      <c r="B80">
+        <v>9</v>
+      </c>
+      <c r="C80" t="s">
+        <v>2</v>
+      </c>
+      <c r="D80" t="s">
+        <v>345</v>
+      </c>
+      <c r="E80" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" t="s">
+        <v>371</v>
+      </c>
+      <c r="B81">
+        <v>9</v>
+      </c>
+      <c r="C81" t="s">
+        <v>2</v>
+      </c>
+      <c r="D81" t="s">
+        <v>345</v>
+      </c>
+      <c r="E81" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" t="s">
+        <v>372</v>
+      </c>
+      <c r="B82">
+        <v>9</v>
+      </c>
+      <c r="C82" t="s">
+        <v>2</v>
+      </c>
+      <c r="D82" t="s">
+        <v>345</v>
+      </c>
+      <c r="E82" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" t="s">
+        <v>373</v>
+      </c>
+      <c r="B83">
+        <v>9</v>
+      </c>
+      <c r="C83" t="s">
+        <v>2</v>
+      </c>
+      <c r="D83" t="s">
+        <v>345</v>
+      </c>
+      <c r="E83" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" t="s">
+        <v>374</v>
+      </c>
+      <c r="B84">
+        <v>9</v>
+      </c>
+      <c r="C84" t="s">
+        <v>2</v>
+      </c>
+      <c r="D84" t="s">
+        <v>345</v>
+      </c>
+      <c r="E84" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" t="s">
+        <v>375</v>
+      </c>
+      <c r="B85">
+        <v>9</v>
+      </c>
+      <c r="C85" t="s">
+        <v>2</v>
+      </c>
+      <c r="D85" t="s">
+        <v>345</v>
+      </c>
+      <c r="E85" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" t="s">
+        <v>376</v>
+      </c>
+      <c r="B86">
+        <v>9</v>
+      </c>
+      <c r="C86" t="s">
+        <v>2</v>
+      </c>
+      <c r="D86" t="s">
+        <v>345</v>
+      </c>
+      <c r="E86" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" t="s">
+        <v>377</v>
+      </c>
+      <c r="B87">
+        <v>9</v>
+      </c>
+      <c r="C87" t="s">
+        <v>2</v>
+      </c>
+      <c r="D87" t="s">
+        <v>345</v>
+      </c>
+      <c r="E87" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" t="s">
+        <v>347</v>
+      </c>
+      <c r="B88">
+        <v>9</v>
+      </c>
+      <c r="C88" t="s">
+        <v>2</v>
+      </c>
+      <c r="D88" t="s">
+        <v>345</v>
+      </c>
+      <c r="E88" t="s">
+        <v>360</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D500C81C-80F5-46C0-959E-2202AF945DAB}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.5546875" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.44140625" customWidth="1"/>
+    <col min="6" max="6" width="9.21875" customWidth="1"/>
+    <col min="7" max="7" width="10.88671875" customWidth="1"/>
     <col min="8" max="8" width="85.77734375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2136,8 +4970,1289 @@
         <v>130</v>
       </c>
     </row>
+    <row r="26" spans="1:8" ht="129.6">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>138</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
+        <v>83</v>
+      </c>
+      <c r="E26" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="57.6">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>142</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="28.8">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>165</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28" t="s">
+        <v>83</v>
+      </c>
+      <c r="E28" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="201.6">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>166</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29" t="s">
+        <v>83</v>
+      </c>
+      <c r="E29" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="72">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>167</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30" t="s">
+        <v>83</v>
+      </c>
+      <c r="E30" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="43.2">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>168</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31" t="s">
+        <v>83</v>
+      </c>
+      <c r="E31" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="158.4">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>169</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32" t="s">
+        <v>83</v>
+      </c>
+      <c r="E32" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="172.8">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>170</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33" t="s">
+        <v>83</v>
+      </c>
+      <c r="E33" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="28.8">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>171</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34" t="s">
+        <v>83</v>
+      </c>
+      <c r="E34" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="57.6">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>172</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35" t="s">
+        <v>83</v>
+      </c>
+      <c r="E35" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="28.8">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>173</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36" t="s">
+        <v>83</v>
+      </c>
+      <c r="E36" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="43.2">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>174</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37" t="s">
+        <v>83</v>
+      </c>
+      <c r="E37" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="57.6">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>188</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38" t="s">
+        <v>83</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="115.2">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>206</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39" t="s">
+        <v>83</v>
+      </c>
+      <c r="E39" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="43.2">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>207</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40" t="s">
+        <v>83</v>
+      </c>
+      <c r="E40" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="43.2">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>208</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41" t="s">
+        <v>83</v>
+      </c>
+      <c r="E41" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="43.2">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>209</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42" t="s">
+        <v>83</v>
+      </c>
+      <c r="E42" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="43.2">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>210</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43" t="s">
+        <v>83</v>
+      </c>
+      <c r="E43" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="43.2">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>211</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44" t="s">
+        <v>83</v>
+      </c>
+      <c r="E44" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="43.2">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>212</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45" t="s">
+        <v>83</v>
+      </c>
+      <c r="E45" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="86.4">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>213</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46" t="s">
+        <v>83</v>
+      </c>
+      <c r="E46" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="244.8">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>223</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47" t="s">
+        <v>83</v>
+      </c>
+      <c r="E47" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="115.2">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>232</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48" t="s">
+        <v>83</v>
+      </c>
+      <c r="E48" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="72">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>233</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49" t="s">
+        <v>83</v>
+      </c>
+      <c r="E49" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="259.2">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>234</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50" t="s">
+        <v>83</v>
+      </c>
+      <c r="E50" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="115.2">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>239</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51" t="s">
+        <v>83</v>
+      </c>
+      <c r="E51" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="43.2">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>256</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52" t="s">
+        <v>83</v>
+      </c>
+      <c r="E52" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="86.4">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>257</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53" t="s">
+        <v>83</v>
+      </c>
+      <c r="E53" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="43.2">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>258</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54" t="s">
+        <v>83</v>
+      </c>
+      <c r="E54" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="57.6">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>259</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55" t="s">
+        <v>83</v>
+      </c>
+      <c r="E55" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="57.6">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>260</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56" t="s">
+        <v>83</v>
+      </c>
+      <c r="E56" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="100.8">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>261</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57" t="s">
+        <v>83</v>
+      </c>
+      <c r="E57" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="115.2">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>262</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="D58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E58" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="57.6">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>263</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59" t="s">
+        <v>83</v>
+      </c>
+      <c r="E59" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="158.4">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>288</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+      <c r="D60" t="s">
+        <v>83</v>
+      </c>
+      <c r="E60" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="158.4">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>289</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="D61" t="s">
+        <v>83</v>
+      </c>
+      <c r="E61" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="158.4">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>290</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62" t="s">
+        <v>83</v>
+      </c>
+      <c r="E62" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="158.4">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>291</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+      <c r="D63" t="s">
+        <v>83</v>
+      </c>
+      <c r="E63" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="158.4">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>292</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+      <c r="D64" t="s">
+        <v>83</v>
+      </c>
+      <c r="E64" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="158.4">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>293</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+      <c r="D65" t="s">
+        <v>83</v>
+      </c>
+      <c r="E65" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="158.4">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>294</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+      <c r="D66" t="s">
+        <v>83</v>
+      </c>
+      <c r="E66" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="158.4">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>295</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
+      <c r="D67" t="s">
+        <v>83</v>
+      </c>
+      <c r="E67" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="129.6">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>298</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
+      <c r="D68" t="s">
+        <v>83</v>
+      </c>
+      <c r="E68" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="72">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>307</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+      <c r="D69" t="s">
+        <v>83</v>
+      </c>
+      <c r="E69" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="72">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>308</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+      <c r="D70" t="s">
+        <v>83</v>
+      </c>
+      <c r="E70" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="115.2">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>309</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+      <c r="D71" t="s">
+        <v>83</v>
+      </c>
+      <c r="E71" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="115.2">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>313</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72" t="s">
+        <v>83</v>
+      </c>
+      <c r="E72" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="115.2">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>318</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+      <c r="D73" t="s">
+        <v>83</v>
+      </c>
+      <c r="E73" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="126.6" customHeight="1">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>323</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+      <c r="D74" t="s">
+        <v>83</v>
+      </c>
+      <c r="E74" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H74" s="5" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="28.8">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>335</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+      <c r="D75" t="s">
+        <v>83</v>
+      </c>
+      <c r="E75" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="158.4">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>336</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+      <c r="D76" t="s">
+        <v>83</v>
+      </c>
+      <c r="E76" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="28.8">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>337</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="D77" t="s">
+        <v>83</v>
+      </c>
+      <c r="E77" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="43.2">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>338</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+      <c r="D78" t="s">
+        <v>83</v>
+      </c>
+      <c r="E78" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="43.2">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>339</v>
+      </c>
+      <c r="C79">
+        <v>1</v>
+      </c>
+      <c r="D79" t="s">
+        <v>83</v>
+      </c>
+      <c r="E79" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="144">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>348</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
+      </c>
+      <c r="D80" t="s">
+        <v>83</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="28.8">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>370</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+      <c r="D81" t="s">
+        <v>83</v>
+      </c>
+      <c r="E81" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="57.6">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>371</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+      <c r="D82" t="s">
+        <v>83</v>
+      </c>
+      <c r="E82" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="28.8">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>372</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+      <c r="D83" t="s">
+        <v>83</v>
+      </c>
+      <c r="E83" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="57.6">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>373</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
+      <c r="D84" t="s">
+        <v>83</v>
+      </c>
+      <c r="E84" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="115.2">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>374</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
+      <c r="D85" t="s">
+        <v>83</v>
+      </c>
+      <c r="E85" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="57.6">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>375</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
+      <c r="D86" t="s">
+        <v>83</v>
+      </c>
+      <c r="E86" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="72">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>376</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
+      </c>
+      <c r="D87" t="s">
+        <v>83</v>
+      </c>
+      <c r="E87" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="43.2">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>377</v>
+      </c>
+      <c r="C88">
+        <v>1</v>
+      </c>
+      <c r="D88" t="s">
+        <v>83</v>
+      </c>
+      <c r="E88" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="100.8">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>347</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
+      <c r="D89" t="s">
+        <v>83</v>
+      </c>
+      <c r="E89" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>386</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <autoFilter ref="A1:H50" xr:uid="{D500C81C-80F5-46C0-959E-2202AF945DAB}"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/database.xlsx
+++ b/data/database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oleh.koval\Desktop\Правила_9пакет\prodject_rules\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{135EDECE-5431-4743-911A-2E79D49849A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4009D905-2E41-48C6-9DF3-E814ACA2DDE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dicts" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1019" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1420" uniqueCount="525">
   <si>
     <t>cod</t>
   </si>
@@ -1247,6 +1247,444 @@
     <t>Визначення В1-клітин (аутореактивних):
 - проведення з одного зразка двох або більше досліджень (код 8131-5 Клітини CD5+CD19+/100 клітин у Крові або код 20611-0 Клітини CD5/100 клітин у Зразку або код 8117-4 Клітини CD19/100 клітин у Крові) – за виконання одного або більше досліджень оплата здійснюється як за одне дослідження
 - проведення з одного зразка двох досліджень (код 20593-0 Клітини CD19/100 клітин у Зразку або код 8117-4 Клітини CD19/100 клітин у Крові) – вважається одним дослідженням.</t>
+  </si>
+  <si>
+    <t>LR.4.11</t>
+  </si>
+  <si>
+    <t>LR.4.12</t>
+  </si>
+  <si>
+    <t>LR.4.13</t>
+  </si>
+  <si>
+    <t>LR.4.14</t>
+  </si>
+  <si>
+    <t>LR.4.15</t>
+  </si>
+  <si>
+    <t>LR.4.16</t>
+  </si>
+  <si>
+    <t>LR.4.17</t>
+  </si>
+  <si>
+    <t>LR.4.18</t>
+  </si>
+  <si>
+    <t>LR.4.19</t>
+  </si>
+  <si>
+    <t>LR.4.20</t>
+  </si>
+  <si>
+    <t>LR.4.21</t>
+  </si>
+  <si>
+    <t>LR.4.22</t>
+  </si>
+  <si>
+    <t>LR.4.23</t>
+  </si>
+  <si>
+    <t>LR.4.24</t>
+  </si>
+  <si>
+    <t>LR.4.25</t>
+  </si>
+  <si>
+    <t>LR.4.26</t>
+  </si>
+  <si>
+    <t>LR411</t>
+  </si>
+  <si>
+    <t>LR412</t>
+  </si>
+  <si>
+    <t>LR413</t>
+  </si>
+  <si>
+    <t>LR414</t>
+  </si>
+  <si>
+    <t>LR415</t>
+  </si>
+  <si>
+    <t>LR416</t>
+  </si>
+  <si>
+    <t>LR417</t>
+  </si>
+  <si>
+    <t>LR418</t>
+  </si>
+  <si>
+    <t>LR419</t>
+  </si>
+  <si>
+    <t>LR420</t>
+  </si>
+  <si>
+    <t>LR421</t>
+  </si>
+  <si>
+    <t>LR422</t>
+  </si>
+  <si>
+    <t>LR423</t>
+  </si>
+  <si>
+    <t>LR424</t>
+  </si>
+  <si>
+    <t>LR425</t>
+  </si>
+  <si>
+    <t>LR426</t>
+  </si>
+  <si>
+    <t>Визначення лімфоцитів</t>
+  </si>
+  <si>
+    <t>Визначення (регуляторних Т) клітини</t>
+  </si>
+  <si>
+    <t>Визначення маркерів порушень Т-клітинної ланки імунітету</t>
+  </si>
+  <si>
+    <t>Визначення хелперів Т4 до клітини-супресори Т8</t>
+  </si>
+  <si>
+    <t>Визначення супресорів Т8</t>
+  </si>
+  <si>
+    <t>Дослідження з кодами: A33025, A33048, A33055, S32001, S33002, D33004, D32001, F33002, H33002, R32004, B33011, A34016 R33004, A34041 A32001, K33002, B33005</t>
+  </si>
+  <si>
+    <t>Дослідження класу L4 підлягають оплаті за умови</t>
+  </si>
+  <si>
+    <t>Визначення лімфоцитів
+- проведення з одного зразка двох або більше досліджень (код 8103-4 Клітини CD45+CD14+/100 клітин у Крові або код 20589-8
+Клітини CD14/100 клітин у Зразку або 17157-9 Клітини CD45RA/100 клітин у Крові) – вважається одним дослідженням.</t>
+  </si>
+  <si>
+    <t>Визначення (регуляторних Т) клітини
+- проведення з одного зразка двох досліджень (код 80700-8 CD25+CD127(регуляторні Т) клітини/100 CD3+CD4+ клітин у Крові та 32495-4 Клітини CD25/100 клітин у Зразку – вважається одним дослідженням.</t>
+  </si>
+  <si>
+    <t>Визначення маркерів порушень Т-клітинної ланки імунітету
+- проведення з одного зразка двох досліджень (код 8103-4 Клітини CD45+CD14+/100 клітин у Крові та 20589-8 Клітини CD14/100 клітин у Зразку) – вважається одним дослідженням.</t>
+  </si>
+  <si>
+    <t>Визначення маркерів порушень Т-клітинної ланки імунітету
+- проведення з одного зразка двох та більше досліджень (13332-2 Клітини CD4+CD25+/100 клітин у Крові та 32495-4 Клітини CD25/100 клітин у Зразку або 80223-1 Клітини CD4/100 лімфоцитів у Зразку) – вважається одним дослідженням</t>
+  </si>
+  <si>
+    <t>Визначення маркерів порушень Т-клітинної ланки імунітету:
+- проведення з одного зразка двох та більше досліджень (код 13333-0 Клітини CD3+CD25+/100 клітин у Крові та 20599-7 Клітини CD3/100 клітин у Зразку або 90304-7 Клітини CD3/100 лімфоцитів у Крові або 32495-4 Клітини CD25/100 клітин у Зразку – вважається одним дослідженням</t>
+  </si>
+  <si>
+    <t>Визначення хелперів Т4 до клітини-супресори Т8:
+- проведення з одного зразка двох та більше досліджень (код 20607-8 Клітини CD3+CD4+ (хелпери Т4)/клітини CD3+CD8+ (клітини-супресори Т8) та код 90304-7 Клітини CD3/100 лімфоцитів у Крові або 80223-1 Клітини CD4/100 лімфоцитів у Зразку або 80222-3 Клітини CD8/100 лімфоцитів у Зразку або 8101-8 Клітини CD3+CD8+ (супресор Т8)/100 клітин у Крові) – вважається одним дослідженням</t>
+  </si>
+  <si>
+    <t>Визначення маркерів порушень Т-клітинної ланки імунітету:
+- проведення з одного зразка двох та більше досліджень (код 34932-4 Клітини CD3+CD4+CD45RO-CD45RA+/100 клітин у Крові та 90304-7 Клітини CD3/100 лімфоцитів у Крові або 80223-1 Клітини CD4/100 лімфоцитів у Зразку або 17157-9 Клітини CD45RA/100 клітин у Крові) – вважається одним дослідженням</t>
+  </si>
+  <si>
+    <t>Визначення маркерів порушень Т-клітинної ланки імунітету:
+- проведення з одного зразка двох та більше досліджень (код 34929-0 Клітини CD3+CD4+CD45RO+CD45RA-/100 клітин у Крові та 90304-7 Клітини CD3/100 лімфоцитів у Крові або 80223-1 Клітини CD4/100 лімфоцитів у Зразку або 17157-9 Клітини CD45RA/100 клітин у Крові) – вважається одним дослідженням.</t>
+  </si>
+  <si>
+    <t>Визначення супресорів Т8:
+- проведення з одного зразка двох та більше досліджень (код 81018 Клітини CD3+CD8+ (супресор Т8)/100 клітин у Крові та код 90304-7 Клітини CD3/100 лімфоцитів у Крові або код 80222-3 Клітини CD8/100 лімфоцитів у Зразку або код 20607-8 Клітини CD3+CD4+ (хелпери Т4)/клітини CD3+CD8+ (клітини-супресори Т8) [# співвідношення] у Зразку) – вважається одним дослідженням</t>
+  </si>
+  <si>
+    <t>Визначення маркерів порушень Т-клітинної ланки імунітету:
+- проведення з одного зразка двох досліджень (код 18408-5 Клітини CD3+HLA-DR+/100 клітин у Крові та код 90304-7 Клітини CD3/100 лімфоцитів у Крові) – вважається одним дослідженням</t>
+  </si>
+  <si>
+    <t>Визначення маркерів порушень Т-клітинної ланки імунітету:
+- проведення з одного зразка двох досліджень (код 34962-1 Клітини CD3+TCR альфа бета+ /100 клітин у Крові та 90304-7 Клітини CD3/100 лімфоцитів у Крові) – вважається одним дослідженням</t>
+  </si>
+  <si>
+    <t>Визначення маркерів порушень Т-клітинної ланки імунітету
+- проведення з одного зразка двох досліджень (код 34962-1 Клітини CD3+TCR альфа бета+ /100 клітин у Крові та 90304-7 Клітини CD3/100 лімфоцитів у Крові) – вважається одним дослідженням</t>
+  </si>
+  <si>
+    <t>Визначення маркерів порушень Т-клітинної ланки імунітету (коди 13337-1, 8131-5, 8103-4, 13343-9, 13332-2, 42189-1, 13333-0, 20607-8, 34932-4, 34929-0, 8101-8, 18408-5, 34962-1, 38236-6) При визначенні вартості за проведення вказаних досліджень застосовуються такі додаткові коефіцієнти:
+- При одночасному виконанні двох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97.
+- При одночасному виконанні трьох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97; на 3-ий показник – коефіцієнт 0,94. Оплата здійснюється за проведення максимум 3-х показників з переліку</t>
+  </si>
+  <si>
+    <t>Визначення маркерів порушень Т-клітинної ланки імунітету (коди 20587-2, 77944-7, 32758-5, 21154-0, 20588-0, 20589-8, 20590-6, 49841-0, 26563-7, 20594-8, 20595-5, 20596-3, 32750-2, 20597-1, 17129-8, 20602-9, 20603-7, 20608-6,20609-4, 57402-0, 77946-2, 17157-9, 32744-5, 32601-7, 21167-2, 32747-8, 20612-8, 42933-2, 17196-7, 51403-4, 77947-0, 17210-6, 17214-8, 32856-7, 32742-9, 51045-3, 33033-2, 93353-1) При визначенні вартості за проведення вказаних досліджень застосовуються такі додаткові коефіцієнти:
+- При одночасному виконанні двох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97.
+- При одночасному виконанні трьох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97; на 3-ий показник – коефіцієнт 0,94.
+- При одночасному виконанні чотирьох показників або більше показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97; на 3-й показник – коефіцієнт 0,94; на 4-й показник – коефіцієнт 0,91.
+- При одночасному виконанні п’яти показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97; на 3-й показник – коефіцієнт 0,94; на 4-й показник – коефіцієнт 0,91, на 5-й показник – коефіцієнт 0,88. Оплата здійснюється за проведення максимум 5-х показників з переліку</t>
+  </si>
+  <si>
+    <t>Дослідження з кодами: A33025, A33048, A33055, S32001, S33002, D33004, D32001, F33002, H33002, R32004, B33011, A34016 R33004, A34041 A32001, K33002, B33005 – оплата здійснюється за умови вказання потрібної інформації в текстовому полі ДЗ</t>
+  </si>
+  <si>
+    <t>Дослідження класу L4 підлягають оплаті за умови виконання їх такими спеціалістами та фахівцями (коди посад P276, P71, P74, P17, P75, P173, P242, P72, P277, P148, P272, P274, P242, Р281)</t>
+  </si>
+  <si>
+    <t>L5</t>
+  </si>
+  <si>
+    <t>Тканинна патологія</t>
+  </si>
+  <si>
+    <t>LR.5.1</t>
+  </si>
+  <si>
+    <t>LR.5.2</t>
+  </si>
+  <si>
+    <t>LR.5.3</t>
+  </si>
+  <si>
+    <t>LR.5.4</t>
+  </si>
+  <si>
+    <t>LR.5.5</t>
+  </si>
+  <si>
+    <t>Коли послуги, описані в класі L5, виконуються на матеріалі, який надається для цитологічного дослідження групи L6,</t>
+  </si>
+  <si>
+    <t>Проведення досліджень (коди 97052-00, B37002, D37001, F37001, H37001, K37001, L37001, N37001, R37001, S37001, T37001, U37001, W37001, X37002, X37006, Y37001, Y37003) відносяться до високоспецифічних досліджень за умови наявності</t>
+  </si>
+  <si>
+    <t>Проведення досліджень (коди 97052-00, B37002, D37001, F37001, H37001, K37001, L37001, N37001, R37001, S37001, T37001, U37001, W37001, X37002, X37006, Y37001, Y37003)</t>
+  </si>
+  <si>
+    <t>Дослідження з кодами: A37001, A38002</t>
+  </si>
+  <si>
+    <t>Дослідження класу L5 підлягають оплаті за умови</t>
+  </si>
+  <si>
+    <t>LR51</t>
+  </si>
+  <si>
+    <t>LR52</t>
+  </si>
+  <si>
+    <t>LR53</t>
+  </si>
+  <si>
+    <t>LR54</t>
+  </si>
+  <si>
+    <t>LR55</t>
+  </si>
+  <si>
+    <t>Коли послуги, описані в класі L5, виконуються на матеріалі, який надається для цитологічного дослідження групи L6, оплата здійснюється лише за дослідження групи L6</t>
+  </si>
+  <si>
+    <t>Проведення досліджень (коди 97052-00, B37002, D37001, F37001, H37001, K37001, L37001, N37001, R37001, S37001, T37001, U37001, W37001, X37002, X37006, Y37001, Y37003) відносяться до високоспецифічних досліджень за умови наявності у пацієнтів діагнозів (коди С00-D48)</t>
+  </si>
+  <si>
+    <t>Проведення досліджень (коди 97052-00, B37002, D37001, F37001, H37001, K37001, L37001, N37001, R37001, S37001, T37001, U37001, W37001, X37002, X37006, Y37001, Y37003) При визначенні вартості за проведення вказаних досліджень застосовуються такі додаткові коефіцієнти:
+- При одночасному виконанні двох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97.
+- При одночасному виконанні трьох показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97; на 3-ий показник – коефіцієнт 0,94.
+- При одночасному виконанні чотирьох показників або більше показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97; на 3-й показник – коефіцієнт 0,94; на 4-й показник – коефіцієнт 0,91.
+- При одночасному виконанні п’яти показників з переліку – на 1-й показник застосовується коефіцієнт 1,0; на 2-й показник – коефіцієнт 0,97; на 3-й показник – коефіцієнт 0,94; на 4-й показник – коефіцієнт 0,91, на 5-й показник – коефіцієнт 0,88. Оплата здійснюється за проведення максимум 5-х показників з переліку</t>
+  </si>
+  <si>
+    <t>Дослідження з кодами: A37001, A38002– оплата здійснюється за умови вказання потрібної інформації в текстовому полі ДЗ</t>
+  </si>
+  <si>
+    <t>Дослідження класу L5 підлягають оплаті за умови виконання їх такими спеціалістами та фахівцями (коди посад P71, P74, P17, P173, P101, P102, P244, P277, P243, P75, P276, P242, Р281)</t>
+  </si>
+  <si>
+    <t>L6</t>
+  </si>
+  <si>
+    <t>Цитологія</t>
+  </si>
+  <si>
+    <t>LR.6.1</t>
+  </si>
+  <si>
+    <t>LR.6.2</t>
+  </si>
+  <si>
+    <t>LR.6.3</t>
+  </si>
+  <si>
+    <t>ПАП-тест</t>
+  </si>
+  <si>
+    <t>Проведення досліджень (коди 97053-00, A37002, B37003, D37002, F37002, H37002, K37002, L37002, N37002, R37002, R37003, S37002, T37002, U37002, W37002, X37003, Y37002)</t>
+  </si>
+  <si>
+    <t>Дослідження класу L6 підлягають оплаті за умови</t>
+  </si>
+  <si>
+    <t>LR61</t>
+  </si>
+  <si>
+    <t>LR62</t>
+  </si>
+  <si>
+    <t>LR63</t>
+  </si>
+  <si>
+    <t>L7</t>
+  </si>
+  <si>
+    <t>L8</t>
+  </si>
+  <si>
+    <t>ПАП-тест за виконання одного або декількох досліджень (коди X37001 X37005 92130-00) – оплата здійснюється як за одне дослідження</t>
+  </si>
+  <si>
+    <t>Проведення досліджень (коди 97053-00, A37002, B37003, D37002, F37002, H37002, K37002, L37002, N37002, R37002, R37003, S37002, T37002, U37002, W37002, X37003, Y37002)
+Оплата здійснюється максимум за 3 дослідження</t>
+  </si>
+  <si>
+    <t>Дослідження класу L6 підлягають оплаті за умови виконання їх такими спеціалістами та фахівцями (коди посад P71, P74, P17, P173, P101, P102, P244, P277, P243, P75, P276, P242, Р281)</t>
+  </si>
+  <si>
+    <t>Генетика</t>
+  </si>
+  <si>
+    <t>LR.7.1</t>
+  </si>
+  <si>
+    <t>LR.7.2</t>
+  </si>
+  <si>
+    <t>LR.7.3</t>
+  </si>
+  <si>
+    <t>LR.7.4</t>
+  </si>
+  <si>
+    <t>LR.7.5</t>
+  </si>
+  <si>
+    <t>Дослідження щодо визначення генної мутації або делеції або транслокації</t>
+  </si>
+  <si>
+    <t>Дослідження (код 70111-0, код W38002)</t>
+  </si>
+  <si>
+    <t>Дослідження з кодом спостереження 35474-6</t>
+  </si>
+  <si>
+    <t>Дослідження з кодами: D38002, W38002</t>
+  </si>
+  <si>
+    <t>Дослідження класу L7 підлягають оплаті за умови</t>
+  </si>
+  <si>
+    <t>LR71</t>
+  </si>
+  <si>
+    <t>LR72</t>
+  </si>
+  <si>
+    <t>LR73</t>
+  </si>
+  <si>
+    <t>LR74</t>
+  </si>
+  <si>
+    <t>LR75</t>
+  </si>
+  <si>
+    <t>Дослідження щодо визначення генної мутації або делеції або транслокації (коди 52757-2, 49706-5, 89037-6, 81842-7, 38928-8, 95770-4, 60497-5, 41097-7, 53887-6, 49857-6, 77050-3, 34675-9, 35137-9, 57310-5, 35291-4, 28060-2, 91712-0, 24475-6, 28005-7, 35645-1, 73735-3, 21686-1, 36917-3, 94197-1, 21759-6, 35359-9, 48970-8, 87436-2, 82246-0, 72654-7, 92002-5, 29770-5, 95773-8, 94242-5, 90256-9, 76037-1, 75401-0, 81844-3, 94206-0) – оплата здійснюється один раз за життя</t>
+  </si>
+  <si>
+    <t>Дослідження (код 70111-0, код W38002) оплачуються один раз з розрахунку на 1 плід (під час вагітності)</t>
+  </si>
+  <si>
+    <t>Дослідження з кодом спостереження 35474-6 Аналіз генної мутації у Крові або Тканині Молекулярно-генетичним методом - оплата здійснюється за пакетом "Неонатальний скринінг" в рамках послуги "Експертна діагностика неонатального скринінгу"</t>
+  </si>
+  <si>
+    <t>Дослідження з кодами: D38002, W38002 – оплата здійснюється за умови вказання потрібної інформації в текстовому полі ДЗ</t>
+  </si>
+  <si>
+    <t>Дослідження класу L7 підлягають оплаті за умови виконання їх такими спеціалістами та фахівцями (коди посад P71, P74, P17, P72, P276, P274)</t>
+  </si>
+  <si>
+    <t>Інші дослідження</t>
+  </si>
+  <si>
+    <t>LR.8.1</t>
+  </si>
+  <si>
+    <t>LR.8.2</t>
+  </si>
+  <si>
+    <t>LR.8.3</t>
+  </si>
+  <si>
+    <t>LR.8.4</t>
+  </si>
+  <si>
+    <t>LR.8.5</t>
+  </si>
+  <si>
+    <t>LR.8.6</t>
+  </si>
+  <si>
+    <t>Аналіз сечі</t>
+  </si>
+  <si>
+    <t>Визначення якості сперми</t>
+  </si>
+  <si>
+    <t>Скринінг на наркотики</t>
+  </si>
+  <si>
+    <t>Дослідження з кодами: U35002, A35010, B35001, X38001, D35001, R38001, A35005, D36002, P38001, F38001, H38001, S38001, X35001, Y33005, Y38001</t>
+  </si>
+  <si>
+    <t>Дослідження класу L8</t>
+  </si>
+  <si>
+    <t>Аналіз сечі (код 5804-0, код 2349-9, код 2887-8, код 2514-8, код 20408-1, код 5794-3) Виконання одного або кількох показників з одного зразка – оплата здійснюється як за одне дослідження</t>
+  </si>
+  <si>
+    <t>Визначення якості сперми (код Y38003 Аналіз; визначення якості сперми та Y38002 Аналіз; кількість сперматозоїдів) Виконання одного або двох показників з одного зразка – оплата здійснюється як за одне дослідження Оплата здійснюється за дослідження, що виконані не більше двох разів за 12 місяців.</t>
+  </si>
+  <si>
+    <t>Аналіз сечі (код 2888-6, код 15076-3, код 2756-5, код 33903-6, код 1978-6, 3104-7, код 12235-8) Виконання одного або кількох показників з одного зразка – оплата здійснюється як за одне дослідження</t>
+  </si>
+  <si>
+    <t>Скринінг на наркотики (код 18282-4, код 3879-4) Виконання одного або кількох показників з одного зразка – оплата здійснюється як за одне дослідження</t>
+  </si>
+  <si>
+    <t>Дослідження з кодами:U35002, A35010, B35001, X38001, D35001, R38001 A35005, D36002, P38001, F38001, H38001, S38001, X35001, Y33005, Y38001– оплата здійснюється за умови вказання потрібної інформації в текстовому полі ДЗ</t>
+  </si>
+  <si>
+    <t>Дослідження класу L8 (крім кодів 5804-0, 2514-8, 20408-1, 5794-3, 182824) підлягають оплаті за умови виконання їх такими спеціалістами та фахівцями (коди посад P71, P74, P17, P75, P243, P173, P277, P146, P272, P242, Р281)</t>
+  </si>
+  <si>
+    <t>LR81</t>
+  </si>
+  <si>
+    <t>LR82</t>
+  </si>
+  <si>
+    <t>LR83</t>
+  </si>
+  <si>
+    <t>LR84</t>
+  </si>
+  <si>
+    <t>LR85</t>
+  </si>
+  <si>
+    <t>LR86</t>
   </si>
 </sst>
 </file>
@@ -1598,11 +2036,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D134"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="50" customWidth="1"/>
+    <col min="3" max="3" width="60.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2926,6 +3364,552 @@
         <v>369</v>
       </c>
       <c r="D95" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" t="s">
+        <v>345</v>
+      </c>
+      <c r="B96" t="s">
+        <v>387</v>
+      </c>
+      <c r="C96" t="s">
+        <v>419</v>
+      </c>
+      <c r="D96" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" t="s">
+        <v>345</v>
+      </c>
+      <c r="B97" t="s">
+        <v>388</v>
+      </c>
+      <c r="C97" t="s">
+        <v>420</v>
+      </c>
+      <c r="D97" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" t="s">
+        <v>345</v>
+      </c>
+      <c r="B98" t="s">
+        <v>389</v>
+      </c>
+      <c r="C98" t="s">
+        <v>421</v>
+      </c>
+      <c r="D98" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" t="s">
+        <v>345</v>
+      </c>
+      <c r="B99" t="s">
+        <v>390</v>
+      </c>
+      <c r="C99" t="s">
+        <v>421</v>
+      </c>
+      <c r="D99" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" t="s">
+        <v>345</v>
+      </c>
+      <c r="B100" t="s">
+        <v>391</v>
+      </c>
+      <c r="C100" t="s">
+        <v>421</v>
+      </c>
+      <c r="D100" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" t="s">
+        <v>345</v>
+      </c>
+      <c r="B101" t="s">
+        <v>392</v>
+      </c>
+      <c r="C101" t="s">
+        <v>422</v>
+      </c>
+      <c r="D101" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" t="s">
+        <v>345</v>
+      </c>
+      <c r="B102" t="s">
+        <v>393</v>
+      </c>
+      <c r="C102" t="s">
+        <v>421</v>
+      </c>
+      <c r="D102" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" t="s">
+        <v>345</v>
+      </c>
+      <c r="B103" t="s">
+        <v>394</v>
+      </c>
+      <c r="C103" t="s">
+        <v>421</v>
+      </c>
+      <c r="D103" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" t="s">
+        <v>345</v>
+      </c>
+      <c r="B104" t="s">
+        <v>395</v>
+      </c>
+      <c r="C104" t="s">
+        <v>423</v>
+      </c>
+      <c r="D104" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" t="s">
+        <v>345</v>
+      </c>
+      <c r="B105" t="s">
+        <v>396</v>
+      </c>
+      <c r="C105" t="s">
+        <v>421</v>
+      </c>
+      <c r="D105" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" t="s">
+        <v>345</v>
+      </c>
+      <c r="B106" t="s">
+        <v>397</v>
+      </c>
+      <c r="C106" t="s">
+        <v>421</v>
+      </c>
+      <c r="D106" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" t="s">
+        <v>345</v>
+      </c>
+      <c r="B107" t="s">
+        <v>398</v>
+      </c>
+      <c r="C107" t="s">
+        <v>421</v>
+      </c>
+      <c r="D107" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" t="s">
+        <v>345</v>
+      </c>
+      <c r="B108" t="s">
+        <v>399</v>
+      </c>
+      <c r="C108" t="s">
+        <v>421</v>
+      </c>
+      <c r="D108" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" t="s">
+        <v>345</v>
+      </c>
+      <c r="B109" t="s">
+        <v>400</v>
+      </c>
+      <c r="C109" t="s">
+        <v>421</v>
+      </c>
+      <c r="D109" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" t="s">
+        <v>345</v>
+      </c>
+      <c r="B110" t="s">
+        <v>401</v>
+      </c>
+      <c r="C110" t="s">
+        <v>424</v>
+      </c>
+      <c r="D110" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" t="s">
+        <v>345</v>
+      </c>
+      <c r="B111" t="s">
+        <v>402</v>
+      </c>
+      <c r="C111" t="s">
+        <v>425</v>
+      </c>
+      <c r="D111" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" t="s">
+        <v>2</v>
+      </c>
+      <c r="B112" t="s">
+        <v>442</v>
+      </c>
+      <c r="C112" t="s">
+        <v>443</v>
+      </c>
+      <c r="D112" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" t="s">
+        <v>442</v>
+      </c>
+      <c r="B113" t="s">
+        <v>444</v>
+      </c>
+      <c r="C113" t="s">
+        <v>449</v>
+      </c>
+      <c r="D113" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" t="s">
+        <v>442</v>
+      </c>
+      <c r="B114" t="s">
+        <v>445</v>
+      </c>
+      <c r="C114" t="s">
+        <v>450</v>
+      </c>
+      <c r="D114" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" t="s">
+        <v>442</v>
+      </c>
+      <c r="B115" t="s">
+        <v>446</v>
+      </c>
+      <c r="C115" t="s">
+        <v>451</v>
+      </c>
+      <c r="D115" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" t="s">
+        <v>442</v>
+      </c>
+      <c r="B116" t="s">
+        <v>447</v>
+      </c>
+      <c r="C116" t="s">
+        <v>452</v>
+      </c>
+      <c r="D116" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" t="s">
+        <v>442</v>
+      </c>
+      <c r="B117" t="s">
+        <v>448</v>
+      </c>
+      <c r="C117" t="s">
+        <v>453</v>
+      </c>
+      <c r="D117" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" t="s">
+        <v>2</v>
+      </c>
+      <c r="B118" t="s">
+        <v>464</v>
+      </c>
+      <c r="C118" t="s">
+        <v>465</v>
+      </c>
+      <c r="D118" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" t="s">
+        <v>464</v>
+      </c>
+      <c r="B119" t="s">
+        <v>466</v>
+      </c>
+      <c r="C119" t="s">
+        <v>469</v>
+      </c>
+      <c r="D119" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" t="s">
+        <v>464</v>
+      </c>
+      <c r="B120" t="s">
+        <v>467</v>
+      </c>
+      <c r="C120" t="s">
+        <v>470</v>
+      </c>
+      <c r="D120" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" t="s">
+        <v>464</v>
+      </c>
+      <c r="B121" t="s">
+        <v>468</v>
+      </c>
+      <c r="C121" t="s">
+        <v>471</v>
+      </c>
+      <c r="D121" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" t="s">
+        <v>2</v>
+      </c>
+      <c r="B122" t="s">
+        <v>475</v>
+      </c>
+      <c r="C122" t="s">
+        <v>480</v>
+      </c>
+      <c r="D122" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" t="s">
+        <v>475</v>
+      </c>
+      <c r="B123" t="s">
+        <v>481</v>
+      </c>
+      <c r="C123" t="s">
+        <v>486</v>
+      </c>
+      <c r="D123" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" t="s">
+        <v>475</v>
+      </c>
+      <c r="B124" t="s">
+        <v>482</v>
+      </c>
+      <c r="C124" t="s">
+        <v>487</v>
+      </c>
+      <c r="D124" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" t="s">
+        <v>475</v>
+      </c>
+      <c r="B125" t="s">
+        <v>483</v>
+      </c>
+      <c r="C125" t="s">
+        <v>488</v>
+      </c>
+      <c r="D125" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" t="s">
+        <v>475</v>
+      </c>
+      <c r="B126" t="s">
+        <v>484</v>
+      </c>
+      <c r="C126" t="s">
+        <v>489</v>
+      </c>
+      <c r="D126" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" t="s">
+        <v>475</v>
+      </c>
+      <c r="B127" t="s">
+        <v>485</v>
+      </c>
+      <c r="C127" t="s">
+        <v>490</v>
+      </c>
+      <c r="D127" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" t="s">
+        <v>2</v>
+      </c>
+      <c r="B128" t="s">
+        <v>476</v>
+      </c>
+      <c r="C128" t="s">
+        <v>501</v>
+      </c>
+      <c r="D128" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129" t="s">
+        <v>476</v>
+      </c>
+      <c r="B129" t="s">
+        <v>502</v>
+      </c>
+      <c r="C129" t="s">
+        <v>508</v>
+      </c>
+      <c r="D129" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" t="s">
+        <v>476</v>
+      </c>
+      <c r="B130" t="s">
+        <v>503</v>
+      </c>
+      <c r="C130" t="s">
+        <v>509</v>
+      </c>
+      <c r="D130" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" t="s">
+        <v>476</v>
+      </c>
+      <c r="B131" t="s">
+        <v>504</v>
+      </c>
+      <c r="C131" t="s">
+        <v>508</v>
+      </c>
+      <c r="D131" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" t="s">
+        <v>476</v>
+      </c>
+      <c r="B132" t="s">
+        <v>505</v>
+      </c>
+      <c r="C132" t="s">
+        <v>510</v>
+      </c>
+      <c r="D132" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" ht="43.2">
+      <c r="A133" t="s">
+        <v>476</v>
+      </c>
+      <c r="B133" t="s">
+        <v>506</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="D133" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" t="s">
+        <v>476</v>
+      </c>
+      <c r="B134" t="s">
+        <v>507</v>
+      </c>
+      <c r="C134" t="s">
+        <v>512</v>
+      </c>
+      <c r="D134" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2937,7 +3921,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D456371C-55CC-41A7-AFCE-65668AB9659F}">
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E123"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="18.21875" customWidth="1"/>
@@ -4442,6 +5426,601 @@
         <v>360</v>
       </c>
     </row>
+    <row r="89" spans="1:5">
+      <c r="A89" t="s">
+        <v>403</v>
+      </c>
+      <c r="B89">
+        <v>9</v>
+      </c>
+      <c r="C89" t="s">
+        <v>2</v>
+      </c>
+      <c r="D89" t="s">
+        <v>345</v>
+      </c>
+      <c r="E89" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" t="s">
+        <v>404</v>
+      </c>
+      <c r="B90">
+        <v>9</v>
+      </c>
+      <c r="C90" t="s">
+        <v>2</v>
+      </c>
+      <c r="D90" t="s">
+        <v>345</v>
+      </c>
+      <c r="E90" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" t="s">
+        <v>405</v>
+      </c>
+      <c r="B91">
+        <v>9</v>
+      </c>
+      <c r="C91" t="s">
+        <v>2</v>
+      </c>
+      <c r="D91" t="s">
+        <v>345</v>
+      </c>
+      <c r="E91" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" t="s">
+        <v>406</v>
+      </c>
+      <c r="B92">
+        <v>9</v>
+      </c>
+      <c r="C92" t="s">
+        <v>2</v>
+      </c>
+      <c r="D92" t="s">
+        <v>345</v>
+      </c>
+      <c r="E92" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" t="s">
+        <v>407</v>
+      </c>
+      <c r="B93">
+        <v>9</v>
+      </c>
+      <c r="C93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D93" t="s">
+        <v>345</v>
+      </c>
+      <c r="E93" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" t="s">
+        <v>408</v>
+      </c>
+      <c r="B94">
+        <v>9</v>
+      </c>
+      <c r="C94" t="s">
+        <v>2</v>
+      </c>
+      <c r="D94" t="s">
+        <v>345</v>
+      </c>
+      <c r="E94" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" t="s">
+        <v>409</v>
+      </c>
+      <c r="B95">
+        <v>9</v>
+      </c>
+      <c r="C95" t="s">
+        <v>2</v>
+      </c>
+      <c r="D95" t="s">
+        <v>345</v>
+      </c>
+      <c r="E95" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" t="s">
+        <v>410</v>
+      </c>
+      <c r="B96">
+        <v>9</v>
+      </c>
+      <c r="C96" t="s">
+        <v>2</v>
+      </c>
+      <c r="D96" t="s">
+        <v>345</v>
+      </c>
+      <c r="E96" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" t="s">
+        <v>411</v>
+      </c>
+      <c r="B97">
+        <v>9</v>
+      </c>
+      <c r="C97" t="s">
+        <v>2</v>
+      </c>
+      <c r="D97" t="s">
+        <v>345</v>
+      </c>
+      <c r="E97" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" t="s">
+        <v>412</v>
+      </c>
+      <c r="B98">
+        <v>9</v>
+      </c>
+      <c r="C98" t="s">
+        <v>2</v>
+      </c>
+      <c r="D98" t="s">
+        <v>345</v>
+      </c>
+      <c r="E98" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" t="s">
+        <v>413</v>
+      </c>
+      <c r="B99">
+        <v>9</v>
+      </c>
+      <c r="C99" t="s">
+        <v>2</v>
+      </c>
+      <c r="D99" t="s">
+        <v>345</v>
+      </c>
+      <c r="E99" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" t="s">
+        <v>414</v>
+      </c>
+      <c r="B100">
+        <v>9</v>
+      </c>
+      <c r="C100" t="s">
+        <v>2</v>
+      </c>
+      <c r="D100" t="s">
+        <v>345</v>
+      </c>
+      <c r="E100" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" t="s">
+        <v>415</v>
+      </c>
+      <c r="B101">
+        <v>9</v>
+      </c>
+      <c r="C101" t="s">
+        <v>2</v>
+      </c>
+      <c r="D101" t="s">
+        <v>345</v>
+      </c>
+      <c r="E101" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" t="s">
+        <v>416</v>
+      </c>
+      <c r="B102">
+        <v>9</v>
+      </c>
+      <c r="C102" t="s">
+        <v>2</v>
+      </c>
+      <c r="D102" t="s">
+        <v>345</v>
+      </c>
+      <c r="E102" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" t="s">
+        <v>417</v>
+      </c>
+      <c r="B103">
+        <v>9</v>
+      </c>
+      <c r="C103" t="s">
+        <v>2</v>
+      </c>
+      <c r="D103" t="s">
+        <v>345</v>
+      </c>
+      <c r="E103" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" t="s">
+        <v>418</v>
+      </c>
+      <c r="B104">
+        <v>9</v>
+      </c>
+      <c r="C104" t="s">
+        <v>2</v>
+      </c>
+      <c r="D104" t="s">
+        <v>345</v>
+      </c>
+      <c r="E104" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" t="s">
+        <v>454</v>
+      </c>
+      <c r="B105">
+        <v>9</v>
+      </c>
+      <c r="C105" t="s">
+        <v>2</v>
+      </c>
+      <c r="D105" t="s">
+        <v>442</v>
+      </c>
+      <c r="E105" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" t="s">
+        <v>455</v>
+      </c>
+      <c r="B106">
+        <v>9</v>
+      </c>
+      <c r="C106" t="s">
+        <v>2</v>
+      </c>
+      <c r="D106" t="s">
+        <v>442</v>
+      </c>
+      <c r="E106" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" t="s">
+        <v>456</v>
+      </c>
+      <c r="B107">
+        <v>9</v>
+      </c>
+      <c r="C107" t="s">
+        <v>2</v>
+      </c>
+      <c r="D107" t="s">
+        <v>442</v>
+      </c>
+      <c r="E107" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" t="s">
+        <v>457</v>
+      </c>
+      <c r="B108">
+        <v>9</v>
+      </c>
+      <c r="C108" t="s">
+        <v>2</v>
+      </c>
+      <c r="D108" t="s">
+        <v>442</v>
+      </c>
+      <c r="E108" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" t="s">
+        <v>458</v>
+      </c>
+      <c r="B109">
+        <v>9</v>
+      </c>
+      <c r="C109" t="s">
+        <v>2</v>
+      </c>
+      <c r="D109" t="s">
+        <v>442</v>
+      </c>
+      <c r="E109" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" t="s">
+        <v>472</v>
+      </c>
+      <c r="B110">
+        <v>9</v>
+      </c>
+      <c r="C110" t="s">
+        <v>2</v>
+      </c>
+      <c r="D110" t="s">
+        <v>464</v>
+      </c>
+      <c r="E110" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" t="s">
+        <v>473</v>
+      </c>
+      <c r="B111">
+        <v>9</v>
+      </c>
+      <c r="C111" t="s">
+        <v>2</v>
+      </c>
+      <c r="D111" t="s">
+        <v>464</v>
+      </c>
+      <c r="E111" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" t="s">
+        <v>474</v>
+      </c>
+      <c r="B112">
+        <v>9</v>
+      </c>
+      <c r="C112" t="s">
+        <v>2</v>
+      </c>
+      <c r="D112" t="s">
+        <v>464</v>
+      </c>
+      <c r="E112" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" t="s">
+        <v>491</v>
+      </c>
+      <c r="B113">
+        <v>9</v>
+      </c>
+      <c r="C113" t="s">
+        <v>2</v>
+      </c>
+      <c r="D113" t="s">
+        <v>475</v>
+      </c>
+      <c r="E113" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" t="s">
+        <v>492</v>
+      </c>
+      <c r="B114">
+        <v>9</v>
+      </c>
+      <c r="C114" t="s">
+        <v>2</v>
+      </c>
+      <c r="D114" t="s">
+        <v>475</v>
+      </c>
+      <c r="E114" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" t="s">
+        <v>493</v>
+      </c>
+      <c r="B115">
+        <v>9</v>
+      </c>
+      <c r="C115" t="s">
+        <v>2</v>
+      </c>
+      <c r="D115" t="s">
+        <v>475</v>
+      </c>
+      <c r="E115" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" t="s">
+        <v>494</v>
+      </c>
+      <c r="B116">
+        <v>9</v>
+      </c>
+      <c r="C116" t="s">
+        <v>2</v>
+      </c>
+      <c r="D116" t="s">
+        <v>475</v>
+      </c>
+      <c r="E116" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" t="s">
+        <v>495</v>
+      </c>
+      <c r="B117">
+        <v>9</v>
+      </c>
+      <c r="C117" t="s">
+        <v>2</v>
+      </c>
+      <c r="D117" t="s">
+        <v>475</v>
+      </c>
+      <c r="E117" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" t="s">
+        <v>519</v>
+      </c>
+      <c r="B118">
+        <v>9</v>
+      </c>
+      <c r="C118" t="s">
+        <v>2</v>
+      </c>
+      <c r="D118" t="s">
+        <v>476</v>
+      </c>
+      <c r="E118" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" t="s">
+        <v>520</v>
+      </c>
+      <c r="B119">
+        <v>9</v>
+      </c>
+      <c r="C119" t="s">
+        <v>2</v>
+      </c>
+      <c r="D119" t="s">
+        <v>476</v>
+      </c>
+      <c r="E119" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" t="s">
+        <v>521</v>
+      </c>
+      <c r="B120">
+        <v>9</v>
+      </c>
+      <c r="C120" t="s">
+        <v>2</v>
+      </c>
+      <c r="D120" t="s">
+        <v>476</v>
+      </c>
+      <c r="E120" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" t="s">
+        <v>522</v>
+      </c>
+      <c r="B121">
+        <v>9</v>
+      </c>
+      <c r="C121" t="s">
+        <v>2</v>
+      </c>
+      <c r="D121" t="s">
+        <v>476</v>
+      </c>
+      <c r="E121" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" t="s">
+        <v>523</v>
+      </c>
+      <c r="B122">
+        <v>9</v>
+      </c>
+      <c r="C122" t="s">
+        <v>2</v>
+      </c>
+      <c r="D122" t="s">
+        <v>476</v>
+      </c>
+      <c r="E122" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" t="s">
+        <v>524</v>
+      </c>
+      <c r="B123">
+        <v>9</v>
+      </c>
+      <c r="C123" t="s">
+        <v>2</v>
+      </c>
+      <c r="D123" t="s">
+        <v>476</v>
+      </c>
+      <c r="E123" t="s">
+        <v>507</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4450,7 +6029,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D500C81C-80F5-46C0-959E-2202AF945DAB}">
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H124"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
@@ -6248,6 +7827,706 @@
       </c>
       <c r="H89" s="3" t="s">
         <v>386</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="72">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>403</v>
+      </c>
+      <c r="C90">
+        <v>1</v>
+      </c>
+      <c r="D90" t="s">
+        <v>83</v>
+      </c>
+      <c r="E90" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="57.6">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>404</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
+      <c r="D91" t="s">
+        <v>83</v>
+      </c>
+      <c r="E91" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="43.2">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>405</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+      <c r="D92" t="s">
+        <v>83</v>
+      </c>
+      <c r="E92" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="57.6">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>406</v>
+      </c>
+      <c r="C93">
+        <v>1</v>
+      </c>
+      <c r="D93" t="s">
+        <v>83</v>
+      </c>
+      <c r="E93" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="72">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>407</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
+      <c r="D94" t="s">
+        <v>83</v>
+      </c>
+      <c r="E94" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="86.4">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>408</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
+      <c r="D95" t="s">
+        <v>83</v>
+      </c>
+      <c r="E95" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="72">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>409</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+      <c r="D96" t="s">
+        <v>83</v>
+      </c>
+      <c r="E96" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="72">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>410</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+      <c r="D97" t="s">
+        <v>83</v>
+      </c>
+      <c r="E97" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="86.4">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>411</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+      <c r="D98" t="s">
+        <v>83</v>
+      </c>
+      <c r="E98" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="43.2">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>412</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
+      <c r="D99" t="s">
+        <v>83</v>
+      </c>
+      <c r="E99" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="57.6">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>413</v>
+      </c>
+      <c r="C100">
+        <v>1</v>
+      </c>
+      <c r="D100" t="s">
+        <v>83</v>
+      </c>
+      <c r="E100" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="57.6">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>414</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
+      <c r="D101" t="s">
+        <v>83</v>
+      </c>
+      <c r="E101" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="129.6">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>415</v>
+      </c>
+      <c r="C102">
+        <v>1</v>
+      </c>
+      <c r="D102" t="s">
+        <v>83</v>
+      </c>
+      <c r="E102" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="244.8">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>416</v>
+      </c>
+      <c r="C103">
+        <v>1</v>
+      </c>
+      <c r="D103" t="s">
+        <v>83</v>
+      </c>
+      <c r="E103" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="43.2">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>417</v>
+      </c>
+      <c r="C104">
+        <v>1</v>
+      </c>
+      <c r="D104" t="s">
+        <v>83</v>
+      </c>
+      <c r="E104" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" ht="43.2">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>418</v>
+      </c>
+      <c r="C105">
+        <v>1</v>
+      </c>
+      <c r="D105" t="s">
+        <v>83</v>
+      </c>
+      <c r="E105" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="28.8">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>454</v>
+      </c>
+      <c r="C106">
+        <v>1</v>
+      </c>
+      <c r="D106" t="s">
+        <v>83</v>
+      </c>
+      <c r="E106" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="43.2">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>455</v>
+      </c>
+      <c r="C107">
+        <v>1</v>
+      </c>
+      <c r="D107" t="s">
+        <v>83</v>
+      </c>
+      <c r="E107" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="216">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>456</v>
+      </c>
+      <c r="C108">
+        <v>1</v>
+      </c>
+      <c r="D108" t="s">
+        <v>83</v>
+      </c>
+      <c r="E108" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" ht="28.8">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>457</v>
+      </c>
+      <c r="C109">
+        <v>1</v>
+      </c>
+      <c r="D109" t="s">
+        <v>83</v>
+      </c>
+      <c r="E109" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="28.8">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>458</v>
+      </c>
+      <c r="C110">
+        <v>1</v>
+      </c>
+      <c r="D110" t="s">
+        <v>83</v>
+      </c>
+      <c r="E110" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="28.8">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>472</v>
+      </c>
+      <c r="C111">
+        <v>1</v>
+      </c>
+      <c r="D111" t="s">
+        <v>83</v>
+      </c>
+      <c r="E111" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H111" s="3" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="43.2">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>473</v>
+      </c>
+      <c r="C112">
+        <v>1</v>
+      </c>
+      <c r="D112" t="s">
+        <v>83</v>
+      </c>
+      <c r="E112" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" ht="28.8">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>474</v>
+      </c>
+      <c r="C113">
+        <v>1</v>
+      </c>
+      <c r="D113" t="s">
+        <v>83</v>
+      </c>
+      <c r="E113" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" ht="72">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>491</v>
+      </c>
+      <c r="C114">
+        <v>1</v>
+      </c>
+      <c r="D114" t="s">
+        <v>83</v>
+      </c>
+      <c r="E114" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="28.8">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>492</v>
+      </c>
+      <c r="C115">
+        <v>1</v>
+      </c>
+      <c r="D115" t="s">
+        <v>83</v>
+      </c>
+      <c r="E115" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="43.2">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>493</v>
+      </c>
+      <c r="C116">
+        <v>1</v>
+      </c>
+      <c r="D116" t="s">
+        <v>83</v>
+      </c>
+      <c r="E116" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" ht="28.8">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>494</v>
+      </c>
+      <c r="C117">
+        <v>1</v>
+      </c>
+      <c r="D117" t="s">
+        <v>83</v>
+      </c>
+      <c r="E117" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" ht="28.8">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" t="s">
+        <v>495</v>
+      </c>
+      <c r="C118">
+        <v>1</v>
+      </c>
+      <c r="D118" t="s">
+        <v>83</v>
+      </c>
+      <c r="E118" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" ht="28.8">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>519</v>
+      </c>
+      <c r="C119">
+        <v>1</v>
+      </c>
+      <c r="D119" t="s">
+        <v>83</v>
+      </c>
+      <c r="E119" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H119" s="3" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" ht="57.6">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" t="s">
+        <v>520</v>
+      </c>
+      <c r="C120">
+        <v>1</v>
+      </c>
+      <c r="D120" t="s">
+        <v>83</v>
+      </c>
+      <c r="E120" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" ht="43.2">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" t="s">
+        <v>521</v>
+      </c>
+      <c r="C121">
+        <v>1</v>
+      </c>
+      <c r="D121" t="s">
+        <v>83</v>
+      </c>
+      <c r="E121" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H121" s="3" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" ht="28.8">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122" t="s">
+        <v>522</v>
+      </c>
+      <c r="C122">
+        <v>1</v>
+      </c>
+      <c r="D122" t="s">
+        <v>83</v>
+      </c>
+      <c r="E122" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H122" s="3" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" ht="43.2">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123" t="s">
+        <v>523</v>
+      </c>
+      <c r="C123">
+        <v>1</v>
+      </c>
+      <c r="D123" t="s">
+        <v>83</v>
+      </c>
+      <c r="E123" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H123" s="3" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" ht="43.2">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124" t="s">
+        <v>524</v>
+      </c>
+      <c r="C124">
+        <v>1</v>
+      </c>
+      <c r="D124" t="s">
+        <v>83</v>
+      </c>
+      <c r="E124" s="2">
+        <v>45839</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>518</v>
       </c>
     </row>
   </sheetData>

--- a/data/database.xlsx
+++ b/data/database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oleh.koval\Desktop\Правила_9пакет\prodject_rules\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4009D905-2E41-48C6-9DF3-E814ACA2DDE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C676C808-5768-4C84-AB46-A3FAB663D4F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dicts" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,8 @@
     <sheet name="documents" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">rule_versions!$A$1:$H$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">dicts!$A$1:$D$138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">rule_versions!$A$1:$H$131</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1420" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1469" uniqueCount="545">
   <si>
     <t>cod</t>
   </si>
@@ -1685,6 +1686,93 @@
   </si>
   <si>
     <t>LR86</t>
+  </si>
+  <si>
+    <t>LR04</t>
+  </si>
+  <si>
+    <t>LR05</t>
+  </si>
+  <si>
+    <t>LR.04</t>
+  </si>
+  <si>
+    <t>LR.05</t>
+  </si>
+  <si>
+    <t>Дослідження, які входять в неонатальний скринінг</t>
+  </si>
+  <si>
+    <t>Дослідження, які можуть проводитися і дорослим і дітям</t>
+  </si>
+  <si>
+    <t>Дослідження, які входять в неонатальний скринінг (первинний та експертний) та зараховуватися у звіт на оплату в рамках амбулаторного пакету: коди спостережень 13965-9, 2762-3, 3077-5, 29293-8, 20661-5, 34466-3, 2309-3, 2399-4, 2398-6, 32799-9, 2553-6, 2818-3, 17492-0, 58457-3, 17752-7, 2772-2, 32240-4, 16550-6, 2676-5, 16711-4, 27336-7, 12467-7, 29770-5, 57318-8, 87436-2, 70111-0</t>
+  </si>
+  <si>
+    <t>Дослідження, які можуть проводитися і дорослим і дітям: коди спостережень 24053-1, 24057-2, 1837-4, 24061-4, 1941-4, 24065-5, 13962-6, 24068-9, 12913-0, 1954-7, 23825-3, 24084-6, 104263-9, 240861, 90234-6, 32540-7, 38477-6, 24089-5, 94488-4, 24101-8, 32759-3, 82883-0, 13964-2, 55806-4, 70211-8, 74935-8, 76038-9, 48633-2, 2762-3, 38355-4, 24078-8, 24076-2, 24094-5, 24096-0, 26904-3, 34466-3, 2399-4, 2398-6, 32799-9, 2818-3, 2772-2, 16550-6, 2676-5, 16711-4</t>
+  </si>
+  <si>
+    <t>Дослідження з кодами: A34038, K34003, B34024, T34031, F34001, A33041, P34001, T35002, A35003, R38001, N34002, A38001 T38001, K34002 K38001, Y35001, W38001, A34022, H34001, U34001, U34003, U34002, W34001, A34030, X34001, S34001, Y34001, R38001, D36002* – оплата здійснюється за умови вказання потрібної інформації в текстовому полі ДЗ</t>
+  </si>
+  <si>
+    <t>Змінено 1.09.2025 *(виключено код X38001, доповнено кодами R38001, D36002)</t>
+  </si>
+  <si>
+    <t>Дослідження класу L3 (крім кодів D33022, A33036, D33013, C19001, C19003, 94558-4) підлягають оплаті за умови виконання їх такими спеціалістами та фахівцями (коди посад P71, P17, P241, P39, P271, P40, P81, P273, P278, P146, P74, P173, P276, P242), крім кодів:
+- F33001 Аналіз; мікробіологія; око;
+- A33036 Скринінг антитіл (швидкий тест на виявлення гепатиту В);
+- 33006 Аналіз; ВІЛ (швидкий тест);
+- C19003 COVID - Проведено ПЛР тест;
+- 94558-4 Антиген SARS-CoV-2 (COVID-19) [Наявність] у Зразку з органів дихання Методом швидкого імунологічного аналізу.*</t>
+  </si>
+  <si>
+    <t>Змінено 1.09.2025 *(доповнено: крім кодів:
+- F33001 Аналіз; мікробіологія; око;
+- A33036 Скринінг антитіл (швидкий тест на виявлення гепатиту В);
+- B33006 Аналіз; ВІЛ (швидкий тест);
+- C19003 COVID - Проведено ПЛР тест;
+- 94558-4 Антиген SARS-CoV-2 (COVID-19) [Наявність] у Зразку з органів дихання Методом імунологічного аналізу.)</t>
+  </si>
+  <si>
+    <t>LR.7.6</t>
+  </si>
+  <si>
+    <t>Дослідження з кодом спостереження 86205-2</t>
+  </si>
+  <si>
+    <t>LR76</t>
+  </si>
+  <si>
+    <t>Дослідження з кодом спостереження 86205-2 Повноекзомне секвенування (WES) у Крові або Тканині Молекулярно-генетичним методом та 94087-4 Панель зміни кількості копій аналізу хромосом у звіт на оплату потрапляє за умови виконання його дітям</t>
+  </si>
+  <si>
+    <t>Дослідження з кодами: U35002, A35010, B35001, X38001*, D35001, A35005, P38001, F38001, H38001, S38001, X35001, Y33005, Y38001– оплата здійснюється за умови вказання потрібної інформації в текстовому полі ДЗ</t>
+  </si>
+  <si>
+    <t>Змінено 1.09.2025 *(виключено коди R38001, D36002, доповнено кодом X38001)</t>
+  </si>
+  <si>
+    <t>Дослідження класу L8 (крім кодів 5804-0, 2514-8, 20408-1, 5794-3, 18282-4) підлягають оплаті за умови виконання їх такими спеціалістами та фахівцями (коди посад P71, P74, P17, P75, P243, P173, P72, P277, P241, P39, P271, P276, P146, P148, P40, P81, P272, P273, P274, P278, P242, P244*) 
+Крім кодів: 
+ -  5804-0 Білок у Сечі; 
+ -  2349-9 Глюкоза у Сечі; 
+ -  2887-8 Білок [Наявність] у Сечі; 
+ -  2514-8 Кетони [Наявність] у Сечі Визначення тестсмужкою; 
+ -  20408-1 Лейкоцити [#/об'єм] у Сечі Визначення тестсмужкою;
+ -  5794-3 Гемоглобін [Наявність] у Сечі Визначення тестсмужкою; 
+ -  18282-4 Канабіноїди [Наявність] у Сечі Методом скринінгу.**</t>
+  </si>
+  <si>
+    <t>Змінено 1.08.2025
+*(виключено коди P71, P74, P17, P75, P243, P173, P277, P146, P272, P242, Р281, доповнено кодами P71, P74, P17, P75, P243, P173, P72, P277, P241, P39, P271, P276, P146, P148, P40, P81, P272, P273, P274, P278, P242, P244)
+**(доповнено: Крім кодів:
+ - 5804-0 Білок у Сечі;
+ - 2349-9 Глюкоза у Сечі;
+ - 2887-8 Білок [Наявність] у Сечі;
+ - 2514-8 Кетони [Наявність] у Сечі Визначення тест-смужкою;
+ - 20408-1 Лейкоцити [#/об'єм] у Сечі Визначення тест-смужкою;
+ - 5794-3 Гемоглобін [Наявність] у Сечі Визначення тест-смужкою;
+ - 18282-4 Канабіноїди [Наявність] у Сечі Методом скринінгу.</t>
   </si>
 </sst>
 </file>
@@ -1719,18 +1807,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1745,14 +1827,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2036,7 +2117,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D134"/>
+  <dimension ref="A1:D137"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
@@ -2058,39 +2139,45 @@
       </c>
     </row>
     <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2098,10 +2185,10 @@
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>527</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>529</v>
       </c>
       <c r="D5" t="s">
         <v>26</v>
@@ -2112,10 +2199,10 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>528</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>46</v>
+        <v>530</v>
       </c>
       <c r="D6" t="s">
         <v>26</v>
@@ -2123,13 +2210,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>50</v>
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
@@ -2137,16 +2224,16 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2154,10 +2241,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
@@ -2168,10 +2255,10 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
         <v>26</v>
@@ -2182,10 +2269,10 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="D11" t="s">
         <v>26</v>
@@ -2196,10 +2283,10 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D12" t="s">
         <v>26</v>
@@ -2210,10 +2297,10 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
         <v>26</v>
@@ -2224,10 +2311,10 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
         <v>26</v>
@@ -2235,13 +2322,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D15" t="s">
         <v>26</v>
@@ -2249,13 +2336,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="B16" t="s">
-        <v>66</v>
+        <v>116</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="D16" t="s">
         <v>26</v>
@@ -2263,16 +2350,16 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="D17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2280,10 +2367,10 @@
         <v>73</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="C18" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="D18" t="s">
         <v>26</v>
@@ -2294,10 +2381,10 @@
         <v>73</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="D19" t="s">
         <v>26</v>
@@ -2308,10 +2395,10 @@
         <v>73</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="C20" t="s">
-        <v>89</v>
+        <v>141</v>
       </c>
       <c r="D20" t="s">
         <v>26</v>
@@ -2322,10 +2409,10 @@
         <v>73</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="C21" t="s">
-        <v>93</v>
+        <v>155</v>
       </c>
       <c r="D21" t="s">
         <v>26</v>
@@ -2336,10 +2423,10 @@
         <v>73</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>145</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c r="D22" t="s">
         <v>26</v>
@@ -2350,10 +2437,10 @@
         <v>73</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="C23" t="s">
-        <v>101</v>
+        <v>157</v>
       </c>
       <c r="D23" t="s">
         <v>26</v>
@@ -2364,10 +2451,10 @@
         <v>73</v>
       </c>
       <c r="B24" t="s">
-        <v>104</v>
+        <v>147</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>158</v>
       </c>
       <c r="D24" t="s">
         <v>26</v>
@@ -2378,10 +2465,10 @@
         <v>73</v>
       </c>
       <c r="B25" t="s">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="C25" t="s">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="D25" t="s">
         <v>26</v>
@@ -2392,10 +2479,10 @@
         <v>73</v>
       </c>
       <c r="B26" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="D26" t="s">
         <v>26</v>
@@ -2406,10 +2493,10 @@
         <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="C27" t="s">
-        <v>109</v>
+        <v>160</v>
       </c>
       <c r="D27" t="s">
         <v>26</v>
@@ -2420,10 +2507,10 @@
         <v>73</v>
       </c>
       <c r="B28" t="s">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="C28" t="s">
-        <v>120</v>
+        <v>161</v>
       </c>
       <c r="D28" t="s">
         <v>26</v>
@@ -2434,10 +2521,10 @@
         <v>73</v>
       </c>
       <c r="B29" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="C29" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="D29" t="s">
         <v>26</v>
@@ -2448,10 +2535,10 @@
         <v>73</v>
       </c>
       <c r="B30" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="C30" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="D30" t="s">
         <v>26</v>
@@ -2462,10 +2549,10 @@
         <v>73</v>
       </c>
       <c r="B31" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="C31" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="D31" t="s">
         <v>26</v>
@@ -2476,10 +2563,10 @@
         <v>73</v>
       </c>
       <c r="B32" t="s">
-        <v>144</v>
+        <v>88</v>
       </c>
       <c r="C32" t="s">
-        <v>155</v>
+        <v>89</v>
       </c>
       <c r="D32" t="s">
         <v>26</v>
@@ -2490,10 +2577,10 @@
         <v>73</v>
       </c>
       <c r="B33" t="s">
-        <v>145</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>156</v>
+        <v>93</v>
       </c>
       <c r="D33" t="s">
         <v>26</v>
@@ -2504,10 +2591,10 @@
         <v>73</v>
       </c>
       <c r="B34" t="s">
-        <v>146</v>
+        <v>96</v>
       </c>
       <c r="C34" t="s">
-        <v>157</v>
+        <v>97</v>
       </c>
       <c r="D34" t="s">
         <v>26</v>
@@ -2518,10 +2605,10 @@
         <v>73</v>
       </c>
       <c r="B35" t="s">
-        <v>147</v>
+        <v>100</v>
       </c>
       <c r="C35" t="s">
-        <v>158</v>
+        <v>101</v>
       </c>
       <c r="D35" t="s">
         <v>26</v>
@@ -2532,10 +2619,10 @@
         <v>73</v>
       </c>
       <c r="B36" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
-        <v>159</v>
+        <v>105</v>
       </c>
       <c r="D36" t="s">
         <v>26</v>
@@ -2546,10 +2633,10 @@
         <v>73</v>
       </c>
       <c r="B37" t="s">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="C37" t="s">
-        <v>160</v>
+        <v>109</v>
       </c>
       <c r="D37" t="s">
         <v>26</v>
@@ -2560,10 +2647,10 @@
         <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="C38" t="s">
-        <v>161</v>
+        <v>113</v>
       </c>
       <c r="D38" t="s">
         <v>26</v>
@@ -2571,13 +2658,13 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>73</v>
+        <v>154</v>
       </c>
       <c r="B39" t="s">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="C39" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="D39" t="s">
         <v>26</v>
@@ -2585,13 +2672,13 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>73</v>
+        <v>154</v>
       </c>
       <c r="B40" t="s">
-        <v>152</v>
+        <v>224</v>
       </c>
       <c r="C40" t="s">
-        <v>163</v>
+        <v>225</v>
       </c>
       <c r="D40" t="s">
         <v>26</v>
@@ -2599,13 +2686,13 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>73</v>
+        <v>154</v>
       </c>
       <c r="B41" t="s">
-        <v>153</v>
+        <v>226</v>
       </c>
       <c r="C41" t="s">
-        <v>164</v>
+        <v>229</v>
       </c>
       <c r="D41" t="s">
         <v>26</v>
@@ -2613,16 +2700,16 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>2</v>
+        <v>154</v>
       </c>
       <c r="B42" t="s">
-        <v>154</v>
+        <v>227</v>
       </c>
       <c r="C42" t="s">
-        <v>185</v>
+        <v>230</v>
       </c>
       <c r="D42" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2630,10 +2717,10 @@
         <v>154</v>
       </c>
       <c r="B43" t="s">
-        <v>186</v>
+        <v>228</v>
       </c>
       <c r="C43" t="s">
-        <v>187</v>
+        <v>231</v>
       </c>
       <c r="D43" t="s">
         <v>26</v>
@@ -2644,10 +2731,10 @@
         <v>154</v>
       </c>
       <c r="B44" t="s">
-        <v>190</v>
+        <v>240</v>
       </c>
       <c r="C44" t="s">
-        <v>198</v>
+        <v>241</v>
       </c>
       <c r="D44" t="s">
         <v>26</v>
@@ -2658,10 +2745,10 @@
         <v>154</v>
       </c>
       <c r="B45" t="s">
-        <v>191</v>
+        <v>242</v>
       </c>
       <c r="C45" t="s">
-        <v>199</v>
+        <v>241</v>
       </c>
       <c r="D45" t="s">
         <v>26</v>
@@ -2672,10 +2759,10 @@
         <v>154</v>
       </c>
       <c r="B46" t="s">
-        <v>192</v>
+        <v>243</v>
       </c>
       <c r="C46" t="s">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="D46" t="s">
         <v>26</v>
@@ -2686,10 +2773,10 @@
         <v>154</v>
       </c>
       <c r="B47" t="s">
-        <v>193</v>
+        <v>244</v>
       </c>
       <c r="C47" t="s">
-        <v>201</v>
+        <v>251</v>
       </c>
       <c r="D47" t="s">
         <v>26</v>
@@ -2700,10 +2787,10 @@
         <v>154</v>
       </c>
       <c r="B48" t="s">
-        <v>194</v>
+        <v>245</v>
       </c>
       <c r="C48" t="s">
-        <v>202</v>
+        <v>252</v>
       </c>
       <c r="D48" t="s">
         <v>26</v>
@@ -2714,10 +2801,10 @@
         <v>154</v>
       </c>
       <c r="B49" t="s">
-        <v>195</v>
+        <v>246</v>
       </c>
       <c r="C49" t="s">
-        <v>203</v>
+        <v>252</v>
       </c>
       <c r="D49" t="s">
         <v>26</v>
@@ -2728,10 +2815,10 @@
         <v>154</v>
       </c>
       <c r="B50" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C50" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D50" t="s">
         <v>26</v>
@@ -2742,10 +2829,10 @@
         <v>154</v>
       </c>
       <c r="B51" t="s">
-        <v>197</v>
+        <v>247</v>
       </c>
       <c r="C51" t="s">
-        <v>205</v>
+        <v>255</v>
       </c>
       <c r="D51" t="s">
         <v>26</v>
@@ -2756,10 +2843,10 @@
         <v>154</v>
       </c>
       <c r="B52" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="C52" t="s">
-        <v>225</v>
+        <v>254</v>
       </c>
       <c r="D52" t="s">
         <v>26</v>
@@ -2770,10 +2857,10 @@
         <v>154</v>
       </c>
       <c r="B53" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C53" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="D53" t="s">
         <v>26</v>
@@ -2784,10 +2871,10 @@
         <v>154</v>
       </c>
       <c r="B54" t="s">
-        <v>227</v>
+        <v>272</v>
       </c>
       <c r="C54" t="s">
-        <v>230</v>
+        <v>280</v>
       </c>
       <c r="D54" t="s">
         <v>26</v>
@@ -2798,10 +2885,10 @@
         <v>154</v>
       </c>
       <c r="B55" t="s">
-        <v>228</v>
+        <v>273</v>
       </c>
       <c r="C55" t="s">
-        <v>231</v>
+        <v>281</v>
       </c>
       <c r="D55" t="s">
         <v>26</v>
@@ -2812,10 +2899,10 @@
         <v>154</v>
       </c>
       <c r="B56" t="s">
-        <v>240</v>
+        <v>274</v>
       </c>
       <c r="C56" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D56" t="s">
         <v>26</v>
@@ -2826,10 +2913,10 @@
         <v>154</v>
       </c>
       <c r="B57" t="s">
-        <v>242</v>
+        <v>275</v>
       </c>
       <c r="C57" t="s">
-        <v>241</v>
+        <v>283</v>
       </c>
       <c r="D57" t="s">
         <v>26</v>
@@ -2840,10 +2927,10 @@
         <v>154</v>
       </c>
       <c r="B58" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="C58" t="s">
-        <v>250</v>
+        <v>284</v>
       </c>
       <c r="D58" t="s">
         <v>26</v>
@@ -2854,10 +2941,10 @@
         <v>154</v>
       </c>
       <c r="B59" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="C59" t="s">
-        <v>251</v>
+        <v>285</v>
       </c>
       <c r="D59" t="s">
         <v>26</v>
@@ -2868,10 +2955,10 @@
         <v>154</v>
       </c>
       <c r="B60" t="s">
-        <v>245</v>
+        <v>278</v>
       </c>
       <c r="C60" t="s">
-        <v>252</v>
+        <v>286</v>
       </c>
       <c r="D60" t="s">
         <v>26</v>
@@ -2882,10 +2969,10 @@
         <v>154</v>
       </c>
       <c r="B61" t="s">
-        <v>246</v>
+        <v>191</v>
       </c>
       <c r="C61" t="s">
-        <v>252</v>
+        <v>199</v>
       </c>
       <c r="D61" t="s">
         <v>26</v>
@@ -2896,10 +2983,10 @@
         <v>154</v>
       </c>
       <c r="B62" t="s">
-        <v>247</v>
+        <v>279</v>
       </c>
       <c r="C62" t="s">
-        <v>255</v>
+        <v>287</v>
       </c>
       <c r="D62" t="s">
         <v>26</v>
@@ -2910,10 +2997,10 @@
         <v>154</v>
       </c>
       <c r="B63" t="s">
-        <v>248</v>
+        <v>299</v>
       </c>
       <c r="C63" t="s">
-        <v>254</v>
+        <v>300</v>
       </c>
       <c r="D63" t="s">
         <v>26</v>
@@ -2924,10 +3011,10 @@
         <v>154</v>
       </c>
       <c r="B64" t="s">
-        <v>249</v>
+        <v>301</v>
       </c>
       <c r="C64" t="s">
-        <v>253</v>
+        <v>304</v>
       </c>
       <c r="D64" t="s">
         <v>26</v>
@@ -2938,10 +3025,10 @@
         <v>154</v>
       </c>
       <c r="B65" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C65" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="D65" t="s">
         <v>26</v>
@@ -2952,10 +3039,10 @@
         <v>154</v>
       </c>
       <c r="B66" t="s">
-        <v>273</v>
+        <v>303</v>
       </c>
       <c r="C66" t="s">
-        <v>281</v>
+        <v>306</v>
       </c>
       <c r="D66" t="s">
         <v>26</v>
@@ -2966,10 +3053,10 @@
         <v>154</v>
       </c>
       <c r="B67" t="s">
-        <v>274</v>
+        <v>314</v>
       </c>
       <c r="C67" t="s">
-        <v>282</v>
+        <v>315</v>
       </c>
       <c r="D67" t="s">
         <v>26</v>
@@ -2980,10 +3067,10 @@
         <v>154</v>
       </c>
       <c r="B68" t="s">
-        <v>275</v>
+        <v>319</v>
       </c>
       <c r="C68" t="s">
-        <v>283</v>
+        <v>320</v>
       </c>
       <c r="D68" t="s">
         <v>26</v>
@@ -2994,10 +3081,10 @@
         <v>154</v>
       </c>
       <c r="B69" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="C69" t="s">
-        <v>284</v>
+        <v>322</v>
       </c>
       <c r="D69" t="s">
         <v>26</v>
@@ -3008,10 +3095,10 @@
         <v>154</v>
       </c>
       <c r="B70" t="s">
-        <v>277</v>
+        <v>325</v>
       </c>
       <c r="C70" t="s">
-        <v>285</v>
+        <v>330</v>
       </c>
       <c r="D70" t="s">
         <v>26</v>
@@ -3022,10 +3109,10 @@
         <v>154</v>
       </c>
       <c r="B71" t="s">
-        <v>278</v>
+        <v>192</v>
       </c>
       <c r="C71" t="s">
-        <v>286</v>
+        <v>200</v>
       </c>
       <c r="D71" t="s">
         <v>26</v>
@@ -3036,10 +3123,10 @@
         <v>154</v>
       </c>
       <c r="B72" t="s">
-        <v>279</v>
+        <v>326</v>
       </c>
       <c r="C72" t="s">
-        <v>287</v>
+        <v>331</v>
       </c>
       <c r="D72" t="s">
         <v>26</v>
@@ -3050,10 +3137,10 @@
         <v>154</v>
       </c>
       <c r="B73" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="C73" t="s">
-        <v>300</v>
+        <v>332</v>
       </c>
       <c r="D73" t="s">
         <v>26</v>
@@ -3064,10 +3151,10 @@
         <v>154</v>
       </c>
       <c r="B74" t="s">
-        <v>301</v>
+        <v>328</v>
       </c>
       <c r="C74" t="s">
-        <v>304</v>
+        <v>333</v>
       </c>
       <c r="D74" t="s">
         <v>26</v>
@@ -3078,10 +3165,10 @@
         <v>154</v>
       </c>
       <c r="B75" t="s">
-        <v>302</v>
+        <v>329</v>
       </c>
       <c r="C75" t="s">
-        <v>305</v>
+        <v>334</v>
       </c>
       <c r="D75" t="s">
         <v>26</v>
@@ -3092,10 +3179,10 @@
         <v>154</v>
       </c>
       <c r="B76" t="s">
-        <v>303</v>
+        <v>193</v>
       </c>
       <c r="C76" t="s">
-        <v>306</v>
+        <v>201</v>
       </c>
       <c r="D76" t="s">
         <v>26</v>
@@ -3106,10 +3193,10 @@
         <v>154</v>
       </c>
       <c r="B77" t="s">
-        <v>314</v>
+        <v>194</v>
       </c>
       <c r="C77" t="s">
-        <v>315</v>
+        <v>202</v>
       </c>
       <c r="D77" t="s">
         <v>26</v>
@@ -3120,10 +3207,10 @@
         <v>154</v>
       </c>
       <c r="B78" t="s">
-        <v>319</v>
+        <v>195</v>
       </c>
       <c r="C78" t="s">
-        <v>320</v>
+        <v>203</v>
       </c>
       <c r="D78" t="s">
         <v>26</v>
@@ -3134,10 +3221,10 @@
         <v>154</v>
       </c>
       <c r="B79" t="s">
-        <v>321</v>
+        <v>196</v>
       </c>
       <c r="C79" t="s">
-        <v>322</v>
+        <v>204</v>
       </c>
       <c r="D79" t="s">
         <v>26</v>
@@ -3148,10 +3235,10 @@
         <v>154</v>
       </c>
       <c r="B80" t="s">
-        <v>325</v>
+        <v>197</v>
       </c>
       <c r="C80" t="s">
-        <v>330</v>
+        <v>205</v>
       </c>
       <c r="D80" t="s">
         <v>26</v>
@@ -3159,13 +3246,13 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>154</v>
+        <v>345</v>
       </c>
       <c r="B81" t="s">
-        <v>326</v>
+        <v>350</v>
       </c>
       <c r="C81" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="D81" t="s">
         <v>26</v>
@@ -3173,13 +3260,13 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>154</v>
+        <v>345</v>
       </c>
       <c r="B82" t="s">
-        <v>327</v>
+        <v>360</v>
       </c>
       <c r="C82" t="s">
-        <v>332</v>
+        <v>369</v>
       </c>
       <c r="D82" t="s">
         <v>26</v>
@@ -3187,13 +3274,13 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>154</v>
+        <v>345</v>
       </c>
       <c r="B83" t="s">
-        <v>328</v>
+        <v>387</v>
       </c>
       <c r="C83" t="s">
-        <v>333</v>
+        <v>419</v>
       </c>
       <c r="D83" t="s">
         <v>26</v>
@@ -3201,13 +3288,13 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>154</v>
+        <v>345</v>
       </c>
       <c r="B84" t="s">
-        <v>329</v>
+        <v>388</v>
       </c>
       <c r="C84" t="s">
-        <v>334</v>
+        <v>420</v>
       </c>
       <c r="D84" t="s">
         <v>26</v>
@@ -3215,16 +3302,16 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>2</v>
+        <v>345</v>
       </c>
       <c r="B85" t="s">
-        <v>345</v>
+        <v>389</v>
       </c>
       <c r="C85" t="s">
-        <v>346</v>
+        <v>421</v>
       </c>
       <c r="D85" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3232,10 +3319,10 @@
         <v>345</v>
       </c>
       <c r="B86" t="s">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="C86" t="s">
-        <v>351</v>
+        <v>421</v>
       </c>
       <c r="D86" t="s">
         <v>26</v>
@@ -3246,10 +3333,10 @@
         <v>345</v>
       </c>
       <c r="B87" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
       <c r="C87" t="s">
-        <v>361</v>
+        <v>421</v>
       </c>
       <c r="D87" t="s">
         <v>26</v>
@@ -3260,10 +3347,10 @@
         <v>345</v>
       </c>
       <c r="B88" t="s">
-        <v>353</v>
+        <v>392</v>
       </c>
       <c r="C88" t="s">
-        <v>362</v>
+        <v>422</v>
       </c>
       <c r="D88" t="s">
         <v>26</v>
@@ -3274,10 +3361,10 @@
         <v>345</v>
       </c>
       <c r="B89" t="s">
-        <v>354</v>
+        <v>393</v>
       </c>
       <c r="C89" t="s">
-        <v>363</v>
+        <v>421</v>
       </c>
       <c r="D89" t="s">
         <v>26</v>
@@ -3288,10 +3375,10 @@
         <v>345</v>
       </c>
       <c r="B90" t="s">
-        <v>355</v>
+        <v>394</v>
       </c>
       <c r="C90" t="s">
-        <v>364</v>
+        <v>421</v>
       </c>
       <c r="D90" t="s">
         <v>26</v>
@@ -3302,10 +3389,10 @@
         <v>345</v>
       </c>
       <c r="B91" t="s">
-        <v>356</v>
+        <v>395</v>
       </c>
       <c r="C91" t="s">
-        <v>365</v>
+        <v>423</v>
       </c>
       <c r="D91" t="s">
         <v>26</v>
@@ -3316,10 +3403,10 @@
         <v>345</v>
       </c>
       <c r="B92" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C92" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="D92" t="s">
         <v>26</v>
@@ -3330,10 +3417,10 @@
         <v>345</v>
       </c>
       <c r="B93" t="s">
-        <v>358</v>
+        <v>396</v>
       </c>
       <c r="C93" t="s">
-        <v>367</v>
+        <v>421</v>
       </c>
       <c r="D93" t="s">
         <v>26</v>
@@ -3344,10 +3431,10 @@
         <v>345</v>
       </c>
       <c r="B94" t="s">
-        <v>359</v>
+        <v>397</v>
       </c>
       <c r="C94" t="s">
-        <v>368</v>
+        <v>421</v>
       </c>
       <c r="D94" t="s">
         <v>26</v>
@@ -3358,10 +3445,10 @@
         <v>345</v>
       </c>
       <c r="B95" t="s">
-        <v>360</v>
+        <v>398</v>
       </c>
       <c r="C95" t="s">
-        <v>369</v>
+        <v>421</v>
       </c>
       <c r="D95" t="s">
         <v>26</v>
@@ -3372,10 +3459,10 @@
         <v>345</v>
       </c>
       <c r="B96" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="C96" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D96" t="s">
         <v>26</v>
@@ -3386,10 +3473,10 @@
         <v>345</v>
       </c>
       <c r="B97" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="C97" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D97" t="s">
         <v>26</v>
@@ -3400,10 +3487,10 @@
         <v>345</v>
       </c>
       <c r="B98" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="C98" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="D98" t="s">
         <v>26</v>
@@ -3414,10 +3501,10 @@
         <v>345</v>
       </c>
       <c r="B99" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="C99" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="D99" t="s">
         <v>26</v>
@@ -3428,10 +3515,10 @@
         <v>345</v>
       </c>
       <c r="B100" t="s">
-        <v>391</v>
+        <v>353</v>
       </c>
       <c r="C100" t="s">
-        <v>421</v>
+        <v>362</v>
       </c>
       <c r="D100" t="s">
         <v>26</v>
@@ -3442,10 +3529,10 @@
         <v>345</v>
       </c>
       <c r="B101" t="s">
-        <v>392</v>
+        <v>354</v>
       </c>
       <c r="C101" t="s">
-        <v>422</v>
+        <v>363</v>
       </c>
       <c r="D101" t="s">
         <v>26</v>
@@ -3456,10 +3543,10 @@
         <v>345</v>
       </c>
       <c r="B102" t="s">
-        <v>393</v>
+        <v>355</v>
       </c>
       <c r="C102" t="s">
-        <v>421</v>
+        <v>364</v>
       </c>
       <c r="D102" t="s">
         <v>26</v>
@@ -3470,10 +3557,10 @@
         <v>345</v>
       </c>
       <c r="B103" t="s">
-        <v>394</v>
+        <v>356</v>
       </c>
       <c r="C103" t="s">
-        <v>421</v>
+        <v>365</v>
       </c>
       <c r="D103" t="s">
         <v>26</v>
@@ -3484,10 +3571,10 @@
         <v>345</v>
       </c>
       <c r="B104" t="s">
-        <v>395</v>
+        <v>357</v>
       </c>
       <c r="C104" t="s">
-        <v>423</v>
+        <v>366</v>
       </c>
       <c r="D104" t="s">
         <v>26</v>
@@ -3498,10 +3585,10 @@
         <v>345</v>
       </c>
       <c r="B105" t="s">
-        <v>396</v>
+        <v>358</v>
       </c>
       <c r="C105" t="s">
-        <v>421</v>
+        <v>367</v>
       </c>
       <c r="D105" t="s">
         <v>26</v>
@@ -3512,10 +3599,10 @@
         <v>345</v>
       </c>
       <c r="B106" t="s">
-        <v>397</v>
+        <v>359</v>
       </c>
       <c r="C106" t="s">
-        <v>421</v>
+        <v>368</v>
       </c>
       <c r="D106" t="s">
         <v>26</v>
@@ -3523,13 +3610,13 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>345</v>
+        <v>442</v>
       </c>
       <c r="B107" t="s">
-        <v>398</v>
+        <v>444</v>
       </c>
       <c r="C107" t="s">
-        <v>421</v>
+        <v>449</v>
       </c>
       <c r="D107" t="s">
         <v>26</v>
@@ -3537,13 +3624,13 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>345</v>
+        <v>442</v>
       </c>
       <c r="B108" t="s">
-        <v>399</v>
+        <v>445</v>
       </c>
       <c r="C108" t="s">
-        <v>421</v>
+        <v>450</v>
       </c>
       <c r="D108" t="s">
         <v>26</v>
@@ -3551,13 +3638,13 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>345</v>
+        <v>442</v>
       </c>
       <c r="B109" t="s">
-        <v>400</v>
+        <v>446</v>
       </c>
       <c r="C109" t="s">
-        <v>421</v>
+        <v>451</v>
       </c>
       <c r="D109" t="s">
         <v>26</v>
@@ -3565,13 +3652,13 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>345</v>
+        <v>442</v>
       </c>
       <c r="B110" t="s">
-        <v>401</v>
+        <v>447</v>
       </c>
       <c r="C110" t="s">
-        <v>424</v>
+        <v>452</v>
       </c>
       <c r="D110" t="s">
         <v>26</v>
@@ -3579,13 +3666,13 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>345</v>
+        <v>442</v>
       </c>
       <c r="B111" t="s">
-        <v>402</v>
+        <v>448</v>
       </c>
       <c r="C111" t="s">
-        <v>425</v>
+        <v>453</v>
       </c>
       <c r="D111" t="s">
         <v>26</v>
@@ -3593,27 +3680,27 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>2</v>
+        <v>464</v>
       </c>
       <c r="B112" t="s">
-        <v>442</v>
+        <v>466</v>
       </c>
       <c r="C112" t="s">
-        <v>443</v>
+        <v>469</v>
       </c>
       <c r="D112" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>442</v>
+        <v>464</v>
       </c>
       <c r="B113" t="s">
-        <v>444</v>
+        <v>467</v>
       </c>
       <c r="C113" t="s">
-        <v>449</v>
+        <v>470</v>
       </c>
       <c r="D113" t="s">
         <v>26</v>
@@ -3621,13 +3708,13 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>442</v>
+        <v>464</v>
       </c>
       <c r="B114" t="s">
-        <v>445</v>
+        <v>468</v>
       </c>
       <c r="C114" t="s">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="D114" t="s">
         <v>26</v>
@@ -3635,13 +3722,13 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>442</v>
+        <v>475</v>
       </c>
       <c r="B115" t="s">
-        <v>446</v>
+        <v>481</v>
       </c>
       <c r="C115" t="s">
-        <v>451</v>
+        <v>486</v>
       </c>
       <c r="D115" t="s">
         <v>26</v>
@@ -3649,13 +3736,13 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>442</v>
+        <v>475</v>
       </c>
       <c r="B116" t="s">
-        <v>447</v>
+        <v>482</v>
       </c>
       <c r="C116" t="s">
-        <v>452</v>
+        <v>487</v>
       </c>
       <c r="D116" t="s">
         <v>26</v>
@@ -3663,13 +3750,13 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>442</v>
+        <v>475</v>
       </c>
       <c r="B117" t="s">
-        <v>448</v>
+        <v>483</v>
       </c>
       <c r="C117" t="s">
-        <v>453</v>
+        <v>488</v>
       </c>
       <c r="D117" t="s">
         <v>26</v>
@@ -3677,27 +3764,27 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>2</v>
+        <v>475</v>
       </c>
       <c r="B118" t="s">
-        <v>464</v>
+        <v>484</v>
       </c>
       <c r="C118" t="s">
-        <v>465</v>
+        <v>489</v>
       </c>
       <c r="D118" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="B119" t="s">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="C119" t="s">
-        <v>469</v>
+        <v>490</v>
       </c>
       <c r="D119" t="s">
         <v>26</v>
@@ -3705,13 +3792,13 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="B120" t="s">
-        <v>467</v>
+        <v>502</v>
       </c>
       <c r="C120" t="s">
-        <v>470</v>
+        <v>508</v>
       </c>
       <c r="D120" t="s">
         <v>26</v>
@@ -3719,13 +3806,13 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="B121" t="s">
-        <v>468</v>
+        <v>503</v>
       </c>
       <c r="C121" t="s">
-        <v>471</v>
+        <v>509</v>
       </c>
       <c r="D121" t="s">
         <v>26</v>
@@ -3733,41 +3820,41 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" t="s">
-        <v>2</v>
+        <v>476</v>
       </c>
       <c r="B122" t="s">
-        <v>475</v>
+        <v>504</v>
       </c>
       <c r="C122" t="s">
-        <v>480</v>
+        <v>508</v>
       </c>
       <c r="D122" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B123" t="s">
-        <v>481</v>
+        <v>505</v>
       </c>
       <c r="C123" t="s">
-        <v>486</v>
+        <v>510</v>
       </c>
       <c r="D123" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="124" spans="1:4">
+    <row r="124" spans="1:4" ht="43.2">
       <c r="A124" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B124" t="s">
-        <v>482</v>
-      </c>
-      <c r="C124" t="s">
-        <v>487</v>
+        <v>506</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>511</v>
       </c>
       <c r="D124" t="s">
         <v>26</v>
@@ -3775,13 +3862,13 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B125" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
       <c r="C125" t="s">
-        <v>488</v>
+        <v>512</v>
       </c>
       <c r="D125" t="s">
         <v>26</v>
@@ -3789,30 +3876,30 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>475</v>
+        <v>2</v>
       </c>
       <c r="B126" t="s">
-        <v>484</v>
-      </c>
-      <c r="C126" t="s">
-        <v>489</v>
+        <v>20</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D126" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>475</v>
+        <v>2</v>
       </c>
       <c r="B127" t="s">
-        <v>485</v>
+        <v>6</v>
       </c>
       <c r="C127" t="s">
-        <v>490</v>
+        <v>7</v>
       </c>
       <c r="D127" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3820,10 +3907,10 @@
         <v>2</v>
       </c>
       <c r="B128" t="s">
-        <v>476</v>
+        <v>73</v>
       </c>
       <c r="C128" t="s">
-        <v>501</v>
+        <v>78</v>
       </c>
       <c r="D128" t="s">
         <v>25</v>
@@ -3831,89 +3918,129 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" t="s">
-        <v>476</v>
+        <v>2</v>
       </c>
       <c r="B129" t="s">
-        <v>502</v>
+        <v>154</v>
       </c>
       <c r="C129" t="s">
-        <v>508</v>
+        <v>185</v>
       </c>
       <c r="D129" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" t="s">
-        <v>476</v>
+        <v>2</v>
       </c>
       <c r="B130" t="s">
-        <v>503</v>
+        <v>345</v>
       </c>
       <c r="C130" t="s">
-        <v>509</v>
+        <v>346</v>
       </c>
       <c r="D130" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" t="s">
-        <v>476</v>
+        <v>2</v>
       </c>
       <c r="B131" t="s">
-        <v>504</v>
+        <v>442</v>
       </c>
       <c r="C131" t="s">
-        <v>508</v>
+        <v>443</v>
       </c>
       <c r="D131" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" t="s">
-        <v>476</v>
+        <v>2</v>
       </c>
       <c r="B132" t="s">
-        <v>505</v>
+        <v>464</v>
       </c>
       <c r="C132" t="s">
-        <v>510</v>
+        <v>465</v>
       </c>
       <c r="D132" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" ht="43.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
       <c r="A133" t="s">
-        <v>476</v>
+        <v>2</v>
       </c>
       <c r="B133" t="s">
-        <v>506</v>
-      </c>
-      <c r="C133" s="3" t="s">
-        <v>511</v>
+        <v>475</v>
+      </c>
+      <c r="C133" t="s">
+        <v>480</v>
       </c>
       <c r="D133" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" t="s">
+        <v>2</v>
+      </c>
+      <c r="B134" t="s">
         <v>476</v>
       </c>
-      <c r="B134" t="s">
-        <v>507</v>
-      </c>
       <c r="C134" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="D134" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="B135" t="s">
+        <v>4</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D135" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="B136" t="s">
+        <v>2</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" t="s">
+        <v>475</v>
+      </c>
+      <c r="B137" t="s">
+        <v>537</v>
+      </c>
+      <c r="C137" t="s">
+        <v>538</v>
+      </c>
+      <c r="D137" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D138">
+    <sortCondition ref="A2:A138"/>
+    <sortCondition ref="B2:B138"/>
+  </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3921,7 +4048,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D456371C-55CC-41A7-AFCE-65668AB9659F}">
-  <dimension ref="A1:E123"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="18.21875" customWidth="1"/>
@@ -6021,6 +6148,57 @@
         <v>507</v>
       </c>
     </row>
+    <row r="124" spans="1:5">
+      <c r="A124" t="s">
+        <v>525</v>
+      </c>
+      <c r="B124">
+        <v>9</v>
+      </c>
+      <c r="C124" t="s">
+        <v>2</v>
+      </c>
+      <c r="D124" t="s">
+        <v>20</v>
+      </c>
+      <c r="E124" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" t="s">
+        <v>526</v>
+      </c>
+      <c r="B125">
+        <v>9</v>
+      </c>
+      <c r="C125" t="s">
+        <v>2</v>
+      </c>
+      <c r="D125" t="s">
+        <v>20</v>
+      </c>
+      <c r="E125" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" t="s">
+        <v>539</v>
+      </c>
+      <c r="B126">
+        <v>9</v>
+      </c>
+      <c r="C126" t="s">
+        <v>2</v>
+      </c>
+      <c r="D126" t="s">
+        <v>475</v>
+      </c>
+      <c r="E126" t="s">
+        <v>537</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6029,14 +6207,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D500C81C-80F5-46C0-959E-2202AF945DAB}">
-  <dimension ref="A1:H124"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:H131"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.5546875" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.21875" customWidth="1"/>
-    <col min="7" max="7" width="10.88671875" customWidth="1"/>
+    <col min="7" max="7" width="33.109375" customWidth="1"/>
     <col min="8" max="8" width="85.77734375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6066,7 +6245,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="132" customHeight="1">
+    <row r="2" spans="1:8" ht="132" hidden="1" customHeight="1">
       <c r="A2">
         <v>1</v>
       </c>
@@ -6086,7 +6265,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="44.4" customHeight="1">
+    <row r="3" spans="1:8" ht="44.4" hidden="1" customHeight="1">
       <c r="A3">
         <v>2</v>
       </c>
@@ -6106,7 +6285,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="52.2" customHeight="1">
+    <row r="4" spans="1:8" ht="52.2" hidden="1" customHeight="1">
       <c r="A4">
         <v>3</v>
       </c>
@@ -6126,7 +6305,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="47.4" customHeight="1">
+    <row r="5" spans="1:8" ht="47.4" hidden="1" customHeight="1">
       <c r="A5">
         <v>4</v>
       </c>
@@ -6146,7 +6325,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="86.4">
+    <row r="6" spans="1:8" ht="86.4" hidden="1">
       <c r="A6">
         <v>5</v>
       </c>
@@ -6166,7 +6345,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="169.8" customHeight="1">
+    <row r="7" spans="1:8" ht="169.8" hidden="1" customHeight="1">
       <c r="A7">
         <v>6</v>
       </c>
@@ -6186,7 +6365,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="115.2">
+    <row r="8" spans="1:8" ht="115.2" hidden="1">
       <c r="A8">
         <v>7</v>
       </c>
@@ -6206,7 +6385,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="160.80000000000001" customHeight="1">
+    <row r="9" spans="1:8" ht="160.80000000000001" hidden="1" customHeight="1">
       <c r="A9">
         <v>8</v>
       </c>
@@ -6226,7 +6405,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="43.2">
+    <row r="10" spans="1:8" ht="43.2" hidden="1">
       <c r="A10">
         <v>9</v>
       </c>
@@ -6246,7 +6425,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="28.8">
+    <row r="11" spans="1:8" ht="28.8" hidden="1">
       <c r="A11">
         <v>10</v>
       </c>
@@ -6266,7 +6445,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="34.200000000000003" customHeight="1">
+    <row r="12" spans="1:8" ht="34.200000000000003" hidden="1" customHeight="1">
       <c r="A12">
         <v>11</v>
       </c>
@@ -6286,7 +6465,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="302.39999999999998">
+    <row r="13" spans="1:8" ht="302.39999999999998" hidden="1">
       <c r="A13">
         <v>12</v>
       </c>
@@ -6306,7 +6485,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="86.4">
+    <row r="14" spans="1:8" ht="86.4" hidden="1">
       <c r="A14">
         <v>13</v>
       </c>
@@ -6326,7 +6505,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="28.8">
+    <row r="15" spans="1:8" ht="28.8" hidden="1">
       <c r="A15">
         <v>14</v>
       </c>
@@ -6346,7 +6525,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="57.6">
+    <row r="16" spans="1:8" ht="57.6" hidden="1">
       <c r="A16">
         <v>15</v>
       </c>
@@ -6366,7 +6545,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="28.8">
+    <row r="17" spans="1:8" ht="28.8" hidden="1">
       <c r="A17">
         <v>16</v>
       </c>
@@ -6386,7 +6565,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="76.2" customHeight="1">
+    <row r="18" spans="1:8" ht="76.2" hidden="1" customHeight="1">
       <c r="A18">
         <v>17</v>
       </c>
@@ -6406,7 +6585,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="127.8" customHeight="1">
+    <row r="19" spans="1:8" ht="127.8" hidden="1" customHeight="1">
       <c r="A19">
         <v>18</v>
       </c>
@@ -6426,7 +6605,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="43.2">
+    <row r="20" spans="1:8" ht="43.2" hidden="1">
       <c r="A20">
         <v>19</v>
       </c>
@@ -6446,7 +6625,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="115.2">
+    <row r="21" spans="1:8" ht="115.2" hidden="1">
       <c r="A21">
         <v>20</v>
       </c>
@@ -6466,7 +6645,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="57.6">
+    <row r="22" spans="1:8" ht="57.6" hidden="1">
       <c r="A22">
         <v>21</v>
       </c>
@@ -6486,7 +6665,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="273.60000000000002">
+    <row r="23" spans="1:8" ht="273.60000000000002" hidden="1">
       <c r="A23">
         <v>22</v>
       </c>
@@ -6506,7 +6685,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="43.2">
+    <row r="24" spans="1:8" ht="43.2" hidden="1">
       <c r="A24">
         <v>23</v>
       </c>
@@ -6526,8 +6705,8 @@
         <v>126</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="273.60000000000002">
-      <c r="A25" s="4">
+    <row r="25" spans="1:8" ht="273.60000000000002" hidden="1">
+      <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
@@ -6542,14 +6721,14 @@
       <c r="E25" s="2">
         <v>45901</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G25" s="3" t="s">
         <v>129</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="129.6">
+    <row r="26" spans="1:8" ht="129.6" hidden="1">
       <c r="A26">
         <v>25</v>
       </c>
@@ -6569,7 +6748,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="57.6">
+    <row r="27" spans="1:8" ht="57.6" hidden="1">
       <c r="A27">
         <v>26</v>
       </c>
@@ -6589,7 +6768,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="28.8">
+    <row r="28" spans="1:8" ht="28.8" hidden="1">
       <c r="A28">
         <v>27</v>
       </c>
@@ -6609,7 +6788,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="201.6">
+    <row r="29" spans="1:8" ht="201.6" hidden="1">
       <c r="A29">
         <v>28</v>
       </c>
@@ -6629,7 +6808,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="72">
+    <row r="30" spans="1:8" ht="72" hidden="1">
       <c r="A30">
         <v>29</v>
       </c>
@@ -6649,7 +6828,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="43.2">
+    <row r="31" spans="1:8" ht="43.2" hidden="1">
       <c r="A31">
         <v>30</v>
       </c>
@@ -6669,7 +6848,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="158.4">
+    <row r="32" spans="1:8" ht="158.4" hidden="1">
       <c r="A32">
         <v>31</v>
       </c>
@@ -6689,7 +6868,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="172.8">
+    <row r="33" spans="1:8" ht="172.8" hidden="1">
       <c r="A33">
         <v>32</v>
       </c>
@@ -6709,7 +6888,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="28.8">
+    <row r="34" spans="1:8" ht="28.8" hidden="1">
       <c r="A34">
         <v>33</v>
       </c>
@@ -6729,7 +6908,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="57.6">
+    <row r="35" spans="1:8" ht="57.6" hidden="1">
       <c r="A35">
         <v>34</v>
       </c>
@@ -6740,7 +6919,7 @@
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="E35" s="2">
         <v>45839</v>
@@ -6749,7 +6928,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="28.8">
+    <row r="36" spans="1:8" ht="28.8" hidden="1">
       <c r="A36">
         <v>35</v>
       </c>
@@ -6769,7 +6948,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="43.2">
+    <row r="37" spans="1:8" ht="43.2" hidden="1">
       <c r="A37">
         <v>36</v>
       </c>
@@ -6789,7 +6968,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="57.6">
+    <row r="38" spans="1:8" ht="57.6" hidden="1">
       <c r="A38">
         <v>37</v>
       </c>
@@ -6809,7 +6988,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="115.2">
+    <row r="39" spans="1:8" ht="115.2" hidden="1">
       <c r="A39">
         <v>38</v>
       </c>
@@ -6829,7 +7008,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="43.2">
+    <row r="40" spans="1:8" ht="43.2" hidden="1">
       <c r="A40">
         <v>39</v>
       </c>
@@ -6849,7 +7028,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="43.2">
+    <row r="41" spans="1:8" ht="43.2" hidden="1">
       <c r="A41">
         <v>40</v>
       </c>
@@ -6869,7 +7048,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="43.2">
+    <row r="42" spans="1:8" ht="43.2" hidden="1">
       <c r="A42">
         <v>41</v>
       </c>
@@ -6889,7 +7068,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="43.2">
+    <row r="43" spans="1:8" ht="43.2" hidden="1">
       <c r="A43">
         <v>42</v>
       </c>
@@ -6909,7 +7088,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="43.2">
+    <row r="44" spans="1:8" ht="43.2" hidden="1">
       <c r="A44">
         <v>43</v>
       </c>
@@ -6929,7 +7108,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="43.2">
+    <row r="45" spans="1:8" ht="43.2" hidden="1">
       <c r="A45">
         <v>44</v>
       </c>
@@ -6949,7 +7128,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="86.4">
+    <row r="46" spans="1:8" ht="86.4" hidden="1">
       <c r="A46">
         <v>45</v>
       </c>
@@ -6969,7 +7148,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="244.8">
+    <row r="47" spans="1:8" ht="244.8" hidden="1">
       <c r="A47">
         <v>46</v>
       </c>
@@ -6989,7 +7168,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="115.2">
+    <row r="48" spans="1:8" ht="115.2" hidden="1">
       <c r="A48">
         <v>47</v>
       </c>
@@ -7009,7 +7188,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="72">
+    <row r="49" spans="1:8" ht="72" hidden="1">
       <c r="A49">
         <v>48</v>
       </c>
@@ -7029,7 +7208,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="259.2">
+    <row r="50" spans="1:8" ht="259.2" hidden="1">
       <c r="A50">
         <v>49</v>
       </c>
@@ -7049,7 +7228,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="115.2">
+    <row r="51" spans="1:8" ht="115.2" hidden="1">
       <c r="A51">
         <v>50</v>
       </c>
@@ -7069,7 +7248,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="43.2">
+    <row r="52" spans="1:8" ht="43.2" hidden="1">
       <c r="A52">
         <v>51</v>
       </c>
@@ -7089,7 +7268,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="86.4">
+    <row r="53" spans="1:8" ht="86.4" hidden="1">
       <c r="A53">
         <v>52</v>
       </c>
@@ -7109,7 +7288,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="43.2">
+    <row r="54" spans="1:8" ht="43.2" hidden="1">
       <c r="A54">
         <v>53</v>
       </c>
@@ -7129,7 +7308,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="57.6">
+    <row r="55" spans="1:8" ht="57.6" hidden="1">
       <c r="A55">
         <v>54</v>
       </c>
@@ -7149,7 +7328,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="57.6">
+    <row r="56" spans="1:8" ht="57.6" hidden="1">
       <c r="A56">
         <v>55</v>
       </c>
@@ -7169,7 +7348,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="100.8">
+    <row r="57" spans="1:8" ht="100.8" hidden="1">
       <c r="A57">
         <v>56</v>
       </c>
@@ -7189,7 +7368,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="115.2">
+    <row r="58" spans="1:8" ht="115.2" hidden="1">
       <c r="A58">
         <v>57</v>
       </c>
@@ -7209,7 +7388,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="57.6">
+    <row r="59" spans="1:8" ht="57.6" hidden="1">
       <c r="A59">
         <v>58</v>
       </c>
@@ -7229,7 +7408,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="158.4">
+    <row r="60" spans="1:8" ht="158.4" hidden="1">
       <c r="A60">
         <v>59</v>
       </c>
@@ -7249,7 +7428,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="158.4">
+    <row r="61" spans="1:8" ht="158.4" hidden="1">
       <c r="A61">
         <v>60</v>
       </c>
@@ -7269,7 +7448,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="158.4">
+    <row r="62" spans="1:8" ht="158.4" hidden="1">
       <c r="A62">
         <v>61</v>
       </c>
@@ -7289,7 +7468,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="158.4">
+    <row r="63" spans="1:8" ht="158.4" hidden="1">
       <c r="A63">
         <v>62</v>
       </c>
@@ -7309,7 +7488,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="158.4">
+    <row r="64" spans="1:8" ht="158.4" hidden="1">
       <c r="A64">
         <v>63</v>
       </c>
@@ -7329,7 +7508,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="158.4">
+    <row r="65" spans="1:8" ht="158.4" hidden="1">
       <c r="A65">
         <v>64</v>
       </c>
@@ -7349,7 +7528,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="158.4">
+    <row r="66" spans="1:8" ht="158.4" hidden="1">
       <c r="A66">
         <v>65</v>
       </c>
@@ -7369,7 +7548,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="158.4">
+    <row r="67" spans="1:8" ht="158.4" hidden="1">
       <c r="A67">
         <v>66</v>
       </c>
@@ -7389,7 +7568,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="129.6">
+    <row r="68" spans="1:8" ht="129.6" hidden="1">
       <c r="A68">
         <v>67</v>
       </c>
@@ -7409,7 +7588,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="72">
+    <row r="69" spans="1:8" ht="72" hidden="1">
       <c r="A69">
         <v>68</v>
       </c>
@@ -7429,7 +7608,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="72">
+    <row r="70" spans="1:8" ht="72" hidden="1">
       <c r="A70">
         <v>69</v>
       </c>
@@ -7449,7 +7628,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="115.2">
+    <row r="71" spans="1:8" ht="115.2" hidden="1">
       <c r="A71">
         <v>70</v>
       </c>
@@ -7469,7 +7648,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="115.2">
+    <row r="72" spans="1:8" ht="115.2" hidden="1">
       <c r="A72">
         <v>71</v>
       </c>
@@ -7489,7 +7668,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="115.2">
+    <row r="73" spans="1:8" ht="115.2" hidden="1">
       <c r="A73">
         <v>72</v>
       </c>
@@ -7509,7 +7688,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="126.6" customHeight="1">
+    <row r="74" spans="1:8" ht="126.6" hidden="1" customHeight="1">
       <c r="A74">
         <v>73</v>
       </c>
@@ -7525,11 +7704,11 @@
       <c r="E74" s="2">
         <v>45839</v>
       </c>
-      <c r="H74" s="5" t="s">
+      <c r="H74" s="4" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="28.8">
+    <row r="75" spans="1:8" ht="28.8" hidden="1">
       <c r="A75">
         <v>74</v>
       </c>
@@ -7549,7 +7728,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="158.4">
+    <row r="76" spans="1:8" ht="158.4" hidden="1">
       <c r="A76">
         <v>75</v>
       </c>
@@ -7569,7 +7748,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="28.8">
+    <row r="77" spans="1:8" ht="28.8" hidden="1">
       <c r="A77">
         <v>76</v>
       </c>
@@ -7589,7 +7768,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="43.2">
+    <row r="78" spans="1:8" ht="43.2" hidden="1">
       <c r="A78">
         <v>77</v>
       </c>
@@ -7609,7 +7788,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="43.2">
+    <row r="79" spans="1:8" ht="43.2" hidden="1">
       <c r="A79">
         <v>78</v>
       </c>
@@ -7620,7 +7799,7 @@
         <v>1</v>
       </c>
       <c r="D79" t="s">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="E79" s="2">
         <v>45839</v>
@@ -7629,7 +7808,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="144">
+    <row r="80" spans="1:8" ht="144" hidden="1">
       <c r="A80">
         <v>79</v>
       </c>
@@ -7649,7 +7828,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="28.8">
+    <row r="81" spans="1:8" ht="28.8" hidden="1">
       <c r="A81">
         <v>80</v>
       </c>
@@ -7669,7 +7848,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="57.6">
+    <row r="82" spans="1:8" ht="57.6" hidden="1">
       <c r="A82">
         <v>81</v>
       </c>
@@ -7689,7 +7868,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="28.8">
+    <row r="83" spans="1:8" ht="28.8" hidden="1">
       <c r="A83">
         <v>82</v>
       </c>
@@ -7709,7 +7888,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="57.6">
+    <row r="84" spans="1:8" ht="57.6" hidden="1">
       <c r="A84">
         <v>83</v>
       </c>
@@ -7729,7 +7908,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="115.2">
+    <row r="85" spans="1:8" ht="115.2" hidden="1">
       <c r="A85">
         <v>84</v>
       </c>
@@ -7749,7 +7928,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="57.6">
+    <row r="86" spans="1:8" ht="57.6" hidden="1">
       <c r="A86">
         <v>85</v>
       </c>
@@ -7769,7 +7948,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="72">
+    <row r="87" spans="1:8" ht="72" hidden="1">
       <c r="A87">
         <v>86</v>
       </c>
@@ -7789,7 +7968,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="43.2">
+    <row r="88" spans="1:8" ht="43.2" hidden="1">
       <c r="A88">
         <v>87</v>
       </c>
@@ -7809,7 +7988,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="100.8">
+    <row r="89" spans="1:8" ht="100.8" hidden="1">
       <c r="A89">
         <v>88</v>
       </c>
@@ -7829,7 +8008,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="72">
+    <row r="90" spans="1:8" ht="72" hidden="1">
       <c r="A90">
         <v>89</v>
       </c>
@@ -7849,7 +8028,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="57.6">
+    <row r="91" spans="1:8" ht="57.6" hidden="1">
       <c r="A91">
         <v>90</v>
       </c>
@@ -7869,7 +8048,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="43.2">
+    <row r="92" spans="1:8" ht="43.2" hidden="1">
       <c r="A92">
         <v>91</v>
       </c>
@@ -7889,7 +8068,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="57.6">
+    <row r="93" spans="1:8" ht="57.6" hidden="1">
       <c r="A93">
         <v>92</v>
       </c>
@@ -7909,7 +8088,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="72">
+    <row r="94" spans="1:8" ht="72" hidden="1">
       <c r="A94">
         <v>93</v>
       </c>
@@ -7929,7 +8108,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="86.4">
+    <row r="95" spans="1:8" ht="86.4" hidden="1">
       <c r="A95">
         <v>94</v>
       </c>
@@ -7949,7 +8128,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="72">
+    <row r="96" spans="1:8" ht="72" hidden="1">
       <c r="A96">
         <v>95</v>
       </c>
@@ -7969,7 +8148,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="72">
+    <row r="97" spans="1:8" ht="72" hidden="1">
       <c r="A97">
         <v>96</v>
       </c>
@@ -7989,7 +8168,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="86.4">
+    <row r="98" spans="1:8" ht="86.4" hidden="1">
       <c r="A98">
         <v>97</v>
       </c>
@@ -8009,7 +8188,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="43.2">
+    <row r="99" spans="1:8" ht="43.2" hidden="1">
       <c r="A99">
         <v>98</v>
       </c>
@@ -8029,7 +8208,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="57.6">
+    <row r="100" spans="1:8" ht="57.6" hidden="1">
       <c r="A100">
         <v>99</v>
       </c>
@@ -8049,7 +8228,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="57.6">
+    <row r="101" spans="1:8" ht="57.6" hidden="1">
       <c r="A101">
         <v>100</v>
       </c>
@@ -8069,7 +8248,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="129.6">
+    <row r="102" spans="1:8" ht="129.6" hidden="1">
       <c r="A102">
         <v>101</v>
       </c>
@@ -8089,7 +8268,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="244.8">
+    <row r="103" spans="1:8" ht="244.8" hidden="1">
       <c r="A103">
         <v>102</v>
       </c>
@@ -8109,7 +8288,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="43.2">
+    <row r="104" spans="1:8" ht="43.2" hidden="1">
       <c r="A104">
         <v>103</v>
       </c>
@@ -8129,7 +8308,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="43.2">
+    <row r="105" spans="1:8" ht="43.2" hidden="1">
       <c r="A105">
         <v>104</v>
       </c>
@@ -8149,7 +8328,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="28.8">
+    <row r="106" spans="1:8" ht="28.8" hidden="1">
       <c r="A106">
         <v>105</v>
       </c>
@@ -8169,7 +8348,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="43.2">
+    <row r="107" spans="1:8" ht="43.2" hidden="1">
       <c r="A107">
         <v>106</v>
       </c>
@@ -8189,7 +8368,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="216">
+    <row r="108" spans="1:8" ht="216" hidden="1">
       <c r="A108">
         <v>107</v>
       </c>
@@ -8209,7 +8388,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="28.8">
+    <row r="109" spans="1:8" ht="28.8" hidden="1">
       <c r="A109">
         <v>108</v>
       </c>
@@ -8229,7 +8408,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="28.8">
+    <row r="110" spans="1:8" ht="28.8" hidden="1">
       <c r="A110">
         <v>109</v>
       </c>
@@ -8249,7 +8428,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="28.8">
+    <row r="111" spans="1:8" ht="28.8" hidden="1">
       <c r="A111">
         <v>110</v>
       </c>
@@ -8269,7 +8448,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="43.2">
+    <row r="112" spans="1:8" ht="43.2" hidden="1">
       <c r="A112">
         <v>111</v>
       </c>
@@ -8289,7 +8468,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="28.8">
+    <row r="113" spans="1:8" ht="28.8" hidden="1">
       <c r="A113">
         <v>112</v>
       </c>
@@ -8309,7 +8488,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="72">
+    <row r="114" spans="1:8" ht="72" hidden="1">
       <c r="A114">
         <v>113</v>
       </c>
@@ -8329,7 +8508,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="28.8">
+    <row r="115" spans="1:8" ht="28.8" hidden="1">
       <c r="A115">
         <v>114</v>
       </c>
@@ -8349,7 +8528,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="43.2">
+    <row r="116" spans="1:8" ht="43.2" hidden="1">
       <c r="A116">
         <v>115</v>
       </c>
@@ -8369,7 +8548,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="28.8">
+    <row r="117" spans="1:8" ht="28.8" hidden="1">
       <c r="A117">
         <v>116</v>
       </c>
@@ -8389,7 +8568,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="28.8">
+    <row r="118" spans="1:8" ht="28.8" hidden="1">
       <c r="A118">
         <v>117</v>
       </c>
@@ -8423,7 +8602,7 @@
         <v>83</v>
       </c>
       <c r="E119" s="2">
-        <v>45839</v>
+        <v>45658</v>
       </c>
       <c r="H119" s="3" t="s">
         <v>513</v>
@@ -8443,7 +8622,7 @@
         <v>83</v>
       </c>
       <c r="E120" s="2">
-        <v>45839</v>
+        <v>45658</v>
       </c>
       <c r="H120" s="3" t="s">
         <v>514</v>
@@ -8463,7 +8642,7 @@
         <v>83</v>
       </c>
       <c r="E121" s="2">
-        <v>45839</v>
+        <v>45658</v>
       </c>
       <c r="H121" s="3" t="s">
         <v>515</v>
@@ -8483,7 +8662,7 @@
         <v>83</v>
       </c>
       <c r="E122" s="2">
-        <v>45839</v>
+        <v>45658</v>
       </c>
       <c r="H122" s="3" t="s">
         <v>516</v>
@@ -8500,10 +8679,10 @@
         <v>1</v>
       </c>
       <c r="D123" t="s">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="E123" s="2">
-        <v>45839</v>
+        <v>45658</v>
       </c>
       <c r="H123" s="3" t="s">
         <v>517</v>
@@ -8520,17 +8699,180 @@
         <v>1</v>
       </c>
       <c r="D124" t="s">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="E124" s="2">
-        <v>45839</v>
+        <v>45658</v>
       </c>
       <c r="H124" s="3" t="s">
         <v>518</v>
       </c>
     </row>
+    <row r="125" spans="1:8" ht="72" hidden="1">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125" t="s">
+        <v>525</v>
+      </c>
+      <c r="C125">
+        <v>1</v>
+      </c>
+      <c r="D125" t="s">
+        <v>83</v>
+      </c>
+      <c r="E125" s="2">
+        <v>45901</v>
+      </c>
+      <c r="H125" s="3" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" ht="72" hidden="1">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126" t="s">
+        <v>526</v>
+      </c>
+      <c r="C126">
+        <v>1</v>
+      </c>
+      <c r="D126" t="s">
+        <v>83</v>
+      </c>
+      <c r="E126" s="2">
+        <v>45901</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" ht="57.6" hidden="1">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" t="s">
+        <v>172</v>
+      </c>
+      <c r="C127">
+        <v>3</v>
+      </c>
+      <c r="D127" t="s">
+        <v>83</v>
+      </c>
+      <c r="E127" s="2">
+        <v>45901</v>
+      </c>
+      <c r="G127" t="s">
+        <v>534</v>
+      </c>
+      <c r="H127" s="3" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" ht="172.8" hidden="1">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128" t="s">
+        <v>339</v>
+      </c>
+      <c r="C128">
+        <v>3</v>
+      </c>
+      <c r="D128" t="s">
+        <v>83</v>
+      </c>
+      <c r="E128" s="2">
+        <v>45901</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="H128" s="3" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" ht="43.2" hidden="1">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129" t="s">
+        <v>539</v>
+      </c>
+      <c r="C129">
+        <v>3</v>
+      </c>
+      <c r="D129" t="s">
+        <v>83</v>
+      </c>
+      <c r="E129" s="2">
+        <v>45901</v>
+      </c>
+      <c r="H129" s="3" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="43.2">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130" t="s">
+        <v>523</v>
+      </c>
+      <c r="C130">
+        <v>3</v>
+      </c>
+      <c r="D130" t="s">
+        <v>83</v>
+      </c>
+      <c r="E130" s="2">
+        <v>45901</v>
+      </c>
+      <c r="G130" t="s">
+        <v>542</v>
+      </c>
+      <c r="H130" s="3" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="301.2" customHeight="1">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131" t="s">
+        <v>524</v>
+      </c>
+      <c r="C131">
+        <v>3</v>
+      </c>
+      <c r="D131" t="s">
+        <v>83</v>
+      </c>
+      <c r="E131" s="2">
+        <v>45870</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="H131" s="3" t="s">
+        <v>543</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H50" xr:uid="{D500C81C-80F5-46C0-959E-2202AF945DAB}"/>
+  <autoFilter ref="A1:H131" xr:uid="{D500C81C-80F5-46C0-959E-2202AF945DAB}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="LR81"/>
+        <filter val="LR82"/>
+        <filter val="LR83"/>
+        <filter val="LR84"/>
+        <filter val="LR85"/>
+        <filter val="LR86"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
